--- a/budget/output/Сводный бюджет СПб.xlsx
+++ b/budget/output/Сводный бюджет СПб.xlsx
@@ -2657,35 +2657,35 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF(B4=0,"-",B43/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IF(C4=0,"-",C43/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IF(D4=0,"-",D43/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D43/D4),"-")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IF(E4=0,"-",E43/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E43/E4),"-")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(F4=0,"-",F43/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F43/F4),"-")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IF(G4=0,"-",G43/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IF(H4=0,"-",H43/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IF(I4=0,"-",I43/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
@@ -4507,35 +4507,35 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IF(B4=0,"-",B80/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IF(C4=0,"-",C80/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IF(D4=0,"-",D80/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D80/D4),"-")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IF(E4=0,"-",E80/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E80/E4),"-")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(F4=0,"-",F80/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F80/F4),"-")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IF(G4=0,"-",G80/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IF(H4=0,"-",H80/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IF(I4=0,"-",I80/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
@@ -4907,35 +4907,35 @@
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B80+B82-B87</f>
+        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>C80+C82-C87</f>
+        <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
         <v/>
       </c>
       <c r="D89" s="9">
-        <f>D80+D82-D87</f>
+        <f>D80+IFERROR(D82*1,0)-IFERROR(D87*1,0)</f>
         <v/>
       </c>
       <c r="E89" s="9">
-        <f>E80+E82-E87</f>
+        <f>E80+IFERROR(E82*1,0)-IFERROR(E87*1,0)</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>F80+F82-F87</f>
+        <f>F80+IFERROR(F82*1,0)-IFERROR(F87*1,0)</f>
         <v/>
       </c>
       <c r="G89" s="9">
-        <f>G80+G82-G87</f>
+        <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>H80+H82-H87</f>
+        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
         <v/>
       </c>
       <c r="I89" s="9">
-        <f>I80+I82-I87</f>
+        <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
@@ -4957,35 +4957,35 @@
         </is>
       </c>
       <c r="B90" s="10">
-        <f>IF(B4=0,"-",B89/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
         <v/>
       </c>
       <c r="C90" s="10">
-        <f>IF(C4=0,"-",C89/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
         <v/>
       </c>
       <c r="D90" s="10">
-        <f>IF(D4=0,"-",D89/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D89/D4),"-")</f>
         <v/>
       </c>
       <c r="E90" s="10">
-        <f>IF(E4=0,"-",E89/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E89/E4),"-")</f>
         <v/>
       </c>
       <c r="F90" s="10">
-        <f>IF(F4=0,"-",F89/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F89/F4),"-")</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>IF(G4=0,"-",G89/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
       <c r="H90" s="10">
-        <f>IF(H4=0,"-",H89/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
         <v/>
       </c>
       <c r="I90" s="10">
-        <f>IF(I4=0,"-",I89/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
@@ -5357,35 +5357,35 @@
         </is>
       </c>
       <c r="B98" s="9">
-        <f>B89-B91-B94-B95</f>
+        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
         <v/>
       </c>
       <c r="C98" s="9">
-        <f>C89-C91-C94-C95</f>
+        <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
         <v/>
       </c>
       <c r="D98" s="9">
-        <f>D89-D91-D94-D95</f>
+        <f>IFERROR(D89*1,0)-IFERROR(D91*1,0)-IFERROR(D94*1,0)-IFERROR(D95*1,0)</f>
         <v/>
       </c>
       <c r="E98" s="9">
-        <f>E89-E91-E94-E95</f>
+        <f>IFERROR(E89*1,0)-IFERROR(E91*1,0)-IFERROR(E94*1,0)-IFERROR(E95*1,0)</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>F89-F91-F94-F95</f>
+        <f>IFERROR(F89*1,0)-IFERROR(F91*1,0)-IFERROR(F94*1,0)-IFERROR(F95*1,0)</f>
         <v/>
       </c>
       <c r="G98" s="9">
-        <f>G89-G91-G94-G95</f>
+        <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>H89-H91-H94-H95</f>
+        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
         <v/>
       </c>
       <c r="I98" s="9">
-        <f>I89-I91-I94-I95</f>
+        <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
@@ -5407,35 +5407,35 @@
         </is>
       </c>
       <c r="B99" s="10">
-        <f>IF(B4=0,"-",B98/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
         <v/>
       </c>
       <c r="C99" s="10">
-        <f>IF(C4=0,"-",C98/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
         <v/>
       </c>
       <c r="D99" s="10">
-        <f>IF(D4=0,"-",D98/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D98/D4),"-")</f>
         <v/>
       </c>
       <c r="E99" s="10">
-        <f>IF(E4=0,"-",E98/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E98/E4),"-")</f>
         <v/>
       </c>
       <c r="F99" s="10">
-        <f>IF(F4=0,"-",F98/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F98/F4),"-")</f>
         <v/>
       </c>
       <c r="G99" s="10">
-        <f>IF(G4=0,"-",G98/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
       <c r="H99" s="10">
-        <f>IF(H4=0,"-",H98/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
         <v/>
       </c>
       <c r="I99" s="10">
-        <f>IF(I4=0,"-",I98/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>
@@ -7820,35 +7820,35 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF(B4=0,"-",B43/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IF(C4=0,"-",C43/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IF(D4=0,"-",D43/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D43/D4),"-")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IF(E4=0,"-",E43/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E43/E4),"-")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(F4=0,"-",F43/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F43/F4),"-")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IF(G4=0,"-",G43/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IF(H4=0,"-",H43/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IF(I4=0,"-",I43/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
@@ -9289,18 +9289,42 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Создано с помощью сервиса ПланФакт</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Перейти в сервис</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" s="4" t="n"/>
@@ -9894,35 +9918,35 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IF(B4=0,"-",B80/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IF(C4=0,"-",C80/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IF(D4=0,"-",D80/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D80/D4),"-")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IF(E4=0,"-",E80/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E80/E4),"-")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(F4=0,"-",F80/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F80/F4),"-")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IF(G4=0,"-",G80/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IF(H4=0,"-",H80/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IF(I4=0,"-",I80/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
@@ -10334,35 +10358,35 @@
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B80+B82-B87</f>
+        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>C80+C82-C87</f>
+        <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
         <v/>
       </c>
       <c r="D89" s="9">
-        <f>D80+D82-D87</f>
+        <f>D80+IFERROR(D82*1,0)-IFERROR(D87*1,0)</f>
         <v/>
       </c>
       <c r="E89" s="9">
-        <f>E80+E82-E87</f>
+        <f>E80+IFERROR(E82*1,0)-IFERROR(E87*1,0)</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>F80+F82-F87</f>
+        <f>F80+IFERROR(F82*1,0)-IFERROR(F87*1,0)</f>
         <v/>
       </c>
       <c r="G89" s="9">
-        <f>G80+G82-G87</f>
+        <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>H80+H82-H87</f>
+        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
         <v/>
       </c>
       <c r="I89" s="9">
-        <f>I80+I82-I87</f>
+        <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
@@ -10384,35 +10408,35 @@
         </is>
       </c>
       <c r="B90" s="10">
-        <f>IF(B4=0,"-",B89/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
         <v/>
       </c>
       <c r="C90" s="10">
-        <f>IF(C4=0,"-",C89/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
         <v/>
       </c>
       <c r="D90" s="10">
-        <f>IF(D4=0,"-",D89/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D89/D4),"-")</f>
         <v/>
       </c>
       <c r="E90" s="10">
-        <f>IF(E4=0,"-",E89/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E89/E4),"-")</f>
         <v/>
       </c>
       <c r="F90" s="10">
-        <f>IF(F4=0,"-",F89/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F89/F4),"-")</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>IF(G4=0,"-",G89/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
       <c r="H90" s="10">
-        <f>IF(H4=0,"-",H89/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
         <v/>
       </c>
       <c r="I90" s="10">
-        <f>IF(I4=0,"-",I89/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
@@ -10814,35 +10838,35 @@
         </is>
       </c>
       <c r="B98" s="9">
-        <f>B89-B91-B94-B95</f>
+        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
         <v/>
       </c>
       <c r="C98" s="9">
-        <f>C89-C91-C94-C95</f>
+        <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
         <v/>
       </c>
       <c r="D98" s="9">
-        <f>D89-D91-D94-D95</f>
+        <f>IFERROR(D89*1,0)-IFERROR(D91*1,0)-IFERROR(D94*1,0)-IFERROR(D95*1,0)</f>
         <v/>
       </c>
       <c r="E98" s="9">
-        <f>E89-E91-E94-E95</f>
+        <f>IFERROR(E89*1,0)-IFERROR(E91*1,0)-IFERROR(E94*1,0)-IFERROR(E95*1,0)</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>F89-F91-F94-F95</f>
+        <f>IFERROR(F89*1,0)-IFERROR(F91*1,0)-IFERROR(F94*1,0)-IFERROR(F95*1,0)</f>
         <v/>
       </c>
       <c r="G98" s="9">
-        <f>G89-G91-G94-G95</f>
+        <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>H89-H91-H94-H95</f>
+        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
         <v/>
       </c>
       <c r="I98" s="9">
-        <f>I89-I91-I94-I95</f>
+        <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
@@ -10864,35 +10888,35 @@
         </is>
       </c>
       <c r="B99" s="10">
-        <f>IF(B4=0,"-",B98/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
         <v/>
       </c>
       <c r="C99" s="10">
-        <f>IF(C4=0,"-",C98/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
         <v/>
       </c>
       <c r="D99" s="10">
-        <f>IF(D4=0,"-",D98/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D98/D4),"-")</f>
         <v/>
       </c>
       <c r="E99" s="10">
-        <f>IF(E4=0,"-",E98/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E98/E4),"-")</f>
         <v/>
       </c>
       <c r="F99" s="10">
-        <f>IF(F4=0,"-",F98/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F98/F4),"-")</f>
         <v/>
       </c>
       <c r="G99" s="10">
-        <f>IF(G4=0,"-",G98/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
       <c r="H99" s="10">
-        <f>IF(H4=0,"-",H98/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
         <v/>
       </c>
       <c r="I99" s="10">
-        <f>IF(I4=0,"-",I98/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>
@@ -13277,35 +13301,35 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF(B4=0,"-",B43/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IF(C4=0,"-",C43/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IF(D4=0,"-",D43/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D43/D4),"-")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IF(E4=0,"-",E43/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E43/E4),"-")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(F4=0,"-",F43/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F43/F4),"-")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IF(G4=0,"-",G43/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IF(H4=0,"-",H43/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IF(I4=0,"-",I43/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
@@ -14746,18 +14770,42 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Создано с помощью сервиса ПланФакт</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Перейти в сервис</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" s="4" t="n"/>
@@ -15351,35 +15399,35 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IF(B4=0,"-",B80/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IF(C4=0,"-",C80/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IF(D4=0,"-",D80/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D80/D4),"-")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IF(E4=0,"-",E80/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E80/E4),"-")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(F4=0,"-",F80/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F80/F4),"-")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IF(G4=0,"-",G80/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IF(H4=0,"-",H80/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IF(I4=0,"-",I80/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
@@ -15791,35 +15839,35 @@
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B80+B82-B87</f>
+        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>C80+C82-C87</f>
+        <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
         <v/>
       </c>
       <c r="D89" s="9">
-        <f>D80+D82-D87</f>
+        <f>D80+IFERROR(D82*1,0)-IFERROR(D87*1,0)</f>
         <v/>
       </c>
       <c r="E89" s="9">
-        <f>E80+E82-E87</f>
+        <f>E80+IFERROR(E82*1,0)-IFERROR(E87*1,0)</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>F80+F82-F87</f>
+        <f>F80+IFERROR(F82*1,0)-IFERROR(F87*1,0)</f>
         <v/>
       </c>
       <c r="G89" s="9">
-        <f>G80+G82-G87</f>
+        <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>H80+H82-H87</f>
+        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
         <v/>
       </c>
       <c r="I89" s="9">
-        <f>I80+I82-I87</f>
+        <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
@@ -15841,35 +15889,35 @@
         </is>
       </c>
       <c r="B90" s="10">
-        <f>IF(B4=0,"-",B89/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
         <v/>
       </c>
       <c r="C90" s="10">
-        <f>IF(C4=0,"-",C89/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
         <v/>
       </c>
       <c r="D90" s="10">
-        <f>IF(D4=0,"-",D89/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D89/D4),"-")</f>
         <v/>
       </c>
       <c r="E90" s="10">
-        <f>IF(E4=0,"-",E89/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E89/E4),"-")</f>
         <v/>
       </c>
       <c r="F90" s="10">
-        <f>IF(F4=0,"-",F89/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F89/F4),"-")</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>IF(G4=0,"-",G89/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
       <c r="H90" s="10">
-        <f>IF(H4=0,"-",H89/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
         <v/>
       </c>
       <c r="I90" s="10">
-        <f>IF(I4=0,"-",I89/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
@@ -16271,35 +16319,35 @@
         </is>
       </c>
       <c r="B98" s="9">
-        <f>B89-B91-B94-B95</f>
+        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
         <v/>
       </c>
       <c r="C98" s="9">
-        <f>C89-C91-C94-C95</f>
+        <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
         <v/>
       </c>
       <c r="D98" s="9">
-        <f>D89-D91-D94-D95</f>
+        <f>IFERROR(D89*1,0)-IFERROR(D91*1,0)-IFERROR(D94*1,0)-IFERROR(D95*1,0)</f>
         <v/>
       </c>
       <c r="E98" s="9">
-        <f>E89-E91-E94-E95</f>
+        <f>IFERROR(E89*1,0)-IFERROR(E91*1,0)-IFERROR(E94*1,0)-IFERROR(E95*1,0)</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>F89-F91-F94-F95</f>
+        <f>IFERROR(F89*1,0)-IFERROR(F91*1,0)-IFERROR(F94*1,0)-IFERROR(F95*1,0)</f>
         <v/>
       </c>
       <c r="G98" s="9">
-        <f>G89-G91-G94-G95</f>
+        <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>H89-H91-H94-H95</f>
+        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
         <v/>
       </c>
       <c r="I98" s="9">
-        <f>I89-I91-I94-I95</f>
+        <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
@@ -16321,35 +16369,35 @@
         </is>
       </c>
       <c r="B99" s="10">
-        <f>IF(B4=0,"-",B98/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
         <v/>
       </c>
       <c r="C99" s="10">
-        <f>IF(C4=0,"-",C98/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
         <v/>
       </c>
       <c r="D99" s="10">
-        <f>IF(D4=0,"-",D98/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D98/D4),"-")</f>
         <v/>
       </c>
       <c r="E99" s="10">
-        <f>IF(E4=0,"-",E98/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E98/E4),"-")</f>
         <v/>
       </c>
       <c r="F99" s="10">
-        <f>IF(F4=0,"-",F98/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F98/F4),"-")</f>
         <v/>
       </c>
       <c r="G99" s="10">
-        <f>IF(G4=0,"-",G98/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
       <c r="H99" s="10">
-        <f>IF(H4=0,"-",H98/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
         <v/>
       </c>
       <c r="I99" s="10">
-        <f>IF(I4=0,"-",I98/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>
@@ -18712,35 +18760,35 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF(B4=0,"-",B43/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IF(C4=0,"-",C43/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IF(D4=0,"-",D43/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D43/D4),"-")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IF(E4=0,"-",E43/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E43/E4),"-")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(F4=0,"-",F43/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F43/F4),"-")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IF(G4=0,"-",G43/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IF(H4=0,"-",H43/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IF(I4=0,"-",I43/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
@@ -20181,18 +20229,42 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Создано с помощью сервиса ПланФакт</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Перейти в сервис</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" s="4" t="n"/>
@@ -20786,35 +20858,35 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IF(B4=0,"-",B80/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IF(C4=0,"-",C80/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IF(D4=0,"-",D80/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D80/D4),"-")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IF(E4=0,"-",E80/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E80/E4),"-")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(F4=0,"-",F80/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F80/F4),"-")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IF(G4=0,"-",G80/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IF(H4=0,"-",H80/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IF(I4=0,"-",I80/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
@@ -21226,35 +21298,35 @@
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B80+B82-B87</f>
+        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>C80+C82-C87</f>
+        <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
         <v/>
       </c>
       <c r="D89" s="9">
-        <f>D80+D82-D87</f>
+        <f>D80+IFERROR(D82*1,0)-IFERROR(D87*1,0)</f>
         <v/>
       </c>
       <c r="E89" s="9">
-        <f>E80+E82-E87</f>
+        <f>E80+IFERROR(E82*1,0)-IFERROR(E87*1,0)</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>F80+F82-F87</f>
+        <f>F80+IFERROR(F82*1,0)-IFERROR(F87*1,0)</f>
         <v/>
       </c>
       <c r="G89" s="9">
-        <f>G80+G82-G87</f>
+        <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>H80+H82-H87</f>
+        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
         <v/>
       </c>
       <c r="I89" s="9">
-        <f>I80+I82-I87</f>
+        <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
@@ -21276,35 +21348,35 @@
         </is>
       </c>
       <c r="B90" s="10">
-        <f>IF(B4=0,"-",B89/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
         <v/>
       </c>
       <c r="C90" s="10">
-        <f>IF(C4=0,"-",C89/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
         <v/>
       </c>
       <c r="D90" s="10">
-        <f>IF(D4=0,"-",D89/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D89/D4),"-")</f>
         <v/>
       </c>
       <c r="E90" s="10">
-        <f>IF(E4=0,"-",E89/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E89/E4),"-")</f>
         <v/>
       </c>
       <c r="F90" s="10">
-        <f>IF(F4=0,"-",F89/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F89/F4),"-")</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>IF(G4=0,"-",G89/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
       <c r="H90" s="10">
-        <f>IF(H4=0,"-",H89/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
         <v/>
       </c>
       <c r="I90" s="10">
-        <f>IF(I4=0,"-",I89/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
@@ -21692,35 +21764,35 @@
         </is>
       </c>
       <c r="B98" s="9">
-        <f>B89-B91-B94-B95</f>
+        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
         <v/>
       </c>
       <c r="C98" s="9">
-        <f>C89-C91-C94-C95</f>
+        <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
         <v/>
       </c>
       <c r="D98" s="9">
-        <f>D89-D91-D94-D95</f>
+        <f>IFERROR(D89*1,0)-IFERROR(D91*1,0)-IFERROR(D94*1,0)-IFERROR(D95*1,0)</f>
         <v/>
       </c>
       <c r="E98" s="9">
-        <f>E89-E91-E94-E95</f>
+        <f>IFERROR(E89*1,0)-IFERROR(E91*1,0)-IFERROR(E94*1,0)-IFERROR(E95*1,0)</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>F89-F91-F94-F95</f>
+        <f>IFERROR(F89*1,0)-IFERROR(F91*1,0)-IFERROR(F94*1,0)-IFERROR(F95*1,0)</f>
         <v/>
       </c>
       <c r="G98" s="9">
-        <f>G89-G91-G94-G95</f>
+        <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>H89-H91-H94-H95</f>
+        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
         <v/>
       </c>
       <c r="I98" s="9">
-        <f>I89-I91-I94-I95</f>
+        <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
@@ -21742,35 +21814,35 @@
         </is>
       </c>
       <c r="B99" s="10">
-        <f>IF(B4=0,"-",B98/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
         <v/>
       </c>
       <c r="C99" s="10">
-        <f>IF(C4=0,"-",C98/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
         <v/>
       </c>
       <c r="D99" s="10">
-        <f>IF(D4=0,"-",D98/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D98/D4),"-")</f>
         <v/>
       </c>
       <c r="E99" s="10">
-        <f>IF(E4=0,"-",E98/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E98/E4),"-")</f>
         <v/>
       </c>
       <c r="F99" s="10">
-        <f>IF(F4=0,"-",F98/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F98/F4),"-")</f>
         <v/>
       </c>
       <c r="G99" s="10">
-        <f>IF(G4=0,"-",G98/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
       <c r="H99" s="10">
-        <f>IF(H4=0,"-",H98/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
         <v/>
       </c>
       <c r="I99" s="10">
-        <f>IF(I4=0,"-",I98/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>
@@ -24127,35 +24199,35 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF(B4=0,"-",B43/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IF(C4=0,"-",C43/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IF(D4=0,"-",D43/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D43/D4),"-")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IF(E4=0,"-",E43/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E43/E4),"-")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(F4=0,"-",F43/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F43/F4),"-")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IF(G4=0,"-",G43/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IF(H4=0,"-",H43/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IF(I4=0,"-",I43/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
@@ -25596,18 +25668,42 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Создано с помощью сервиса ПланФакт</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Перейти в сервис</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" s="4" t="n"/>
@@ -26201,35 +26297,35 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IF(B4=0,"-",B80/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IF(C4=0,"-",C80/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IF(D4=0,"-",D80/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D80/D4),"-")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IF(E4=0,"-",E80/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E80/E4),"-")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(F4=0,"-",F80/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F80/F4),"-")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IF(G4=0,"-",G80/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IF(H4=0,"-",H80/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IF(I4=0,"-",I80/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
@@ -26641,35 +26737,35 @@
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B80+B82-B87</f>
+        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>C80+C82-C87</f>
+        <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
         <v/>
       </c>
       <c r="D89" s="9">
-        <f>D80+D82-D87</f>
+        <f>D80+IFERROR(D82*1,0)-IFERROR(D87*1,0)</f>
         <v/>
       </c>
       <c r="E89" s="9">
-        <f>E80+E82-E87</f>
+        <f>E80+IFERROR(E82*1,0)-IFERROR(E87*1,0)</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>F80+F82-F87</f>
+        <f>F80+IFERROR(F82*1,0)-IFERROR(F87*1,0)</f>
         <v/>
       </c>
       <c r="G89" s="9">
-        <f>G80+G82-G87</f>
+        <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>H80+H82-H87</f>
+        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
         <v/>
       </c>
       <c r="I89" s="9">
-        <f>I80+I82-I87</f>
+        <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
@@ -26691,35 +26787,35 @@
         </is>
       </c>
       <c r="B90" s="10">
-        <f>IF(B4=0,"-",B89/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
         <v/>
       </c>
       <c r="C90" s="10">
-        <f>IF(C4=0,"-",C89/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
         <v/>
       </c>
       <c r="D90" s="10">
-        <f>IF(D4=0,"-",D89/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D89/D4),"-")</f>
         <v/>
       </c>
       <c r="E90" s="10">
-        <f>IF(E4=0,"-",E89/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E89/E4),"-")</f>
         <v/>
       </c>
       <c r="F90" s="10">
-        <f>IF(F4=0,"-",F89/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F89/F4),"-")</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>IF(G4=0,"-",G89/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
       <c r="H90" s="10">
-        <f>IF(H4=0,"-",H89/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
         <v/>
       </c>
       <c r="I90" s="10">
-        <f>IF(I4=0,"-",I89/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
@@ -27115,35 +27211,35 @@
         </is>
       </c>
       <c r="B98" s="9">
-        <f>B89-B91-B94-B95</f>
+        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
         <v/>
       </c>
       <c r="C98" s="9">
-        <f>C89-C91-C94-C95</f>
+        <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
         <v/>
       </c>
       <c r="D98" s="9">
-        <f>D89-D91-D94-D95</f>
+        <f>IFERROR(D89*1,0)-IFERROR(D91*1,0)-IFERROR(D94*1,0)-IFERROR(D95*1,0)</f>
         <v/>
       </c>
       <c r="E98" s="9">
-        <f>E89-E91-E94-E95</f>
+        <f>IFERROR(E89*1,0)-IFERROR(E91*1,0)-IFERROR(E94*1,0)-IFERROR(E95*1,0)</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>F89-F91-F94-F95</f>
+        <f>IFERROR(F89*1,0)-IFERROR(F91*1,0)-IFERROR(F94*1,0)-IFERROR(F95*1,0)</f>
         <v/>
       </c>
       <c r="G98" s="9">
-        <f>G89-G91-G94-G95</f>
+        <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>H89-H91-H94-H95</f>
+        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
         <v/>
       </c>
       <c r="I98" s="9">
-        <f>I89-I91-I94-I95</f>
+        <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
@@ -27165,35 +27261,35 @@
         </is>
       </c>
       <c r="B99" s="10">
-        <f>IF(B4=0,"-",B98/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
         <v/>
       </c>
       <c r="C99" s="10">
-        <f>IF(C4=0,"-",C98/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
         <v/>
       </c>
       <c r="D99" s="10">
-        <f>IF(D4=0,"-",D98/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D98/D4),"-")</f>
         <v/>
       </c>
       <c r="E99" s="10">
-        <f>IF(E4=0,"-",E98/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E98/E4),"-")</f>
         <v/>
       </c>
       <c r="F99" s="10">
-        <f>IF(F4=0,"-",F98/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F98/F4),"-")</f>
         <v/>
       </c>
       <c r="G99" s="10">
-        <f>IF(G4=0,"-",G98/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
       <c r="H99" s="10">
-        <f>IF(H4=0,"-",H98/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
         <v/>
       </c>
       <c r="I99" s="10">
-        <f>IF(I4=0,"-",I98/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>

--- a/budget/output/Сводный бюджет СПб.xlsx
+++ b/budget/output/Сводный бюджет СПб.xlsx
@@ -680,9 +680,10 @@
         <f>SUM(G5,G6)</f>
         <v/>
       </c>
-      <c r="H4" s="7">
-        <f>SUM(H5,H6)</f>
-        <v/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="7">
         <f>SUM(I5,I6)</f>
@@ -707,7 +708,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>SUM('Астон.Движение'!B5,'Астон.Реформа'!B5,'Милый дом'!B5,'River Park'!B5)</f>
+        <f>SUM(C5,D5,E5,F5)</f>
         <v/>
       </c>
       <c r="C5" s="7">
@@ -730,9 +731,10 @@
         <f>SUM('Астон.Движение'!G5,'Астон.Реформа'!G5,'Милый дом'!G5,'River Park'!G5)</f>
         <v/>
       </c>
-      <c r="H5" s="7">
-        <f>SUM('Астон.Движение'!H5,'Астон.Реформа'!H5,'Милый дом'!H5,'River Park'!H5)</f>
-        <v/>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I5" s="7">
         <f>SUM('Астон.Движение'!I5,'Астон.Реформа'!I5,'Милый дом'!I5,'River Park'!I5)</f>
@@ -780,9 +782,10 @@
         <f>SUM(G7,G8,G9)</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>SUM(H7,H8,H9)</f>
-        <v/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I6" s="7">
         <f>SUM(I7,I8,I9)</f>
@@ -807,7 +810,7 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>SUM('Астон.Движение'!B7,'Астон.Реформа'!B7,'Милый дом'!B7,'River Park'!B7)</f>
+        <f>SUM(C7,D7,E7,F7)</f>
         <v/>
       </c>
       <c r="C7" s="7">
@@ -830,9 +833,10 @@
         <f>SUM('Астон.Движение'!G7,'Астон.Реформа'!G7,'Милый дом'!G7,'River Park'!G7)</f>
         <v/>
       </c>
-      <c r="H7" s="7">
-        <f>SUM('Астон.Движение'!H7,'Астон.Реформа'!H7,'Милый дом'!H7,'River Park'!H7)</f>
-        <v/>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I7" s="7">
         <f>SUM('Астон.Движение'!I7,'Астон.Реформа'!I7,'Милый дом'!I7,'River Park'!I7)</f>
@@ -857,7 +861,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>SUM('Астон.Движение'!B8,'Астон.Реформа'!B8,'Милый дом'!B8,'River Park'!B8)</f>
+        <f>SUM(C8,D8,E8,F8)</f>
         <v/>
       </c>
       <c r="C8" s="7">
@@ -880,9 +884,10 @@
         <f>SUM('Астон.Движение'!G8,'Астон.Реформа'!G8,'Милый дом'!G8,'River Park'!G8)</f>
         <v/>
       </c>
-      <c r="H8" s="7">
-        <f>SUM('Астон.Движение'!H8,'Астон.Реформа'!H8,'Милый дом'!H8,'River Park'!H8)</f>
-        <v/>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I8" s="7">
         <f>SUM('Астон.Движение'!I8,'Астон.Реформа'!I8,'Милый дом'!I8,'River Park'!I8)</f>
@@ -907,7 +912,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>SUM('Астон.Движение'!B9,'Астон.Реформа'!B9,'Милый дом'!B9,'River Park'!B9)</f>
+        <f>SUM(C9,D9,E9,F9)</f>
         <v/>
       </c>
       <c r="C9" s="7">
@@ -930,9 +935,10 @@
         <f>SUM('Астон.Движение'!G9,'Астон.Реформа'!G9,'Милый дом'!G9,'River Park'!G9)</f>
         <v/>
       </c>
-      <c r="H9" s="7">
-        <f>SUM('Астон.Движение'!H9,'Астон.Реформа'!H9,'Милый дом'!H9,'River Park'!H9)</f>
-        <v/>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I9" s="7">
         <f>SUM('Астон.Движение'!I9,'Астон.Реформа'!I9,'Милый дом'!I9,'River Park'!I9)</f>
@@ -980,9 +986,10 @@
         <f>SUM(G11,G12,G13,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30,G31,G32,G33,G34)</f>
         <v/>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(H11,H12,H13,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30,H31,H32,H33,H34)</f>
-        <v/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7">
         <f>SUM(I11,I12,I13,I21,I22,I23,I24,I25,I26,I27,I28,I29,I30,I31,I32,I33,I34)</f>
@@ -1007,7 +1014,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>SUM('Астон.Движение'!B11,'Астон.Реформа'!B11,'Милый дом'!B11,'River Park'!B11)</f>
+        <f>SUM(C11,D11,E11,F11)</f>
         <v/>
       </c>
       <c r="C11" s="7">
@@ -1030,9 +1037,10 @@
         <f>SUM('Астон.Движение'!G11,'Астон.Реформа'!G11,'Милый дом'!G11,'River Park'!G11)</f>
         <v/>
       </c>
-      <c r="H11" s="7">
-        <f>SUM('Астон.Движение'!H11,'Астон.Реформа'!H11,'Милый дом'!H11,'River Park'!H11)</f>
-        <v/>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I11" s="7">
         <f>SUM('Астон.Движение'!I11,'Астон.Реформа'!I11,'Милый дом'!I11,'River Park'!I11)</f>
@@ -1057,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>SUM('Астон.Движение'!B12,'Астон.Реформа'!B12,'Милый дом'!B12,'River Park'!B12)</f>
+        <f>SUM(C12,D12,E12,F12)</f>
         <v/>
       </c>
       <c r="C12" s="7">
@@ -1080,9 +1088,10 @@
         <f>SUM('Астон.Движение'!G12,'Астон.Реформа'!G12,'Милый дом'!G12,'River Park'!G12)</f>
         <v/>
       </c>
-      <c r="H12" s="7">
-        <f>SUM('Астон.Движение'!H12,'Астон.Реформа'!H12,'Милый дом'!H12,'River Park'!H12)</f>
-        <v/>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I12" s="7">
         <f>SUM('Астон.Движение'!I12,'Астон.Реформа'!I12,'Милый дом'!I12,'River Park'!I12)</f>
@@ -1130,9 +1139,10 @@
         <f>SUM(G14,G15,G16,G17,G18,G19,G20)</f>
         <v/>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(H14,H15,H16,H17,H18,H19,H20)</f>
-        <v/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7">
         <f>SUM(I14,I15,I16,I17,I18,I19,I20)</f>
@@ -1157,7 +1167,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>SUM('Астон.Движение'!B14,'Астон.Реформа'!B14,'Милый дом'!B14,'River Park'!B14)</f>
+        <f>SUM(C14,D14,E14,F14)</f>
         <v/>
       </c>
       <c r="C14" s="7">
@@ -1180,9 +1190,10 @@
         <f>SUM('Астон.Движение'!G14,'Астон.Реформа'!G14,'Милый дом'!G14,'River Park'!G14)</f>
         <v/>
       </c>
-      <c r="H14" s="7">
-        <f>SUM('Астон.Движение'!H14,'Астон.Реформа'!H14,'Милый дом'!H14,'River Park'!H14)</f>
-        <v/>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I14" s="7">
         <f>SUM('Астон.Движение'!I14,'Астон.Реформа'!I14,'Милый дом'!I14,'River Park'!I14)</f>
@@ -1207,7 +1218,7 @@
         </is>
       </c>
       <c r="B15" s="7">
-        <f>SUM('Астон.Движение'!B15,'Астон.Реформа'!B15,'Милый дом'!B15,'River Park'!B15)</f>
+        <f>SUM(C15,D15,E15,F15)</f>
         <v/>
       </c>
       <c r="C15" s="7">
@@ -1230,9 +1241,10 @@
         <f>SUM('Астон.Движение'!G15,'Астон.Реформа'!G15,'Милый дом'!G15,'River Park'!G15)</f>
         <v/>
       </c>
-      <c r="H15" s="7">
-        <f>SUM('Астон.Движение'!H15,'Астон.Реформа'!H15,'Милый дом'!H15,'River Park'!H15)</f>
-        <v/>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I15" s="7">
         <f>SUM('Астон.Движение'!I15,'Астон.Реформа'!I15,'Милый дом'!I15,'River Park'!I15)</f>
@@ -1257,7 +1269,7 @@
         </is>
       </c>
       <c r="B16" s="7">
-        <f>SUM('Астон.Движение'!B16,'Астон.Реформа'!B16,'Милый дом'!B16,'River Park'!B16)</f>
+        <f>SUM(C16,D16,E16,F16)</f>
         <v/>
       </c>
       <c r="C16" s="7">
@@ -1280,9 +1292,10 @@
         <f>SUM('Астон.Движение'!G16,'Астон.Реформа'!G16,'Милый дом'!G16,'River Park'!G16)</f>
         <v/>
       </c>
-      <c r="H16" s="7">
-        <f>SUM('Астон.Движение'!H16,'Астон.Реформа'!H16,'Милый дом'!H16,'River Park'!H16)</f>
-        <v/>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I16" s="7">
         <f>SUM('Астон.Движение'!I16,'Астон.Реформа'!I16,'Милый дом'!I16,'River Park'!I16)</f>
@@ -1307,7 +1320,7 @@
         </is>
       </c>
       <c r="B17" s="7">
-        <f>SUM('Астон.Движение'!B17,'Астон.Реформа'!B17,'Милый дом'!B17,'River Park'!B17)</f>
+        <f>SUM(C17,D17,E17,F17)</f>
         <v/>
       </c>
       <c r="C17" s="7">
@@ -1330,9 +1343,10 @@
         <f>SUM('Астон.Движение'!G17,'Астон.Реформа'!G17,'Милый дом'!G17,'River Park'!G17)</f>
         <v/>
       </c>
-      <c r="H17" s="7">
-        <f>SUM('Астон.Движение'!H17,'Астон.Реформа'!H17,'Милый дом'!H17,'River Park'!H17)</f>
-        <v/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I17" s="7">
         <f>SUM('Астон.Движение'!I17,'Астон.Реформа'!I17,'Милый дом'!I17,'River Park'!I17)</f>
@@ -1357,7 +1371,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM('Астон.Движение'!B18,'Астон.Реформа'!B18,'Милый дом'!B18,'River Park'!B18)</f>
+        <f>SUM(C18,D18,E18,F18)</f>
         <v/>
       </c>
       <c r="C18" s="7">
@@ -1380,9 +1394,10 @@
         <f>SUM('Астон.Движение'!G18,'Астон.Реформа'!G18,'Милый дом'!G18,'River Park'!G18)</f>
         <v/>
       </c>
-      <c r="H18" s="7">
-        <f>SUM('Астон.Движение'!H18,'Астон.Реформа'!H18,'Милый дом'!H18,'River Park'!H18)</f>
-        <v/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I18" s="7">
         <f>SUM('Астон.Движение'!I18,'Астон.Реформа'!I18,'Милый дом'!I18,'River Park'!I18)</f>
@@ -1407,7 +1422,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM('Астон.Движение'!B19,'Астон.Реформа'!B19,'Милый дом'!B19,'River Park'!B19)</f>
+        <f>SUM(C19,D19,E19,F19)</f>
         <v/>
       </c>
       <c r="C19" s="7">
@@ -1430,9 +1445,10 @@
         <f>SUM('Астон.Движение'!G19,'Астон.Реформа'!G19,'Милый дом'!G19,'River Park'!G19)</f>
         <v/>
       </c>
-      <c r="H19" s="7">
-        <f>SUM('Астон.Движение'!H19,'Астон.Реформа'!H19,'Милый дом'!H19,'River Park'!H19)</f>
-        <v/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I19" s="7">
         <f>SUM('Астон.Движение'!I19,'Астон.Реформа'!I19,'Милый дом'!I19,'River Park'!I19)</f>
@@ -1457,7 +1473,7 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>SUM('Астон.Движение'!B20,'Астон.Реформа'!B20,'Милый дом'!B20,'River Park'!B20)</f>
+        <f>SUM(C20,D20,E20,F20)</f>
         <v/>
       </c>
       <c r="C20" s="7">
@@ -1480,9 +1496,10 @@
         <f>SUM('Астон.Движение'!G20,'Астон.Реформа'!G20,'Милый дом'!G20,'River Park'!G20)</f>
         <v/>
       </c>
-      <c r="H20" s="7">
-        <f>SUM('Астон.Движение'!H20,'Астон.Реформа'!H20,'Милый дом'!H20,'River Park'!H20)</f>
-        <v/>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I20" s="7">
         <f>SUM('Астон.Движение'!I20,'Астон.Реформа'!I20,'Милый дом'!I20,'River Park'!I20)</f>
@@ -1507,7 +1524,7 @@
         </is>
       </c>
       <c r="B21" s="7">
-        <f>SUM('Астон.Движение'!B21,'Астон.Реформа'!B21,'Милый дом'!B21,'River Park'!B21)</f>
+        <f>SUM(C21,D21,E21,F21)</f>
         <v/>
       </c>
       <c r="C21" s="7">
@@ -1530,9 +1547,10 @@
         <f>SUM('Астон.Движение'!G21,'Астон.Реформа'!G21,'Милый дом'!G21,'River Park'!G21)</f>
         <v/>
       </c>
-      <c r="H21" s="7">
-        <f>SUM('Астон.Движение'!H21,'Астон.Реформа'!H21,'Милый дом'!H21,'River Park'!H21)</f>
-        <v/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I21" s="7">
         <f>SUM('Астон.Движение'!I21,'Астон.Реформа'!I21,'Милый дом'!I21,'River Park'!I21)</f>
@@ -1557,7 +1575,7 @@
         </is>
       </c>
       <c r="B22" s="7">
-        <f>SUM('Астон.Движение'!B22,'Астон.Реформа'!B22,'Милый дом'!B22,'River Park'!B22)</f>
+        <f>SUM(C22,D22,E22,F22)</f>
         <v/>
       </c>
       <c r="C22" s="7">
@@ -1580,9 +1598,10 @@
         <f>SUM('Астон.Движение'!G22,'Астон.Реформа'!G22,'Милый дом'!G22,'River Park'!G22)</f>
         <v/>
       </c>
-      <c r="H22" s="7">
-        <f>SUM('Астон.Движение'!H22,'Астон.Реформа'!H22,'Милый дом'!H22,'River Park'!H22)</f>
-        <v/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I22" s="7">
         <f>SUM('Астон.Движение'!I22,'Астон.Реформа'!I22,'Милый дом'!I22,'River Park'!I22)</f>
@@ -1607,7 +1626,7 @@
         </is>
       </c>
       <c r="B23" s="7">
-        <f>SUM('Астон.Движение'!B23,'Астон.Реформа'!B23,'Милый дом'!B23,'River Park'!B23)</f>
+        <f>SUM(C23,D23,E23,F23)</f>
         <v/>
       </c>
       <c r="C23" s="7">
@@ -1630,9 +1649,10 @@
         <f>SUM('Астон.Движение'!G23,'Астон.Реформа'!G23,'Милый дом'!G23,'River Park'!G23)</f>
         <v/>
       </c>
-      <c r="H23" s="7">
-        <f>SUM('Астон.Движение'!H23,'Астон.Реформа'!H23,'Милый дом'!H23,'River Park'!H23)</f>
-        <v/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I23" s="7">
         <f>SUM('Астон.Движение'!I23,'Астон.Реформа'!I23,'Милый дом'!I23,'River Park'!I23)</f>
@@ -1657,7 +1677,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>SUM('Астон.Движение'!B24,'Астон.Реформа'!B24,'Милый дом'!B24,'River Park'!B24)</f>
+        <f>SUM(C24,D24,E24,F24)</f>
         <v/>
       </c>
       <c r="C24" s="7">
@@ -1680,9 +1700,10 @@
         <f>SUM('Астон.Движение'!G24,'Астон.Реформа'!G24,'Милый дом'!G24,'River Park'!G24)</f>
         <v/>
       </c>
-      <c r="H24" s="7">
-        <f>SUM('Астон.Движение'!H24,'Астон.Реформа'!H24,'Милый дом'!H24,'River Park'!H24)</f>
-        <v/>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I24" s="7">
         <f>SUM('Астон.Движение'!I24,'Астон.Реформа'!I24,'Милый дом'!I24,'River Park'!I24)</f>
@@ -1707,7 +1728,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>SUM('Астон.Движение'!B25,'Астон.Реформа'!B25,'Милый дом'!B25,'River Park'!B25)</f>
+        <f>SUM(C25,D25,E25,F25)</f>
         <v/>
       </c>
       <c r="C25" s="7">
@@ -1730,9 +1751,10 @@
         <f>SUM('Астон.Движение'!G25,'Астон.Реформа'!G25,'Милый дом'!G25,'River Park'!G25)</f>
         <v/>
       </c>
-      <c r="H25" s="7">
-        <f>SUM('Астон.Движение'!H25,'Астон.Реформа'!H25,'Милый дом'!H25,'River Park'!H25)</f>
-        <v/>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I25" s="7">
         <f>SUM('Астон.Движение'!I25,'Астон.Реформа'!I25,'Милый дом'!I25,'River Park'!I25)</f>
@@ -1757,7 +1779,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>SUM('Астон.Движение'!B26,'Астон.Реформа'!B26,'Милый дом'!B26,'River Park'!B26)</f>
+        <f>SUM(C26,D26,E26,F26)</f>
         <v/>
       </c>
       <c r="C26" s="7">
@@ -1780,9 +1802,10 @@
         <f>SUM('Астон.Движение'!G26,'Астон.Реформа'!G26,'Милый дом'!G26,'River Park'!G26)</f>
         <v/>
       </c>
-      <c r="H26" s="7">
-        <f>SUM('Астон.Движение'!H26,'Астон.Реформа'!H26,'Милый дом'!H26,'River Park'!H26)</f>
-        <v/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I26" s="7">
         <f>SUM('Астон.Движение'!I26,'Астон.Реформа'!I26,'Милый дом'!I26,'River Park'!I26)</f>
@@ -1807,7 +1830,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>SUM('Астон.Движение'!B27,'Астон.Реформа'!B27,'Милый дом'!B27,'River Park'!B27)</f>
+        <f>SUM(C27,D27,E27,F27)</f>
         <v/>
       </c>
       <c r="C27" s="7">
@@ -1830,9 +1853,10 @@
         <f>SUM('Астон.Движение'!G27,'Астон.Реформа'!G27,'Милый дом'!G27,'River Park'!G27)</f>
         <v/>
       </c>
-      <c r="H27" s="7">
-        <f>SUM('Астон.Движение'!H27,'Астон.Реформа'!H27,'Милый дом'!H27,'River Park'!H27)</f>
-        <v/>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I27" s="7">
         <f>SUM('Астон.Движение'!I27,'Астон.Реформа'!I27,'Милый дом'!I27,'River Park'!I27)</f>
@@ -1857,7 +1881,7 @@
         </is>
       </c>
       <c r="B28" s="7">
-        <f>SUM('Астон.Движение'!B28,'Астон.Реформа'!B28,'Милый дом'!B28,'River Park'!B28)</f>
+        <f>SUM(C28,D28,E28,F28)</f>
         <v/>
       </c>
       <c r="C28" s="7">
@@ -1880,9 +1904,10 @@
         <f>SUM('Астон.Движение'!G28,'Астон.Реформа'!G28,'Милый дом'!G28,'River Park'!G28)</f>
         <v/>
       </c>
-      <c r="H28" s="7">
-        <f>SUM('Астон.Движение'!H28,'Астон.Реформа'!H28,'Милый дом'!H28,'River Park'!H28)</f>
-        <v/>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I28" s="7">
         <f>SUM('Астон.Движение'!I28,'Астон.Реформа'!I28,'Милый дом'!I28,'River Park'!I28)</f>
@@ -1907,7 +1932,7 @@
         </is>
       </c>
       <c r="B29" s="7">
-        <f>SUM('Астон.Движение'!B29,'Астон.Реформа'!B29,'Милый дом'!B29,'River Park'!B29)</f>
+        <f>SUM(C29,D29,E29,F29)</f>
         <v/>
       </c>
       <c r="C29" s="7">
@@ -1930,9 +1955,10 @@
         <f>SUM('Астон.Движение'!G29,'Астон.Реформа'!G29,'Милый дом'!G29,'River Park'!G29)</f>
         <v/>
       </c>
-      <c r="H29" s="7">
-        <f>SUM('Астон.Движение'!H29,'Астон.Реформа'!H29,'Милый дом'!H29,'River Park'!H29)</f>
-        <v/>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I29" s="7">
         <f>SUM('Астон.Движение'!I29,'Астон.Реформа'!I29,'Милый дом'!I29,'River Park'!I29)</f>
@@ -1957,7 +1983,7 @@
         </is>
       </c>
       <c r="B30" s="7">
-        <f>SUM('Астон.Движение'!B30,'Астон.Реформа'!B30,'Милый дом'!B30,'River Park'!B30)</f>
+        <f>SUM(C30,D30,E30,F30)</f>
         <v/>
       </c>
       <c r="C30" s="7">
@@ -1980,9 +2006,10 @@
         <f>SUM('Астон.Движение'!G30,'Астон.Реформа'!G30,'Милый дом'!G30,'River Park'!G30)</f>
         <v/>
       </c>
-      <c r="H30" s="7">
-        <f>SUM('Астон.Движение'!H30,'Астон.Реформа'!H30,'Милый дом'!H30,'River Park'!H30)</f>
-        <v/>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I30" s="7">
         <f>SUM('Астон.Движение'!I30,'Астон.Реформа'!I30,'Милый дом'!I30,'River Park'!I30)</f>
@@ -2007,7 +2034,7 @@
         </is>
       </c>
       <c r="B31" s="7">
-        <f>SUM('Астон.Движение'!B31,'Астон.Реформа'!B31,'Милый дом'!B31,'River Park'!B31)</f>
+        <f>SUM(C31,D31,E31,F31)</f>
         <v/>
       </c>
       <c r="C31" s="7">
@@ -2030,9 +2057,10 @@
         <f>SUM('Астон.Движение'!G31,'Астон.Реформа'!G31,'Милый дом'!G31,'River Park'!G31)</f>
         <v/>
       </c>
-      <c r="H31" s="7">
-        <f>SUM('Астон.Движение'!H31,'Астон.Реформа'!H31,'Милый дом'!H31,'River Park'!H31)</f>
-        <v/>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I31" s="7">
         <f>SUM('Астон.Движение'!I31,'Астон.Реформа'!I31,'Милый дом'!I31,'River Park'!I31)</f>
@@ -2057,7 +2085,7 @@
         </is>
       </c>
       <c r="B32" s="7">
-        <f>SUM('Астон.Движение'!B32,'Астон.Реформа'!B32,'Милый дом'!B32,'River Park'!B32)</f>
+        <f>SUM(C32,D32,E32,F32)</f>
         <v/>
       </c>
       <c r="C32" s="7">
@@ -2080,9 +2108,10 @@
         <f>SUM('Астон.Движение'!G32,'Астон.Реформа'!G32,'Милый дом'!G32,'River Park'!G32)</f>
         <v/>
       </c>
-      <c r="H32" s="7">
-        <f>SUM('Астон.Движение'!H32,'Астон.Реформа'!H32,'Милый дом'!H32,'River Park'!H32)</f>
-        <v/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I32" s="7">
         <f>SUM('Астон.Движение'!I32,'Астон.Реформа'!I32,'Милый дом'!I32,'River Park'!I32)</f>
@@ -2107,7 +2136,7 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>SUM('Астон.Движение'!B33,'Астон.Реформа'!B33,'Милый дом'!B33,'River Park'!B33)</f>
+        <f>SUM(C33,D33,E33,F33)</f>
         <v/>
       </c>
       <c r="C33" s="7">
@@ -2130,9 +2159,10 @@
         <f>SUM('Астон.Движение'!G33,'Астон.Реформа'!G33,'Милый дом'!G33,'River Park'!G33)</f>
         <v/>
       </c>
-      <c r="H33" s="7">
-        <f>SUM('Астон.Движение'!H33,'Астон.Реформа'!H33,'Милый дом'!H33,'River Park'!H33)</f>
-        <v/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I33" s="7">
         <f>SUM('Астон.Движение'!I33,'Астон.Реформа'!I33,'Милый дом'!I33,'River Park'!I33)</f>
@@ -2180,9 +2210,10 @@
         <f>SUM(G35,G36,G37,G38,G39,G40,G41,G42)</f>
         <v/>
       </c>
-      <c r="H34" s="7">
-        <f>SUM(H35,H36,H37,H38,H39,H40,H41,H42)</f>
-        <v/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" s="7">
         <f>SUM(I35,I36,I37,I38,I39,I40,I41,I42)</f>
@@ -2207,7 +2238,7 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>SUM('Астон.Движение'!B35,'Астон.Реформа'!B35,'Милый дом'!B35,'River Park'!B35)</f>
+        <f>SUM(C35,D35,E35,F35)</f>
         <v/>
       </c>
       <c r="C35" s="7">
@@ -2230,9 +2261,10 @@
         <f>SUM('Астон.Движение'!G35,'Астон.Реформа'!G35,'Милый дом'!G35,'River Park'!G35)</f>
         <v/>
       </c>
-      <c r="H35" s="7">
-        <f>SUM('Астон.Движение'!H35,'Астон.Реформа'!H35,'Милый дом'!H35,'River Park'!H35)</f>
-        <v/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I35" s="7">
         <f>SUM('Астон.Движение'!I35,'Астон.Реформа'!I35,'Милый дом'!I35,'River Park'!I35)</f>
@@ -2257,7 +2289,7 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>SUM('Астон.Движение'!B36,'Астон.Реформа'!B36,'Милый дом'!B36,'River Park'!B36)</f>
+        <f>SUM(C36,D36,E36,F36)</f>
         <v/>
       </c>
       <c r="C36" s="7">
@@ -2280,9 +2312,10 @@
         <f>SUM('Астон.Движение'!G36,'Астон.Реформа'!G36,'Милый дом'!G36,'River Park'!G36)</f>
         <v/>
       </c>
-      <c r="H36" s="7">
-        <f>SUM('Астон.Движение'!H36,'Астон.Реформа'!H36,'Милый дом'!H36,'River Park'!H36)</f>
-        <v/>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I36" s="7">
         <f>SUM('Астон.Движение'!I36,'Астон.Реформа'!I36,'Милый дом'!I36,'River Park'!I36)</f>
@@ -2307,7 +2340,7 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>SUM('Астон.Движение'!B37,'Астон.Реформа'!B37,'Милый дом'!B37,'River Park'!B37)</f>
+        <f>SUM(C37,D37,E37,F37)</f>
         <v/>
       </c>
       <c r="C37" s="7">
@@ -2330,9 +2363,10 @@
         <f>SUM('Астон.Движение'!G37,'Астон.Реформа'!G37,'Милый дом'!G37,'River Park'!G37)</f>
         <v/>
       </c>
-      <c r="H37" s="7">
-        <f>SUM('Астон.Движение'!H37,'Астон.Реформа'!H37,'Милый дом'!H37,'River Park'!H37)</f>
-        <v/>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I37" s="7">
         <f>SUM('Астон.Движение'!I37,'Астон.Реформа'!I37,'Милый дом'!I37,'River Park'!I37)</f>
@@ -2357,7 +2391,7 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>SUM('Астон.Движение'!B38,'Астон.Реформа'!B38,'Милый дом'!B38,'River Park'!B38)</f>
+        <f>SUM(C38,D38,E38,F38)</f>
         <v/>
       </c>
       <c r="C38" s="7">
@@ -2380,9 +2414,10 @@
         <f>SUM('Астон.Движение'!G38,'Астон.Реформа'!G38,'Милый дом'!G38,'River Park'!G38)</f>
         <v/>
       </c>
-      <c r="H38" s="7">
-        <f>SUM('Астон.Движение'!H38,'Астон.Реформа'!H38,'Милый дом'!H38,'River Park'!H38)</f>
-        <v/>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I38" s="7">
         <f>SUM('Астон.Движение'!I38,'Астон.Реформа'!I38,'Милый дом'!I38,'River Park'!I38)</f>
@@ -2407,7 +2442,7 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>SUM('Астон.Движение'!B39,'Астон.Реформа'!B39,'Милый дом'!B39,'River Park'!B39)</f>
+        <f>SUM(C39,D39,E39,F39)</f>
         <v/>
       </c>
       <c r="C39" s="7">
@@ -2430,9 +2465,10 @@
         <f>SUM('Астон.Движение'!G39,'Астон.Реформа'!G39,'Милый дом'!G39,'River Park'!G39)</f>
         <v/>
       </c>
-      <c r="H39" s="7">
-        <f>SUM('Астон.Движение'!H39,'Астон.Реформа'!H39,'Милый дом'!H39,'River Park'!H39)</f>
-        <v/>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I39" s="7">
         <f>SUM('Астон.Движение'!I39,'Астон.Реформа'!I39,'Милый дом'!I39,'River Park'!I39)</f>
@@ -2457,7 +2493,7 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>SUM('Астон.Движение'!B40,'Астон.Реформа'!B40,'Милый дом'!B40,'River Park'!B40)</f>
+        <f>SUM(C40,D40,E40,F40)</f>
         <v/>
       </c>
       <c r="C40" s="7">
@@ -2480,9 +2516,10 @@
         <f>SUM('Астон.Движение'!G40,'Астон.Реформа'!G40,'Милый дом'!G40,'River Park'!G40)</f>
         <v/>
       </c>
-      <c r="H40" s="7">
-        <f>SUM('Астон.Движение'!H40,'Астон.Реформа'!H40,'Милый дом'!H40,'River Park'!H40)</f>
-        <v/>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I40" s="7">
         <f>SUM('Астон.Движение'!I40,'Астон.Реформа'!I40,'Милый дом'!I40,'River Park'!I40)</f>
@@ -2507,7 +2544,7 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>SUM('Астон.Движение'!B41,'Астон.Реформа'!B41,'Милый дом'!B41,'River Park'!B41)</f>
+        <f>SUM(C41,D41,E41,F41)</f>
         <v/>
       </c>
       <c r="C41" s="7">
@@ -2530,9 +2567,10 @@
         <f>SUM('Астон.Движение'!G41,'Астон.Реформа'!G41,'Милый дом'!G41,'River Park'!G41)</f>
         <v/>
       </c>
-      <c r="H41" s="7">
-        <f>SUM('Астон.Движение'!H41,'Астон.Реформа'!H41,'Милый дом'!H41,'River Park'!H41)</f>
-        <v/>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I41" s="7">
         <f>SUM('Астон.Движение'!I41,'Астон.Реформа'!I41,'Милый дом'!I41,'River Park'!I41)</f>
@@ -2557,7 +2595,7 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>SUM('Астон.Движение'!B42,'Астон.Реформа'!B42,'Милый дом'!B42,'River Park'!B42)</f>
+        <f>SUM(C42,D42,E42,F42)</f>
         <v/>
       </c>
       <c r="C42" s="7">
@@ -2580,9 +2618,10 @@
         <f>SUM('Астон.Движение'!G42,'Астон.Реформа'!G42,'Милый дом'!G42,'River Park'!G42)</f>
         <v/>
       </c>
-      <c r="H42" s="7">
-        <f>SUM('Астон.Движение'!H42,'Астон.Реформа'!H42,'Милый дом'!H42,'River Park'!H42)</f>
-        <v/>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I42" s="7">
         <f>SUM('Астон.Движение'!I42,'Астон.Реформа'!I42,'Милый дом'!I42,'River Park'!I42)</f>
@@ -2630,9 +2669,10 @@
         <f>G4-G10</f>
         <v/>
       </c>
-      <c r="H43" s="9">
-        <f>H4-H10</f>
-        <v/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="9">
         <f>I4-I10</f>
@@ -2680,9 +2720,10 @@
         <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
-        <v/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="10">
         <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
@@ -2730,9 +2771,10 @@
         <f>SUM(G46,G47,G48,G52,G56,G57,G58,G59,G60,G63,G64,G65,G66,G67,G68,G69,G70,G71,G72,G73,G74,G75,G76,G77,G78,G79)</f>
         <v/>
       </c>
-      <c r="H45" s="7">
-        <f>SUM(H46,H47,H48,H52,H56,H57,H58,H59,H60,H63,H64,H65,H66,H67,H68,H69,H70,H71,H72,H73,H74,H75,H76,H77,H78,H79)</f>
-        <v/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="7">
         <f>SUM(I46,I47,I48,I52,I56,I57,I58,I59,I60,I63,I64,I65,I66,I67,I68,I69,I70,I71,I72,I73,I74,I75,I76,I77,I78,I79)</f>
@@ -2757,7 +2799,7 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>SUM('Астон.Движение'!B46,'Астон.Реформа'!B46,'Милый дом'!B46,'River Park'!B46)</f>
+        <f>SUM(C46,D46,E46,F46)</f>
         <v/>
       </c>
       <c r="C46" s="7">
@@ -2780,9 +2822,10 @@
         <f>SUM('Астон.Движение'!G46,'Астон.Реформа'!G46,'Милый дом'!G46,'River Park'!G46)</f>
         <v/>
       </c>
-      <c r="H46" s="7">
-        <f>SUM('Астон.Движение'!H46,'Астон.Реформа'!H46,'Милый дом'!H46,'River Park'!H46)</f>
-        <v/>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I46" s="7">
         <f>SUM('Астон.Движение'!I46,'Астон.Реформа'!I46,'Милый дом'!I46,'River Park'!I46)</f>
@@ -2807,7 +2850,7 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>SUM('Астон.Движение'!B47,'Астон.Реформа'!B47,'Милый дом'!B47,'River Park'!B47)</f>
+        <f>SUM(C47,D47,E47,F47)</f>
         <v/>
       </c>
       <c r="C47" s="7">
@@ -2830,9 +2873,10 @@
         <f>SUM('Астон.Движение'!G47,'Астон.Реформа'!G47,'Милый дом'!G47,'River Park'!G47)</f>
         <v/>
       </c>
-      <c r="H47" s="7">
-        <f>SUM('Астон.Движение'!H47,'Астон.Реформа'!H47,'Милый дом'!H47,'River Park'!H47)</f>
-        <v/>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I47" s="7">
         <f>SUM('Астон.Движение'!I47,'Астон.Реформа'!I47,'Милый дом'!I47,'River Park'!I47)</f>
@@ -2880,9 +2924,10 @@
         <f>SUM(G49,G50,G51)</f>
         <v/>
       </c>
-      <c r="H48" s="7">
-        <f>SUM(H49,H50,H51)</f>
-        <v/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="7">
         <f>SUM(I49,I50,I51)</f>
@@ -2907,7 +2952,7 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>SUM('Астон.Движение'!B49,'Астон.Реформа'!B49,'Милый дом'!B49,'River Park'!B49)</f>
+        <f>SUM(C49,D49,E49,F49)</f>
         <v/>
       </c>
       <c r="C49" s="7">
@@ -2930,9 +2975,10 @@
         <f>SUM('Астон.Движение'!G49,'Астон.Реформа'!G49,'Милый дом'!G49,'River Park'!G49)</f>
         <v/>
       </c>
-      <c r="H49" s="7">
-        <f>SUM('Астон.Движение'!H49,'Астон.Реформа'!H49,'Милый дом'!H49,'River Park'!H49)</f>
-        <v/>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I49" s="7">
         <f>SUM('Астон.Движение'!I49,'Астон.Реформа'!I49,'Милый дом'!I49,'River Park'!I49)</f>
@@ -2957,7 +3003,7 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>SUM('Астон.Движение'!B50,'Астон.Реформа'!B50,'Милый дом'!B50,'River Park'!B50)</f>
+        <f>SUM(C50,D50,E50,F50)</f>
         <v/>
       </c>
       <c r="C50" s="7">
@@ -2980,9 +3026,10 @@
         <f>SUM('Астон.Движение'!G50,'Астон.Реформа'!G50,'Милый дом'!G50,'River Park'!G50)</f>
         <v/>
       </c>
-      <c r="H50" s="7">
-        <f>SUM('Астон.Движение'!H50,'Астон.Реформа'!H50,'Милый дом'!H50,'River Park'!H50)</f>
-        <v/>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I50" s="7">
         <f>SUM('Астон.Движение'!I50,'Астон.Реформа'!I50,'Милый дом'!I50,'River Park'!I50)</f>
@@ -3007,7 +3054,7 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>SUM('Астон.Движение'!B51,'Астон.Реформа'!B51,'Милый дом'!B51,'River Park'!B51)</f>
+        <f>SUM(C51,D51,E51,F51)</f>
         <v/>
       </c>
       <c r="C51" s="7">
@@ -3030,9 +3077,10 @@
         <f>SUM('Астон.Движение'!G51,'Астон.Реформа'!G51,'Милый дом'!G51,'River Park'!G51)</f>
         <v/>
       </c>
-      <c r="H51" s="7">
-        <f>SUM('Астон.Движение'!H51,'Астон.Реформа'!H51,'Милый дом'!H51,'River Park'!H51)</f>
-        <v/>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I51" s="7">
         <f>SUM('Астон.Движение'!I51,'Астон.Реформа'!I51,'Милый дом'!I51,'River Park'!I51)</f>
@@ -3080,9 +3128,10 @@
         <f>SUM(G53,G54,G55)</f>
         <v/>
       </c>
-      <c r="H52" s="7">
-        <f>SUM(H53,H54,H55)</f>
-        <v/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="7">
         <f>SUM(I53,I54,I55)</f>
@@ -3107,7 +3156,7 @@
         </is>
       </c>
       <c r="B53" s="7">
-        <f>SUM('Астон.Движение'!B53,'Астон.Реформа'!B53,'Милый дом'!B53,'River Park'!B53)</f>
+        <f>SUM(C53,D53,E53,F53)</f>
         <v/>
       </c>
       <c r="C53" s="7">
@@ -3130,9 +3179,10 @@
         <f>SUM('Астон.Движение'!G53,'Астон.Реформа'!G53,'Милый дом'!G53,'River Park'!G53)</f>
         <v/>
       </c>
-      <c r="H53" s="7">
-        <f>SUM('Астон.Движение'!H53,'Астон.Реформа'!H53,'Милый дом'!H53,'River Park'!H53)</f>
-        <v/>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I53" s="7">
         <f>SUM('Астон.Движение'!I53,'Астон.Реформа'!I53,'Милый дом'!I53,'River Park'!I53)</f>
@@ -3157,7 +3207,7 @@
         </is>
       </c>
       <c r="B54" s="7">
-        <f>SUM('Астон.Движение'!B54,'Астон.Реформа'!B54,'Милый дом'!B54,'River Park'!B54)</f>
+        <f>SUM(C54,D54,E54,F54)</f>
         <v/>
       </c>
       <c r="C54" s="7">
@@ -3180,9 +3230,10 @@
         <f>SUM('Астон.Движение'!G54,'Астон.Реформа'!G54,'Милый дом'!G54,'River Park'!G54)</f>
         <v/>
       </c>
-      <c r="H54" s="7">
-        <f>SUM('Астон.Движение'!H54,'Астон.Реформа'!H54,'Милый дом'!H54,'River Park'!H54)</f>
-        <v/>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I54" s="7">
         <f>SUM('Астон.Движение'!I54,'Астон.Реформа'!I54,'Милый дом'!I54,'River Park'!I54)</f>
@@ -3207,7 +3258,7 @@
         </is>
       </c>
       <c r="B55" s="7">
-        <f>SUM('Астон.Движение'!B55,'Астон.Реформа'!B55,'Милый дом'!B55,'River Park'!B55)</f>
+        <f>SUM(C55,D55,E55,F55)</f>
         <v/>
       </c>
       <c r="C55" s="7">
@@ -3230,9 +3281,10 @@
         <f>SUM('Астон.Движение'!G55,'Астон.Реформа'!G55,'Милый дом'!G55,'River Park'!G55)</f>
         <v/>
       </c>
-      <c r="H55" s="7">
-        <f>SUM('Астон.Движение'!H55,'Астон.Реформа'!H55,'Милый дом'!H55,'River Park'!H55)</f>
-        <v/>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I55" s="7">
         <f>SUM('Астон.Движение'!I55,'Астон.Реформа'!I55,'Милый дом'!I55,'River Park'!I55)</f>
@@ -3257,7 +3309,7 @@
         </is>
       </c>
       <c r="B56" s="7">
-        <f>SUM('Астон.Движение'!B56,'Астон.Реформа'!B56,'Милый дом'!B56,'River Park'!B56)</f>
+        <f>SUM(C56,D56,E56,F56)</f>
         <v/>
       </c>
       <c r="C56" s="7">
@@ -3280,9 +3332,10 @@
         <f>SUM('Астон.Движение'!G56,'Астон.Реформа'!G56,'Милый дом'!G56,'River Park'!G56)</f>
         <v/>
       </c>
-      <c r="H56" s="7">
-        <f>SUM('Астон.Движение'!H56,'Астон.Реформа'!H56,'Милый дом'!H56,'River Park'!H56)</f>
-        <v/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I56" s="7">
         <f>SUM('Астон.Движение'!I56,'Астон.Реформа'!I56,'Милый дом'!I56,'River Park'!I56)</f>
@@ -3307,7 +3360,7 @@
         </is>
       </c>
       <c r="B57" s="7">
-        <f>SUM('Астон.Движение'!B57,'Астон.Реформа'!B57,'Милый дом'!B57,'River Park'!B57)</f>
+        <f>SUM(C57,D57,E57,F57)</f>
         <v/>
       </c>
       <c r="C57" s="7">
@@ -3330,9 +3383,10 @@
         <f>SUM('Астон.Движение'!G57,'Астон.Реформа'!G57,'Милый дом'!G57,'River Park'!G57)</f>
         <v/>
       </c>
-      <c r="H57" s="7">
-        <f>SUM('Астон.Движение'!H57,'Астон.Реформа'!H57,'Милый дом'!H57,'River Park'!H57)</f>
-        <v/>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I57" s="7">
         <f>SUM('Астон.Движение'!I57,'Астон.Реформа'!I57,'Милый дом'!I57,'River Park'!I57)</f>
@@ -3357,7 +3411,7 @@
         </is>
       </c>
       <c r="B58" s="7">
-        <f>SUM('Астон.Движение'!B58,'Астон.Реформа'!B58,'Милый дом'!B58,'River Park'!B58)</f>
+        <f>SUM(C58,D58,E58,F58)</f>
         <v/>
       </c>
       <c r="C58" s="7">
@@ -3380,9 +3434,10 @@
         <f>SUM('Астон.Движение'!G58,'Астон.Реформа'!G58,'Милый дом'!G58,'River Park'!G58)</f>
         <v/>
       </c>
-      <c r="H58" s="7">
-        <f>SUM('Астон.Движение'!H58,'Астон.Реформа'!H58,'Милый дом'!H58,'River Park'!H58)</f>
-        <v/>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I58" s="7">
         <f>SUM('Астон.Движение'!I58,'Астон.Реформа'!I58,'Милый дом'!I58,'River Park'!I58)</f>
@@ -3407,7 +3462,7 @@
         </is>
       </c>
       <c r="B59" s="7">
-        <f>SUM('Астон.Движение'!B59,'Астон.Реформа'!B59,'Милый дом'!B59,'River Park'!B59)</f>
+        <f>SUM(C59,D59,E59,F59)</f>
         <v/>
       </c>
       <c r="C59" s="7">
@@ -3430,9 +3485,10 @@
         <f>SUM('Астон.Движение'!G59,'Астон.Реформа'!G59,'Милый дом'!G59,'River Park'!G59)</f>
         <v/>
       </c>
-      <c r="H59" s="7">
-        <f>SUM('Астон.Движение'!H59,'Астон.Реформа'!H59,'Милый дом'!H59,'River Park'!H59)</f>
-        <v/>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I59" s="7">
         <f>SUM('Астон.Движение'!I59,'Астон.Реформа'!I59,'Милый дом'!I59,'River Park'!I59)</f>
@@ -3480,9 +3536,10 @@
         <f>SUM(G61,G62)</f>
         <v/>
       </c>
-      <c r="H60" s="7">
-        <f>SUM(H61,H62)</f>
-        <v/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="7">
         <f>SUM(I61,I62)</f>
@@ -3507,7 +3564,7 @@
         </is>
       </c>
       <c r="B61" s="7">
-        <f>SUM('Астон.Движение'!B61,'Астон.Реформа'!B61,'Милый дом'!B61,'River Park'!B61)</f>
+        <f>SUM(C61,D61,E61,F61)</f>
         <v/>
       </c>
       <c r="C61" s="7">
@@ -3530,9 +3587,10 @@
         <f>SUM('Астон.Движение'!G61,'Астон.Реформа'!G61,'Милый дом'!G61,'River Park'!G61)</f>
         <v/>
       </c>
-      <c r="H61" s="7">
-        <f>SUM('Астон.Движение'!H61,'Астон.Реформа'!H61,'Милый дом'!H61,'River Park'!H61)</f>
-        <v/>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I61" s="7">
         <f>SUM('Астон.Движение'!I61,'Астон.Реформа'!I61,'Милый дом'!I61,'River Park'!I61)</f>
@@ -3557,7 +3615,7 @@
         </is>
       </c>
       <c r="B62" s="7">
-        <f>SUM('Астон.Движение'!B62,'Астон.Реформа'!B62,'Милый дом'!B62,'River Park'!B62)</f>
+        <f>SUM(C62,D62,E62,F62)</f>
         <v/>
       </c>
       <c r="C62" s="7">
@@ -3580,9 +3638,10 @@
         <f>SUM('Астон.Движение'!G62,'Астон.Реформа'!G62,'Милый дом'!G62,'River Park'!G62)</f>
         <v/>
       </c>
-      <c r="H62" s="7">
-        <f>SUM('Астон.Движение'!H62,'Астон.Реформа'!H62,'Милый дом'!H62,'River Park'!H62)</f>
-        <v/>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I62" s="7">
         <f>SUM('Астон.Движение'!I62,'Астон.Реформа'!I62,'Милый дом'!I62,'River Park'!I62)</f>
@@ -3607,7 +3666,7 @@
         </is>
       </c>
       <c r="B63" s="7">
-        <f>SUM('Астон.Движение'!B63,'Астон.Реформа'!B63,'Милый дом'!B63,'River Park'!B63)</f>
+        <f>SUM(C63,D63,E63,F63)</f>
         <v/>
       </c>
       <c r="C63" s="7">
@@ -3630,9 +3689,10 @@
         <f>SUM('Астон.Движение'!G63,'Астон.Реформа'!G63,'Милый дом'!G63,'River Park'!G63)</f>
         <v/>
       </c>
-      <c r="H63" s="7">
-        <f>SUM('Астон.Движение'!H63,'Астон.Реформа'!H63,'Милый дом'!H63,'River Park'!H63)</f>
-        <v/>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I63" s="7">
         <f>SUM('Астон.Движение'!I63,'Астон.Реформа'!I63,'Милый дом'!I63,'River Park'!I63)</f>
@@ -3657,7 +3717,7 @@
         </is>
       </c>
       <c r="B64" s="7">
-        <f>SUM('Астон.Движение'!B64,'Астон.Реформа'!B64,'Милый дом'!B64,'River Park'!B64)</f>
+        <f>SUM(C64,D64,E64,F64)</f>
         <v/>
       </c>
       <c r="C64" s="7">
@@ -3680,9 +3740,10 @@
         <f>SUM('Астон.Движение'!G64,'Астон.Реформа'!G64,'Милый дом'!G64,'River Park'!G64)</f>
         <v/>
       </c>
-      <c r="H64" s="7">
-        <f>SUM('Астон.Движение'!H64,'Астон.Реформа'!H64,'Милый дом'!H64,'River Park'!H64)</f>
-        <v/>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I64" s="7">
         <f>SUM('Астон.Движение'!I64,'Астон.Реформа'!I64,'Милый дом'!I64,'River Park'!I64)</f>
@@ -3707,7 +3768,7 @@
         </is>
       </c>
       <c r="B65" s="7">
-        <f>SUM('Астон.Движение'!B65,'Астон.Реформа'!B65,'Милый дом'!B65,'River Park'!B65)</f>
+        <f>SUM(C65,D65,E65,F65)</f>
         <v/>
       </c>
       <c r="C65" s="7">
@@ -3730,9 +3791,10 @@
         <f>SUM('Астон.Движение'!G65,'Астон.Реформа'!G65,'Милый дом'!G65,'River Park'!G65)</f>
         <v/>
       </c>
-      <c r="H65" s="7">
-        <f>SUM('Астон.Движение'!H65,'Астон.Реформа'!H65,'Милый дом'!H65,'River Park'!H65)</f>
-        <v/>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I65" s="7">
         <f>SUM('Астон.Движение'!I65,'Астон.Реформа'!I65,'Милый дом'!I65,'River Park'!I65)</f>
@@ -3757,7 +3819,7 @@
         </is>
       </c>
       <c r="B66" s="7">
-        <f>SUM('Астон.Движение'!B66,'Астон.Реформа'!B66,'Милый дом'!B66,'River Park'!B66)</f>
+        <f>SUM(C66,D66,E66,F66)</f>
         <v/>
       </c>
       <c r="C66" s="7">
@@ -3780,9 +3842,10 @@
         <f>SUM('Астон.Движение'!G66,'Астон.Реформа'!G66,'Милый дом'!G66,'River Park'!G66)</f>
         <v/>
       </c>
-      <c r="H66" s="7">
-        <f>SUM('Астон.Движение'!H66,'Астон.Реформа'!H66,'Милый дом'!H66,'River Park'!H66)</f>
-        <v/>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I66" s="7">
         <f>SUM('Астон.Движение'!I66,'Астон.Реформа'!I66,'Милый дом'!I66,'River Park'!I66)</f>
@@ -3807,7 +3870,7 @@
         </is>
       </c>
       <c r="B67" s="7">
-        <f>SUM('Астон.Движение'!B67,'Астон.Реформа'!B67,'Милый дом'!B67,'River Park'!B67)</f>
+        <f>SUM(C67,D67,E67,F67)</f>
         <v/>
       </c>
       <c r="C67" s="7">
@@ -3830,9 +3893,10 @@
         <f>SUM('Астон.Движение'!G67,'Астон.Реформа'!G67,'Милый дом'!G67,'River Park'!G67)</f>
         <v/>
       </c>
-      <c r="H67" s="7">
-        <f>SUM('Астон.Движение'!H67,'Астон.Реформа'!H67,'Милый дом'!H67,'River Park'!H67)</f>
-        <v/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I67" s="7">
         <f>SUM('Астон.Движение'!I67,'Астон.Реформа'!I67,'Милый дом'!I67,'River Park'!I67)</f>
@@ -3857,7 +3921,7 @@
         </is>
       </c>
       <c r="B68" s="7">
-        <f>SUM('Астон.Движение'!B68,'Астон.Реформа'!B68,'Милый дом'!B68,'River Park'!B68)</f>
+        <f>SUM(C68,D68,E68,F68)</f>
         <v/>
       </c>
       <c r="C68" s="7">
@@ -3880,9 +3944,10 @@
         <f>SUM('Астон.Движение'!G68,'Астон.Реформа'!G68,'Милый дом'!G68,'River Park'!G68)</f>
         <v/>
       </c>
-      <c r="H68" s="7">
-        <f>SUM('Астон.Движение'!H68,'Астон.Реформа'!H68,'Милый дом'!H68,'River Park'!H68)</f>
-        <v/>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I68" s="7">
         <f>SUM('Астон.Движение'!I68,'Астон.Реформа'!I68,'Милый дом'!I68,'River Park'!I68)</f>
@@ -3907,7 +3972,7 @@
         </is>
       </c>
       <c r="B69" s="7">
-        <f>SUM('Астон.Движение'!B69,'Астон.Реформа'!B69,'Милый дом'!B69,'River Park'!B69)</f>
+        <f>SUM(C69,D69,E69,F69)</f>
         <v/>
       </c>
       <c r="C69" s="7">
@@ -3930,9 +3995,10 @@
         <f>SUM('Астон.Движение'!G69,'Астон.Реформа'!G69,'Милый дом'!G69,'River Park'!G69)</f>
         <v/>
       </c>
-      <c r="H69" s="7">
-        <f>SUM('Астон.Движение'!H69,'Астон.Реформа'!H69,'Милый дом'!H69,'River Park'!H69)</f>
-        <v/>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I69" s="7">
         <f>SUM('Астон.Движение'!I69,'Астон.Реформа'!I69,'Милый дом'!I69,'River Park'!I69)</f>
@@ -3957,7 +4023,7 @@
         </is>
       </c>
       <c r="B70" s="7">
-        <f>SUM('Астон.Движение'!B70,'Астон.Реформа'!B70,'Милый дом'!B70,'River Park'!B70)</f>
+        <f>SUM(C70,D70,E70,F70)</f>
         <v/>
       </c>
       <c r="C70" s="7">
@@ -3980,9 +4046,10 @@
         <f>SUM('Астон.Движение'!G70,'Астон.Реформа'!G70,'Милый дом'!G70,'River Park'!G70)</f>
         <v/>
       </c>
-      <c r="H70" s="7">
-        <f>SUM('Астон.Движение'!H70,'Астон.Реформа'!H70,'Милый дом'!H70,'River Park'!H70)</f>
-        <v/>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I70" s="7">
         <f>SUM('Астон.Движение'!I70,'Астон.Реформа'!I70,'Милый дом'!I70,'River Park'!I70)</f>
@@ -4007,7 +4074,7 @@
         </is>
       </c>
       <c r="B71" s="7">
-        <f>SUM('Астон.Движение'!B71,'Астон.Реформа'!B71,'Милый дом'!B71,'River Park'!B71)</f>
+        <f>SUM(C71,D71,E71,F71)</f>
         <v/>
       </c>
       <c r="C71" s="7">
@@ -4030,9 +4097,10 @@
         <f>SUM('Астон.Движение'!G71,'Астон.Реформа'!G71,'Милый дом'!G71,'River Park'!G71)</f>
         <v/>
       </c>
-      <c r="H71" s="7">
-        <f>SUM('Астон.Движение'!H71,'Астон.Реформа'!H71,'Милый дом'!H71,'River Park'!H71)</f>
-        <v/>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I71" s="7">
         <f>SUM('Астон.Движение'!I71,'Астон.Реформа'!I71,'Милый дом'!I71,'River Park'!I71)</f>
@@ -4057,7 +4125,7 @@
         </is>
       </c>
       <c r="B72" s="7">
-        <f>SUM('Астон.Движение'!B72,'Астон.Реформа'!B72,'Милый дом'!B72,'River Park'!B72)</f>
+        <f>SUM(C72,D72,E72,F72)</f>
         <v/>
       </c>
       <c r="C72" s="7">
@@ -4080,9 +4148,10 @@
         <f>SUM('Астон.Движение'!G72,'Астон.Реформа'!G72,'Милый дом'!G72,'River Park'!G72)</f>
         <v/>
       </c>
-      <c r="H72" s="7">
-        <f>SUM('Астон.Движение'!H72,'Астон.Реформа'!H72,'Милый дом'!H72,'River Park'!H72)</f>
-        <v/>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I72" s="7">
         <f>SUM('Астон.Движение'!I72,'Астон.Реформа'!I72,'Милый дом'!I72,'River Park'!I72)</f>
@@ -4107,7 +4176,7 @@
         </is>
       </c>
       <c r="B73" s="7">
-        <f>SUM('Астон.Движение'!B73,'Астон.Реформа'!B73,'Милый дом'!B73,'River Park'!B73)</f>
+        <f>SUM(C73,D73,E73,F73)</f>
         <v/>
       </c>
       <c r="C73" s="7">
@@ -4130,9 +4199,10 @@
         <f>SUM('Астон.Движение'!G73,'Астон.Реформа'!G73,'Милый дом'!G73,'River Park'!G73)</f>
         <v/>
       </c>
-      <c r="H73" s="7">
-        <f>SUM('Астон.Движение'!H73,'Астон.Реформа'!H73,'Милый дом'!H73,'River Park'!H73)</f>
-        <v/>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I73" s="7">
         <f>SUM('Астон.Движение'!I73,'Астон.Реформа'!I73,'Милый дом'!I73,'River Park'!I73)</f>
@@ -4157,7 +4227,7 @@
         </is>
       </c>
       <c r="B74" s="7">
-        <f>SUM('Астон.Движение'!B74,'Астон.Реформа'!B74,'Милый дом'!B74,'River Park'!B74)</f>
+        <f>SUM(C74,D74,E74,F74)</f>
         <v/>
       </c>
       <c r="C74" s="7">
@@ -4180,9 +4250,10 @@
         <f>SUM('Астон.Движение'!G74,'Астон.Реформа'!G74,'Милый дом'!G74,'River Park'!G74)</f>
         <v/>
       </c>
-      <c r="H74" s="7">
-        <f>SUM('Астон.Движение'!H74,'Астон.Реформа'!H74,'Милый дом'!H74,'River Park'!H74)</f>
-        <v/>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I74" s="7">
         <f>SUM('Астон.Движение'!I74,'Астон.Реформа'!I74,'Милый дом'!I74,'River Park'!I74)</f>
@@ -4207,7 +4278,7 @@
         </is>
       </c>
       <c r="B75" s="7">
-        <f>SUM('Астон.Движение'!B75,'Астон.Реформа'!B75,'Милый дом'!B75,'River Park'!B75)</f>
+        <f>SUM(C75,D75,E75,F75)</f>
         <v/>
       </c>
       <c r="C75" s="7">
@@ -4230,9 +4301,10 @@
         <f>SUM('Астон.Движение'!G75,'Астон.Реформа'!G75,'Милый дом'!G75,'River Park'!G75)</f>
         <v/>
       </c>
-      <c r="H75" s="7">
-        <f>SUM('Астон.Движение'!H75,'Астон.Реформа'!H75,'Милый дом'!H75,'River Park'!H75)</f>
-        <v/>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I75" s="7">
         <f>SUM('Астон.Движение'!I75,'Астон.Реформа'!I75,'Милый дом'!I75,'River Park'!I75)</f>
@@ -4257,7 +4329,7 @@
         </is>
       </c>
       <c r="B76" s="7">
-        <f>SUM('Астон.Движение'!B76,'Астон.Реформа'!B76,'Милый дом'!B76,'River Park'!B76)</f>
+        <f>SUM(C76,D76,E76,F76)</f>
         <v/>
       </c>
       <c r="C76" s="7">
@@ -4280,9 +4352,10 @@
         <f>SUM('Астон.Движение'!G76,'Астон.Реформа'!G76,'Милый дом'!G76,'River Park'!G76)</f>
         <v/>
       </c>
-      <c r="H76" s="7">
-        <f>SUM('Астон.Движение'!H76,'Астон.Реформа'!H76,'Милый дом'!H76,'River Park'!H76)</f>
-        <v/>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I76" s="7">
         <f>SUM('Астон.Движение'!I76,'Астон.Реформа'!I76,'Милый дом'!I76,'River Park'!I76)</f>
@@ -4307,7 +4380,7 @@
         </is>
       </c>
       <c r="B77" s="7">
-        <f>SUM('Астон.Движение'!B77,'Астон.Реформа'!B77,'Милый дом'!B77,'River Park'!B77)</f>
+        <f>SUM(C77,D77,E77,F77)</f>
         <v/>
       </c>
       <c r="C77" s="7">
@@ -4330,9 +4403,10 @@
         <f>SUM('Астон.Движение'!G77,'Астон.Реформа'!G77,'Милый дом'!G77,'River Park'!G77)</f>
         <v/>
       </c>
-      <c r="H77" s="7">
-        <f>SUM('Астон.Движение'!H77,'Астон.Реформа'!H77,'Милый дом'!H77,'River Park'!H77)</f>
-        <v/>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I77" s="7">
         <f>SUM('Астон.Движение'!I77,'Астон.Реформа'!I77,'Милый дом'!I77,'River Park'!I77)</f>
@@ -4357,7 +4431,7 @@
         </is>
       </c>
       <c r="B78" s="7">
-        <f>SUM('Астон.Движение'!B78,'Астон.Реформа'!B78,'Милый дом'!B78,'River Park'!B78)</f>
+        <f>SUM(C78,D78,E78,F78)</f>
         <v/>
       </c>
       <c r="C78" s="7">
@@ -4380,9 +4454,10 @@
         <f>SUM('Астон.Движение'!G78,'Астон.Реформа'!G78,'Милый дом'!G78,'River Park'!G78)</f>
         <v/>
       </c>
-      <c r="H78" s="7">
-        <f>SUM('Астон.Движение'!H78,'Астон.Реформа'!H78,'Милый дом'!H78,'River Park'!H78)</f>
-        <v/>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I78" s="7">
         <f>SUM('Астон.Движение'!I78,'Астон.Реформа'!I78,'Милый дом'!I78,'River Park'!I78)</f>
@@ -4407,7 +4482,7 @@
         </is>
       </c>
       <c r="B79" s="7">
-        <f>SUM('Астон.Движение'!B79,'Астон.Реформа'!B79,'Милый дом'!B79,'River Park'!B79)</f>
+        <f>SUM(C79,D79,E79,F79)</f>
         <v/>
       </c>
       <c r="C79" s="7">
@@ -4430,9 +4505,10 @@
         <f>SUM('Астон.Движение'!G79,'Астон.Реформа'!G79,'Милый дом'!G79,'River Park'!G79)</f>
         <v/>
       </c>
-      <c r="H79" s="7">
-        <f>SUM('Астон.Движение'!H79,'Астон.Реформа'!H79,'Милый дом'!H79,'River Park'!H79)</f>
-        <v/>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I79" s="7">
         <f>SUM('Астон.Движение'!I79,'Астон.Реформа'!I79,'Милый дом'!I79,'River Park'!I79)</f>
@@ -4480,9 +4556,10 @@
         <f>G43-G45</f>
         <v/>
       </c>
-      <c r="H80" s="9">
-        <f>H43-H45</f>
-        <v/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" s="9">
         <f>I43-I45</f>
@@ -4530,9 +4607,10 @@
         <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
-      <c r="H81" s="10">
-        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
-        <v/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" s="10">
         <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
@@ -4580,9 +4658,10 @@
         <f>SUM(G83,G84,G85,G86)</f>
         <v/>
       </c>
-      <c r="H82" s="7">
-        <f>SUM(H83,H84,H85,H86)</f>
-        <v/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" s="7">
         <f>SUM(I83,I84,I85,I86)</f>
@@ -4607,7 +4686,7 @@
         </is>
       </c>
       <c r="B83" s="7">
-        <f>SUM('Астон.Движение'!B83,'Астон.Реформа'!B83,'Милый дом'!B83,'River Park'!B83)</f>
+        <f>SUM(C83,D83,E83,F83)</f>
         <v/>
       </c>
       <c r="C83" s="7">
@@ -4630,9 +4709,10 @@
         <f>SUM('Астон.Движение'!G83,'Астон.Реформа'!G83,'Милый дом'!G83,'River Park'!G83)</f>
         <v/>
       </c>
-      <c r="H83" s="7">
-        <f>SUM('Астон.Движение'!H83,'Астон.Реформа'!H83,'Милый дом'!H83,'River Park'!H83)</f>
-        <v/>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I83" s="7">
         <f>SUM('Астон.Движение'!I83,'Астон.Реформа'!I83,'Милый дом'!I83,'River Park'!I83)</f>
@@ -4657,7 +4737,7 @@
         </is>
       </c>
       <c r="B84" s="7">
-        <f>SUM('Астон.Движение'!B84,'Астон.Реформа'!B84,'Милый дом'!B84,'River Park'!B84)</f>
+        <f>SUM(C84,D84,E84,F84)</f>
         <v/>
       </c>
       <c r="C84" s="7">
@@ -4680,9 +4760,10 @@
         <f>SUM('Астон.Движение'!G84,'Астон.Реформа'!G84,'Милый дом'!G84,'River Park'!G84)</f>
         <v/>
       </c>
-      <c r="H84" s="7">
-        <f>SUM('Астон.Движение'!H84,'Астон.Реформа'!H84,'Милый дом'!H84,'River Park'!H84)</f>
-        <v/>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I84" s="7">
         <f>SUM('Астон.Движение'!I84,'Астон.Реформа'!I84,'Милый дом'!I84,'River Park'!I84)</f>
@@ -4707,7 +4788,7 @@
         </is>
       </c>
       <c r="B85" s="7">
-        <f>SUM('Астон.Движение'!B85,'Астон.Реформа'!B85,'Милый дом'!B85,'River Park'!B85)</f>
+        <f>SUM(C85,D85,E85,F85)</f>
         <v/>
       </c>
       <c r="C85" s="7">
@@ -4730,9 +4811,10 @@
         <f>SUM('Астон.Движение'!G85,'Астон.Реформа'!G85,'Милый дом'!G85,'River Park'!G85)</f>
         <v/>
       </c>
-      <c r="H85" s="7">
-        <f>SUM('Астон.Движение'!H85,'Астон.Реформа'!H85,'Милый дом'!H85,'River Park'!H85)</f>
-        <v/>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I85" s="7">
         <f>SUM('Астон.Движение'!I85,'Астон.Реформа'!I85,'Милый дом'!I85,'River Park'!I85)</f>
@@ -4757,7 +4839,7 @@
         </is>
       </c>
       <c r="B86" s="7">
-        <f>SUM('Астон.Движение'!B86,'Астон.Реформа'!B86,'Милый дом'!B86,'River Park'!B86)</f>
+        <f>SUM(C86,D86,E86,F86)</f>
         <v/>
       </c>
       <c r="C86" s="7">
@@ -4780,9 +4862,10 @@
         <f>SUM('Астон.Движение'!G86,'Астон.Реформа'!G86,'Милый дом'!G86,'River Park'!G86)</f>
         <v/>
       </c>
-      <c r="H86" s="7">
-        <f>SUM('Астон.Движение'!H86,'Астон.Реформа'!H86,'Милый дом'!H86,'River Park'!H86)</f>
-        <v/>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I86" s="7">
         <f>SUM('Астон.Движение'!I86,'Астон.Реформа'!I86,'Милый дом'!I86,'River Park'!I86)</f>
@@ -4830,9 +4913,10 @@
         <f>SUM(G88)</f>
         <v/>
       </c>
-      <c r="H87" s="7">
-        <f>SUM(H88)</f>
-        <v/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="7">
         <f>SUM(I88)</f>
@@ -4857,7 +4941,7 @@
         </is>
       </c>
       <c r="B88" s="7">
-        <f>SUM('Астон.Движение'!B88,'Астон.Реформа'!B88,'Милый дом'!B88,'River Park'!B88)</f>
+        <f>SUM(C88,D88,E88,F88)</f>
         <v/>
       </c>
       <c r="C88" s="7">
@@ -4880,9 +4964,10 @@
         <f>SUM('Астон.Движение'!G88,'Астон.Реформа'!G88,'Милый дом'!G88,'River Park'!G88)</f>
         <v/>
       </c>
-      <c r="H88" s="7">
-        <f>SUM('Астон.Движение'!H88,'Астон.Реформа'!H88,'Милый дом'!H88,'River Park'!H88)</f>
-        <v/>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I88" s="7">
         <f>SUM('Астон.Движение'!I88,'Астон.Реформа'!I88,'Милый дом'!I88,'River Park'!I88)</f>
@@ -4930,9 +5015,10 @@
         <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
-        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
-        <v/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="9">
         <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
@@ -4980,9 +5066,10 @@
         <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
-      <c r="H90" s="10">
-        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
-        <v/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I90" s="10">
         <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
@@ -5030,9 +5117,10 @@
         <f>SUM(G92,G93)</f>
         <v/>
       </c>
-      <c r="H91" s="7">
-        <f>SUM(H92,H93)</f>
-        <v/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I91" s="7">
         <f>SUM(I92,I93)</f>
@@ -5057,7 +5145,7 @@
         </is>
       </c>
       <c r="B92" s="7">
-        <f>SUM('Астон.Движение'!B92,'Астон.Реформа'!B92,'Милый дом'!B92,'River Park'!B92)</f>
+        <f>SUM(C92,D92,E92,F92)</f>
         <v/>
       </c>
       <c r="C92" s="7">
@@ -5080,9 +5168,10 @@
         <f>SUM('Астон.Движение'!G92,'Астон.Реформа'!G92,'Милый дом'!G92,'River Park'!G92)</f>
         <v/>
       </c>
-      <c r="H92" s="7">
-        <f>SUM('Астон.Движение'!H92,'Астон.Реформа'!H92,'Милый дом'!H92,'River Park'!H92)</f>
-        <v/>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I92" s="7">
         <f>SUM('Астон.Движение'!I92,'Астон.Реформа'!I92,'Милый дом'!I92,'River Park'!I92)</f>
@@ -5107,7 +5196,7 @@
         </is>
       </c>
       <c r="B93" s="7">
-        <f>SUM('Астон.Движение'!B93,'Астон.Реформа'!B93,'Милый дом'!B93,'River Park'!B93)</f>
+        <f>SUM(C93,D93,E93,F93)</f>
         <v/>
       </c>
       <c r="C93" s="7">
@@ -5130,9 +5219,10 @@
         <f>SUM('Астон.Движение'!G93,'Астон.Реформа'!G93,'Милый дом'!G93,'River Park'!G93)</f>
         <v/>
       </c>
-      <c r="H93" s="7">
-        <f>SUM('Астон.Движение'!H93,'Астон.Реформа'!H93,'Милый дом'!H93,'River Park'!H93)</f>
-        <v/>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I93" s="7">
         <f>SUM('Астон.Движение'!I93,'Астон.Реформа'!I93,'Милый дом'!I93,'River Park'!I93)</f>
@@ -5157,7 +5247,7 @@
         </is>
       </c>
       <c r="B94" s="7">
-        <f>SUM('Астон.Движение'!B94,'Астон.Реформа'!B94,'Милый дом'!B94,'River Park'!B94)</f>
+        <f>SUM(C94,D94,E94,F94)</f>
         <v/>
       </c>
       <c r="C94" s="7">
@@ -5180,9 +5270,10 @@
         <f>SUM('Астон.Движение'!G94,'Астон.Реформа'!G94,'Милый дом'!G94,'River Park'!G94)</f>
         <v/>
       </c>
-      <c r="H94" s="7">
-        <f>SUM('Астон.Движение'!H94,'Астон.Реформа'!H94,'Милый дом'!H94,'River Park'!H94)</f>
-        <v/>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I94" s="7">
         <f>SUM('Астон.Движение'!I94,'Астон.Реформа'!I94,'Милый дом'!I94,'River Park'!I94)</f>
@@ -5230,9 +5321,10 @@
         <f>SUM(G96,G97)</f>
         <v/>
       </c>
-      <c r="H95" s="7">
-        <f>SUM(H96,H97)</f>
-        <v/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="7">
         <f>SUM(I96,I97)</f>
@@ -5257,7 +5349,7 @@
         </is>
       </c>
       <c r="B96" s="7">
-        <f>SUM('Астон.Движение'!B96,'Астон.Реформа'!B96,'Милый дом'!B96,'River Park'!B96)</f>
+        <f>SUM(C96,D96,E96,F96)</f>
         <v/>
       </c>
       <c r="C96" s="7">
@@ -5280,9 +5372,10 @@
         <f>SUM('Астон.Движение'!G96,'Астон.Реформа'!G96,'Милый дом'!G96,'River Park'!G96)</f>
         <v/>
       </c>
-      <c r="H96" s="7">
-        <f>SUM('Астон.Движение'!H96,'Астон.Реформа'!H96,'Милый дом'!H96,'River Park'!H96)</f>
-        <v/>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I96" s="7">
         <f>SUM('Астон.Движение'!I96,'Астон.Реформа'!I96,'Милый дом'!I96,'River Park'!I96)</f>
@@ -5307,7 +5400,7 @@
         </is>
       </c>
       <c r="B97" s="7">
-        <f>SUM('Астон.Движение'!B97,'Астон.Реформа'!B97,'Милый дом'!B97,'River Park'!B97)</f>
+        <f>SUM(C97,D97,E97,F97)</f>
         <v/>
       </c>
       <c r="C97" s="7">
@@ -5330,9 +5423,10 @@
         <f>SUM('Астон.Движение'!G97,'Астон.Реформа'!G97,'Милый дом'!G97,'River Park'!G97)</f>
         <v/>
       </c>
-      <c r="H97" s="7">
-        <f>SUM('Астон.Движение'!H97,'Астон.Реформа'!H97,'Милый дом'!H97,'River Park'!H97)</f>
-        <v/>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I97" s="7">
         <f>SUM('Астон.Движение'!I97,'Астон.Реформа'!I97,'Милый дом'!I97,'River Park'!I97)</f>
@@ -5380,9 +5474,10 @@
         <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
-      <c r="H98" s="9">
-        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
-        <v/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="9">
         <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
@@ -5430,9 +5525,10 @@
         <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
-      <c r="H99" s="10">
-        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
-        <v/>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="10">
         <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
@@ -5639,9 +5735,10 @@
         <f>SUM(G5,G6)</f>
         <v/>
       </c>
-      <c r="H4" s="7">
-        <f>SUM(H5,H6)</f>
-        <v/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="7">
         <f>SUM(I5,I6)</f>
@@ -5665,10 +5762,9 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="7">
+        <f>SUM(C5,D5,E5,F5)</f>
+        <v/>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -5747,9 +5843,10 @@
         <f>SUM(G7,G8,G9)</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>SUM(H7,H8,H9)</f>
-        <v/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I6" s="7">
         <f>SUM(I7,I8,I9)</f>
@@ -5773,8 +5870,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>656000</v>
+      <c r="B7" s="7">
+        <f>SUM(C7,D7,E7,F7)</f>
+        <v/>
       </c>
       <c r="C7" s="7" t="n">
         <v>164000</v>
@@ -5821,10 +5919,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="7">
+        <f>SUM(C8,D8,E8,F8)</f>
+        <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -5879,10 +5976,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="7">
+        <f>SUM(C9,D9,E9,F9)</f>
+        <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -5961,9 +6057,10 @@
         <f>SUM(G11,G12,G13,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30,G31,G32,G33,G34)</f>
         <v/>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(H11,H12,H13,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30,H31,H32,H33,H34)</f>
-        <v/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7">
         <f>SUM(I11,I12,I13,I21,I22,I23,I24,I25,I26,I27,I28,I29,I30,I31,I32,I33,I34)</f>
@@ -5987,10 +6084,9 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="7">
+        <f>SUM(C11,D11,E11,F11)</f>
+        <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -6045,8 +6141,9 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
-        <v>1486</v>
+      <c r="B12" s="7">
+        <f>SUM(C12,D12,E12,F12)</f>
+        <v/>
       </c>
       <c r="C12" s="7" t="n">
         <v>1486</v>
@@ -6123,9 +6220,10 @@
         <f>SUM(G14,G15,G16,G17,G18,G19,G20)</f>
         <v/>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(H14,H15,H16,H17,H18,H19,H20)</f>
-        <v/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7">
         <f>SUM(I14,I15,I16,I17,I18,I19,I20)</f>
@@ -6149,10 +6247,9 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="7">
+        <f>SUM(C14,D14,E14,F14)</f>
+        <v/>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -6207,10 +6304,9 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="7">
+        <f>SUM(C15,D15,E15,F15)</f>
+        <v/>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -6265,10 +6361,9 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="7">
+        <f>SUM(C16,D16,E16,F16)</f>
+        <v/>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -6323,8 +6418,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>8000</v>
+      <c r="B17" s="7">
+        <f>SUM(C17,D17,E17,F17)</f>
+        <v/>
       </c>
       <c r="C17" s="7" t="n">
         <v>2000</v>
@@ -6371,8 +6467,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>7262</v>
+      <c r="B18" s="7">
+        <f>SUM(C18,D18,E18,F18)</f>
+        <v/>
       </c>
       <c r="C18" s="7" t="n">
         <v>1262</v>
@@ -6419,10 +6516,9 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B19" s="7">
+        <f>SUM(C19,D19,E19,F19)</f>
+        <v/>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -6477,10 +6573,9 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="7">
+        <f>SUM(C20,D20,E20,F20)</f>
+        <v/>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -6535,8 +6630,9 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>200000</v>
+      <c r="B21" s="7">
+        <f>SUM(C21,D21,E21,F21)</f>
+        <v/>
       </c>
       <c r="C21" s="7" t="n">
         <v>50000</v>
@@ -6583,8 +6679,9 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>280000</v>
+      <c r="B22" s="7">
+        <f>SUM(C22,D22,E22,F22)</f>
+        <v/>
       </c>
       <c r="C22" s="7" t="n">
         <v>70000</v>
@@ -6631,10 +6728,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="7">
+        <f>SUM(C23,D23,E23,F23)</f>
+        <v/>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -6689,10 +6785,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="7">
+        <f>SUM(C24,D24,E24,F24)</f>
+        <v/>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -6747,10 +6842,9 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="7">
+        <f>SUM(C25,D25,E25,F25)</f>
+        <v/>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -6805,10 +6899,9 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="7">
+        <f>SUM(C26,D26,E26,F26)</f>
+        <v/>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -6863,10 +6956,9 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="7">
+        <f>SUM(C27,D27,E27,F27)</f>
+        <v/>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -6921,10 +7013,9 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="7">
+        <f>SUM(C28,D28,E28,F28)</f>
+        <v/>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -6979,10 +7070,9 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="7">
+        <f>SUM(C29,D29,E29,F29)</f>
+        <v/>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -7037,10 +7127,9 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="7">
+        <f>SUM(C30,D30,E30,F30)</f>
+        <v/>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -7095,10 +7184,9 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="7">
+        <f>SUM(C31,D31,E31,F31)</f>
+        <v/>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -7153,10 +7241,9 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="7">
+        <f>SUM(C32,D32,E32,F32)</f>
+        <v/>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -7211,10 +7298,9 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B33" s="7">
+        <f>SUM(C33,D33,E33,F33)</f>
+        <v/>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -7293,9 +7379,10 @@
         <f>SUM(G35,G36,G37,G38,G39,G40,G41,G42)</f>
         <v/>
       </c>
-      <c r="H34" s="7">
-        <f>SUM(H35,H36,H37,H38,H39,H40,H41,H42)</f>
-        <v/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" s="7">
         <f>SUM(I35,I36,I37,I38,I39,I40,I41,I42)</f>
@@ -7319,10 +7406,9 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="7">
+        <f>SUM(C35,D35,E35,F35)</f>
+        <v/>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -7377,10 +7463,9 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="7">
+        <f>SUM(C36,D36,E36,F36)</f>
+        <v/>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -7435,8 +7520,9 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
-        <v>332.45</v>
+      <c r="B37" s="7">
+        <f>SUM(C37,D37,E37,F37)</f>
+        <v/>
       </c>
       <c r="C37" s="7" t="n">
         <v>332.45</v>
@@ -7489,10 +7575,9 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="7">
+        <f>SUM(C38,D38,E38,F38)</f>
+        <v/>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -7547,8 +7632,9 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
-        <v>33600</v>
+      <c r="B39" s="7">
+        <f>SUM(C39,D39,E39,F39)</f>
+        <v/>
       </c>
       <c r="C39" s="7" t="n">
         <v>8400</v>
@@ -7595,10 +7681,9 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="7">
+        <f>SUM(C40,D40,E40,F40)</f>
+        <v/>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -7653,10 +7738,9 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="7">
+        <f>SUM(C41,D41,E41,F41)</f>
+        <v/>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
@@ -7711,10 +7795,9 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="7">
+        <f>SUM(C42,D42,E42,F42)</f>
+        <v/>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -7793,9 +7876,10 @@
         <f>G4-G10</f>
         <v/>
       </c>
-      <c r="H43" s="9">
-        <f>H4-H10</f>
-        <v/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="9">
         <f>I4-I10</f>
@@ -7843,9 +7927,10 @@
         <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
-        <v/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="10">
         <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
@@ -7893,9 +7978,10 @@
         <f>SUM(G46,G47,G48,G52,G56,G57,G58,G59,G60,G63,G64,G65,G66,G67,G68,G69,G70,G71,G72,G73,G74,G75,G76,G77,G78,G79)</f>
         <v/>
       </c>
-      <c r="H45" s="7">
-        <f>SUM(H46,H47,H48,H52,H56,H57,H58,H59,H60,H63,H64,H65,H66,H67,H68,H69,H70,H71,H72,H73,H74,H75,H76,H77,H78,H79)</f>
-        <v/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="7">
         <f>SUM(I46,I47,I48,I52,I56,I57,I58,I59,I60,I63,I64,I65,I66,I67,I68,I69,I70,I71,I72,I73,I74,I75,I76,I77,I78,I79)</f>
@@ -7919,10 +8005,9 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="7">
+        <f>SUM(C46,D46,E46,F46)</f>
+        <v/>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
@@ -7977,10 +8062,9 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="7">
+        <f>SUM(C47,D47,E47,F47)</f>
+        <v/>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -8059,9 +8143,10 @@
         <f>SUM(G49,G50,G51)</f>
         <v/>
       </c>
-      <c r="H48" s="7">
-        <f>SUM(H49,H50,H51)</f>
-        <v/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="7">
         <f>SUM(I49,I50,I51)</f>
@@ -8085,10 +8170,9 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="7">
+        <f>SUM(C49,D49,E49,F49)</f>
+        <v/>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -8143,10 +8227,9 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="7">
+        <f>SUM(C50,D50,E50,F50)</f>
+        <v/>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -8201,10 +8284,9 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="7">
+        <f>SUM(C51,D51,E51,F51)</f>
+        <v/>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -8283,9 +8365,10 @@
         <f>SUM(G53,G54,G55)</f>
         <v/>
       </c>
-      <c r="H52" s="7">
-        <f>SUM(H53,H54,H55)</f>
-        <v/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="7">
         <f>SUM(I53,I54,I55)</f>
@@ -8309,10 +8392,9 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="7">
+        <f>SUM(C53,D53,E53,F53)</f>
+        <v/>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -8367,10 +8449,9 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="7">
+        <f>SUM(C54,D54,E54,F54)</f>
+        <v/>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -8425,10 +8506,9 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B55" s="7">
+        <f>SUM(C55,D55,E55,F55)</f>
+        <v/>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -8483,10 +8563,9 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="7">
+        <f>SUM(C56,D56,E56,F56)</f>
+        <v/>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -8541,10 +8620,9 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="7">
+        <f>SUM(C57,D57,E57,F57)</f>
+        <v/>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -8599,10 +8677,9 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="7">
+        <f>SUM(C58,D58,E58,F58)</f>
+        <v/>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -8657,10 +8734,9 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="7">
+        <f>SUM(C59,D59,E59,F59)</f>
+        <v/>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -8739,9 +8815,10 @@
         <f>SUM(G61,G62)</f>
         <v/>
       </c>
-      <c r="H60" s="7">
-        <f>SUM(H61,H62)</f>
-        <v/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="7">
         <f>SUM(I61,I62)</f>
@@ -8765,10 +8842,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="7">
+        <f>SUM(C61,D61,E61,F61)</f>
+        <v/>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -8823,10 +8899,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="7">
+        <f>SUM(C62,D62,E62,F62)</f>
+        <v/>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -8881,10 +8956,9 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="7">
+        <f>SUM(C63,D63,E63,F63)</f>
+        <v/>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -8939,10 +9013,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="7">
+        <f>SUM(C64,D64,E64,F64)</f>
+        <v/>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -8997,10 +9070,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="7">
+        <f>SUM(C65,D65,E65,F65)</f>
+        <v/>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -9055,10 +9127,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="7">
+        <f>SUM(C66,D66,E66,F66)</f>
+        <v/>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -9113,10 +9184,9 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="7">
+        <f>SUM(C67,D67,E67,F67)</f>
+        <v/>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -9171,10 +9241,9 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="7">
+        <f>SUM(C68,D68,E68,F68)</f>
+        <v/>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -9229,10 +9298,9 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="7">
+        <f>SUM(C69,D69,E69,F69)</f>
+        <v/>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -9287,10 +9355,9 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="7">
+        <f>SUM(C70,D70,E70,F70)</f>
+        <v/>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -9345,10 +9412,9 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="7">
+        <f>SUM(C71,D71,E71,F71)</f>
+        <v/>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -9403,10 +9469,9 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="7">
+        <f>SUM(C72,D72,E72,F72)</f>
+        <v/>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -9461,10 +9526,9 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="7">
+        <f>SUM(C73,D73,E73,F73)</f>
+        <v/>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -9519,10 +9583,9 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="7">
+        <f>SUM(C74,D74,E74,F74)</f>
+        <v/>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -9577,10 +9640,9 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="7">
+        <f>SUM(C75,D75,E75,F75)</f>
+        <v/>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -9635,10 +9697,9 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="7">
+        <f>SUM(C76,D76,E76,F76)</f>
+        <v/>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -9693,10 +9754,9 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="7">
+        <f>SUM(C77,D77,E77,F77)</f>
+        <v/>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -9751,10 +9811,9 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="7">
+        <f>SUM(C78,D78,E78,F78)</f>
+        <v/>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -9809,10 +9868,9 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="7">
+        <f>SUM(C79,D79,E79,F79)</f>
+        <v/>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -9891,9 +9949,10 @@
         <f>G43-G45</f>
         <v/>
       </c>
-      <c r="H80" s="9">
-        <f>H43-H45</f>
-        <v/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" s="9">
         <f>I43-I45</f>
@@ -9941,9 +10000,10 @@
         <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
-      <c r="H81" s="10">
-        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
-        <v/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" s="10">
         <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
@@ -9991,9 +10051,10 @@
         <f>SUM(G83,G84,G85,G86)</f>
         <v/>
       </c>
-      <c r="H82" s="7">
-        <f>SUM(H83,H84,H85,H86)</f>
-        <v/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" s="7">
         <f>SUM(I83,I84,I85,I86)</f>
@@ -10017,10 +10078,9 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="7">
+        <f>SUM(C83,D83,E83,F83)</f>
+        <v/>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -10075,10 +10135,9 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="7">
+        <f>SUM(C84,D84,E84,F84)</f>
+        <v/>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -10133,10 +10192,9 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="7">
+        <f>SUM(C85,D85,E85,F85)</f>
+        <v/>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -10191,10 +10249,9 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="7">
+        <f>SUM(C86,D86,E86,F86)</f>
+        <v/>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -10273,9 +10330,10 @@
         <f>SUM(G88)</f>
         <v/>
       </c>
-      <c r="H87" s="7">
-        <f>SUM(H88)</f>
-        <v/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="7">
         <f>SUM(I88)</f>
@@ -10299,10 +10357,9 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="7">
+        <f>SUM(C88,D88,E88,F88)</f>
+        <v/>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -10381,9 +10438,10 @@
         <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
-        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
-        <v/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="9">
         <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
@@ -10431,9 +10489,10 @@
         <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
-      <c r="H90" s="10">
-        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
-        <v/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I90" s="10">
         <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
@@ -10481,9 +10540,10 @@
         <f>SUM(G92,G93)</f>
         <v/>
       </c>
-      <c r="H91" s="7">
-        <f>SUM(H92,H93)</f>
-        <v/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I91" s="7">
         <f>SUM(I92,I93)</f>
@@ -10507,10 +10567,9 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="7">
+        <f>SUM(C92,D92,E92,F92)</f>
+        <v/>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -10565,10 +10624,9 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="7">
+        <f>SUM(C93,D93,E93,F93)</f>
+        <v/>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -10623,10 +10681,9 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="7">
+        <f>SUM(C94,D94,E94,F94)</f>
+        <v/>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -10705,9 +10762,10 @@
         <f>SUM(G96,G97)</f>
         <v/>
       </c>
-      <c r="H95" s="7">
-        <f>SUM(H96,H97)</f>
-        <v/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="7">
         <f>SUM(I96,I97)</f>
@@ -10731,8 +10789,9 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
-        <v>46000</v>
+      <c r="B96" s="7">
+        <f>SUM(C96,D96,E96,F96)</f>
+        <v/>
       </c>
       <c r="C96" s="7" t="n">
         <v>11500</v>
@@ -10779,10 +10838,9 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="7">
+        <f>SUM(C97,D97,E97,F97)</f>
+        <v/>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
@@ -10861,9 +10919,10 @@
         <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
-      <c r="H98" s="9">
-        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
-        <v/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="9">
         <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
@@ -10911,9 +10970,10 @@
         <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
-      <c r="H99" s="10">
-        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
-        <v/>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="10">
         <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
@@ -11120,9 +11180,10 @@
         <f>SUM(G5,G6)</f>
         <v/>
       </c>
-      <c r="H4" s="7">
-        <f>SUM(H5,H6)</f>
-        <v/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="7">
         <f>SUM(I5,I6)</f>
@@ -11146,10 +11207,9 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="7">
+        <f>SUM(C5,D5,E5,F5)</f>
+        <v/>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -11228,9 +11288,10 @@
         <f>SUM(G7,G8,G9)</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>SUM(H7,H8,H9)</f>
-        <v/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I6" s="7">
         <f>SUM(I7,I8,I9)</f>
@@ -11254,8 +11315,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>384000</v>
+      <c r="B7" s="7">
+        <f>SUM(C7,D7,E7,F7)</f>
+        <v/>
       </c>
       <c r="C7" s="7" t="n">
         <v>96000</v>
@@ -11302,10 +11364,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="7">
+        <f>SUM(C8,D8,E8,F8)</f>
+        <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -11360,10 +11421,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="7">
+        <f>SUM(C9,D9,E9,F9)</f>
+        <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -11442,9 +11502,10 @@
         <f>SUM(G11,G12,G13,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30,G31,G32,G33,G34)</f>
         <v/>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(H11,H12,H13,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30,H31,H32,H33,H34)</f>
-        <v/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7">
         <f>SUM(I11,I12,I13,I21,I22,I23,I24,I25,I26,I27,I28,I29,I30,I31,I32,I33,I34)</f>
@@ -11468,10 +11529,9 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="7">
+        <f>SUM(C11,D11,E11,F11)</f>
+        <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -11526,10 +11586,9 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="7">
+        <f>SUM(C12,D12,E12,F12)</f>
+        <v/>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -11608,9 +11667,10 @@
         <f>SUM(G14,G15,G16,G17,G18,G19,G20)</f>
         <v/>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(H14,H15,H16,H17,H18,H19,H20)</f>
-        <v/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7">
         <f>SUM(I14,I15,I16,I17,I18,I19,I20)</f>
@@ -11634,10 +11694,9 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="7">
+        <f>SUM(C14,D14,E14,F14)</f>
+        <v/>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -11692,10 +11751,9 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="7">
+        <f>SUM(C15,D15,E15,F15)</f>
+        <v/>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -11750,10 +11808,9 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="7">
+        <f>SUM(C16,D16,E16,F16)</f>
+        <v/>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -11808,8 +11865,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>8000</v>
+      <c r="B17" s="7">
+        <f>SUM(C17,D17,E17,F17)</f>
+        <v/>
       </c>
       <c r="C17" s="7" t="n">
         <v>2000</v>
@@ -11856,8 +11914,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>8000</v>
+      <c r="B18" s="7">
+        <f>SUM(C18,D18,E18,F18)</f>
+        <v/>
       </c>
       <c r="C18" s="7" t="n">
         <v>2000</v>
@@ -11904,10 +11963,9 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B19" s="7">
+        <f>SUM(C19,D19,E19,F19)</f>
+        <v/>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -11962,10 +12020,9 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="7">
+        <f>SUM(C20,D20,E20,F20)</f>
+        <v/>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -12020,8 +12077,9 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>140000</v>
+      <c r="B21" s="7">
+        <f>SUM(C21,D21,E21,F21)</f>
+        <v/>
       </c>
       <c r="C21" s="7" t="n">
         <v>35000</v>
@@ -12068,8 +12126,9 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>140000</v>
+      <c r="B22" s="7">
+        <f>SUM(C22,D22,E22,F22)</f>
+        <v/>
       </c>
       <c r="C22" s="7" t="n">
         <v>35000</v>
@@ -12116,8 +12175,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
-        <v>42000</v>
+      <c r="B23" s="7">
+        <f>SUM(C23,D23,E23,F23)</f>
+        <v/>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -12166,10 +12226,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="7">
+        <f>SUM(C24,D24,E24,F24)</f>
+        <v/>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -12224,10 +12283,9 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="7">
+        <f>SUM(C25,D25,E25,F25)</f>
+        <v/>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -12282,10 +12340,9 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="7">
+        <f>SUM(C26,D26,E26,F26)</f>
+        <v/>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -12340,10 +12397,9 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="7">
+        <f>SUM(C27,D27,E27,F27)</f>
+        <v/>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -12398,10 +12454,9 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="7">
+        <f>SUM(C28,D28,E28,F28)</f>
+        <v/>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -12456,10 +12511,9 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="7">
+        <f>SUM(C29,D29,E29,F29)</f>
+        <v/>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -12514,10 +12568,9 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="7">
+        <f>SUM(C30,D30,E30,F30)</f>
+        <v/>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -12572,10 +12625,9 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="7">
+        <f>SUM(C31,D31,E31,F31)</f>
+        <v/>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -12630,10 +12682,9 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="7">
+        <f>SUM(C32,D32,E32,F32)</f>
+        <v/>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -12688,10 +12739,9 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B33" s="7">
+        <f>SUM(C33,D33,E33,F33)</f>
+        <v/>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -12770,9 +12820,10 @@
         <f>SUM(G35,G36,G37,G38,G39,G40,G41,G42)</f>
         <v/>
       </c>
-      <c r="H34" s="7">
-        <f>SUM(H35,H36,H37,H38,H39,H40,H41,H42)</f>
-        <v/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" s="7">
         <f>SUM(I35,I36,I37,I38,I39,I40,I41,I42)</f>
@@ -12796,10 +12847,9 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="7">
+        <f>SUM(C35,D35,E35,F35)</f>
+        <v/>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -12854,10 +12904,9 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="7">
+        <f>SUM(C36,D36,E36,F36)</f>
+        <v/>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -12912,10 +12961,9 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="7">
+        <f>SUM(C37,D37,E37,F37)</f>
+        <v/>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
@@ -12970,10 +13018,9 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="7">
+        <f>SUM(C38,D38,E38,F38)</f>
+        <v/>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -13028,8 +13075,9 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
-        <v>12000</v>
+      <c r="B39" s="7">
+        <f>SUM(C39,D39,E39,F39)</f>
+        <v/>
       </c>
       <c r="C39" s="7" t="n">
         <v>3000</v>
@@ -13076,10 +13124,9 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="7">
+        <f>SUM(C40,D40,E40,F40)</f>
+        <v/>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -13134,10 +13181,9 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="7">
+        <f>SUM(C41,D41,E41,F41)</f>
+        <v/>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
@@ -13192,10 +13238,9 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="7">
+        <f>SUM(C42,D42,E42,F42)</f>
+        <v/>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -13274,9 +13319,10 @@
         <f>G4-G10</f>
         <v/>
       </c>
-      <c r="H43" s="9">
-        <f>H4-H10</f>
-        <v/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="9">
         <f>I4-I10</f>
@@ -13324,9 +13370,10 @@
         <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
-        <v/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="10">
         <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
@@ -13374,9 +13421,10 @@
         <f>SUM(G46,G47,G48,G52,G56,G57,G58,G59,G60,G63,G64,G65,G66,G67,G68,G69,G70,G71,G72,G73,G74,G75,G76,G77,G78,G79)</f>
         <v/>
       </c>
-      <c r="H45" s="7">
-        <f>SUM(H46,H47,H48,H52,H56,H57,H58,H59,H60,H63,H64,H65,H66,H67,H68,H69,H70,H71,H72,H73,H74,H75,H76,H77,H78,H79)</f>
-        <v/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="7">
         <f>SUM(I46,I47,I48,I52,I56,I57,I58,I59,I60,I63,I64,I65,I66,I67,I68,I69,I70,I71,I72,I73,I74,I75,I76,I77,I78,I79)</f>
@@ -13400,10 +13448,9 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="7">
+        <f>SUM(C46,D46,E46,F46)</f>
+        <v/>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
@@ -13458,10 +13505,9 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="7">
+        <f>SUM(C47,D47,E47,F47)</f>
+        <v/>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -13540,9 +13586,10 @@
         <f>SUM(G49,G50,G51)</f>
         <v/>
       </c>
-      <c r="H48" s="7">
-        <f>SUM(H49,H50,H51)</f>
-        <v/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="7">
         <f>SUM(I49,I50,I51)</f>
@@ -13566,10 +13613,9 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="7">
+        <f>SUM(C49,D49,E49,F49)</f>
+        <v/>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -13624,10 +13670,9 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="7">
+        <f>SUM(C50,D50,E50,F50)</f>
+        <v/>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -13682,10 +13727,9 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="7">
+        <f>SUM(C51,D51,E51,F51)</f>
+        <v/>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -13764,9 +13808,10 @@
         <f>SUM(G53,G54,G55)</f>
         <v/>
       </c>
-      <c r="H52" s="7">
-        <f>SUM(H53,H54,H55)</f>
-        <v/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="7">
         <f>SUM(I53,I54,I55)</f>
@@ -13790,10 +13835,9 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="7">
+        <f>SUM(C53,D53,E53,F53)</f>
+        <v/>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -13848,10 +13892,9 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="7">
+        <f>SUM(C54,D54,E54,F54)</f>
+        <v/>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -13906,10 +13949,9 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B55" s="7">
+        <f>SUM(C55,D55,E55,F55)</f>
+        <v/>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -13964,10 +14006,9 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="7">
+        <f>SUM(C56,D56,E56,F56)</f>
+        <v/>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -14022,10 +14063,9 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="7">
+        <f>SUM(C57,D57,E57,F57)</f>
+        <v/>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -14080,10 +14120,9 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="7">
+        <f>SUM(C58,D58,E58,F58)</f>
+        <v/>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -14138,10 +14177,9 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="7">
+        <f>SUM(C59,D59,E59,F59)</f>
+        <v/>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -14220,9 +14258,10 @@
         <f>SUM(G61,G62)</f>
         <v/>
       </c>
-      <c r="H60" s="7">
-        <f>SUM(H61,H62)</f>
-        <v/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="7">
         <f>SUM(I61,I62)</f>
@@ -14246,10 +14285,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="7">
+        <f>SUM(C61,D61,E61,F61)</f>
+        <v/>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -14304,10 +14342,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="7">
+        <f>SUM(C62,D62,E62,F62)</f>
+        <v/>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -14362,10 +14399,9 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="7">
+        <f>SUM(C63,D63,E63,F63)</f>
+        <v/>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -14420,10 +14456,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="7">
+        <f>SUM(C64,D64,E64,F64)</f>
+        <v/>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -14478,10 +14513,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="7">
+        <f>SUM(C65,D65,E65,F65)</f>
+        <v/>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -14536,10 +14570,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="7">
+        <f>SUM(C66,D66,E66,F66)</f>
+        <v/>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -14594,10 +14627,9 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="7">
+        <f>SUM(C67,D67,E67,F67)</f>
+        <v/>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -14652,10 +14684,9 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="7">
+        <f>SUM(C68,D68,E68,F68)</f>
+        <v/>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -14710,10 +14741,9 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="7">
+        <f>SUM(C69,D69,E69,F69)</f>
+        <v/>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -14768,10 +14798,9 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="7">
+        <f>SUM(C70,D70,E70,F70)</f>
+        <v/>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -14826,10 +14855,9 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="7">
+        <f>SUM(C71,D71,E71,F71)</f>
+        <v/>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -14884,10 +14912,9 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="7">
+        <f>SUM(C72,D72,E72,F72)</f>
+        <v/>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -14942,10 +14969,9 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="7">
+        <f>SUM(C73,D73,E73,F73)</f>
+        <v/>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -15000,10 +15026,9 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="7">
+        <f>SUM(C74,D74,E74,F74)</f>
+        <v/>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -15058,10 +15083,9 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="7">
+        <f>SUM(C75,D75,E75,F75)</f>
+        <v/>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -15116,10 +15140,9 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="7">
+        <f>SUM(C76,D76,E76,F76)</f>
+        <v/>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -15174,10 +15197,9 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="7">
+        <f>SUM(C77,D77,E77,F77)</f>
+        <v/>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -15232,10 +15254,9 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="7">
+        <f>SUM(C78,D78,E78,F78)</f>
+        <v/>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -15290,10 +15311,9 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="7">
+        <f>SUM(C79,D79,E79,F79)</f>
+        <v/>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -15372,9 +15392,10 @@
         <f>G43-G45</f>
         <v/>
       </c>
-      <c r="H80" s="9">
-        <f>H43-H45</f>
-        <v/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" s="9">
         <f>I43-I45</f>
@@ -15422,9 +15443,10 @@
         <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
-      <c r="H81" s="10">
-        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
-        <v/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" s="10">
         <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
@@ -15472,9 +15494,10 @@
         <f>SUM(G83,G84,G85,G86)</f>
         <v/>
       </c>
-      <c r="H82" s="7">
-        <f>SUM(H83,H84,H85,H86)</f>
-        <v/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" s="7">
         <f>SUM(I83,I84,I85,I86)</f>
@@ -15498,10 +15521,9 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="7">
+        <f>SUM(C83,D83,E83,F83)</f>
+        <v/>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -15556,10 +15578,9 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="7">
+        <f>SUM(C84,D84,E84,F84)</f>
+        <v/>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -15614,10 +15635,9 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="7">
+        <f>SUM(C85,D85,E85,F85)</f>
+        <v/>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -15672,10 +15692,9 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="7">
+        <f>SUM(C86,D86,E86,F86)</f>
+        <v/>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -15754,9 +15773,10 @@
         <f>SUM(G88)</f>
         <v/>
       </c>
-      <c r="H87" s="7">
-        <f>SUM(H88)</f>
-        <v/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="7">
         <f>SUM(I88)</f>
@@ -15780,10 +15800,9 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="7">
+        <f>SUM(C88,D88,E88,F88)</f>
+        <v/>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -15862,9 +15881,10 @@
         <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
-        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
-        <v/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="9">
         <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
@@ -15912,9 +15932,10 @@
         <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
-      <c r="H90" s="10">
-        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
-        <v/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I90" s="10">
         <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
@@ -15962,9 +15983,10 @@
         <f>SUM(G92,G93)</f>
         <v/>
       </c>
-      <c r="H91" s="7">
-        <f>SUM(H92,H93)</f>
-        <v/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I91" s="7">
         <f>SUM(I92,I93)</f>
@@ -15988,10 +16010,9 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="7">
+        <f>SUM(C92,D92,E92,F92)</f>
+        <v/>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -16046,10 +16067,9 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="7">
+        <f>SUM(C93,D93,E93,F93)</f>
+        <v/>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -16104,10 +16124,9 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="7">
+        <f>SUM(C94,D94,E94,F94)</f>
+        <v/>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -16186,9 +16205,10 @@
         <f>SUM(G96,G97)</f>
         <v/>
       </c>
-      <c r="H95" s="7">
-        <f>SUM(H96,H97)</f>
-        <v/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="7">
         <f>SUM(I96,I97)</f>
@@ -16212,8 +16232,9 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
-        <v>26800</v>
+      <c r="B96" s="7">
+        <f>SUM(C96,D96,E96,F96)</f>
+        <v/>
       </c>
       <c r="C96" s="7" t="n">
         <v>6700</v>
@@ -16260,10 +16281,9 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="7">
+        <f>SUM(C97,D97,E97,F97)</f>
+        <v/>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
@@ -16342,9 +16362,10 @@
         <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
-      <c r="H98" s="9">
-        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
-        <v/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="9">
         <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
@@ -16392,9 +16413,10 @@
         <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
-      <c r="H99" s="10">
-        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
-        <v/>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="10">
         <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
@@ -16601,9 +16623,10 @@
         <f>SUM(G5,G6)</f>
         <v/>
       </c>
-      <c r="H4" s="7">
-        <f>SUM(H5,H6)</f>
-        <v/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="7">
         <f>SUM(I5,I6)</f>
@@ -16627,10 +16650,9 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="7">
+        <f>SUM(C5,D5,E5,F5)</f>
+        <v/>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -16709,9 +16731,10 @@
         <f>SUM(G7,G8,G9)</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>SUM(H7,H8,H9)</f>
-        <v/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I6" s="7">
         <f>SUM(I7,I8,I9)</f>
@@ -16735,8 +16758,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>2451750.6</v>
+      <c r="B7" s="7">
+        <f>SUM(C7,D7,E7,F7)</f>
+        <v/>
       </c>
       <c r="C7" s="7" t="n">
         <v>373920.6</v>
@@ -16783,10 +16807,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="7">
+        <f>SUM(C8,D8,E8,F8)</f>
+        <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -16841,10 +16864,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="7">
+        <f>SUM(C9,D9,E9,F9)</f>
+        <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -16923,9 +16945,10 @@
         <f>SUM(G11,G12,G13,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30,G31,G32,G33,G34)</f>
         <v/>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(H11,H12,H13,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30,H31,H32,H33,H34)</f>
-        <v/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7">
         <f>SUM(I11,I12,I13,I21,I22,I23,I24,I25,I26,I27,I28,I29,I30,I31,I32,I33,I34)</f>
@@ -16949,10 +16972,9 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="7">
+        <f>SUM(C11,D11,E11,F11)</f>
+        <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -17007,10 +17029,9 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="7">
+        <f>SUM(C12,D12,E12,F12)</f>
+        <v/>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -17089,9 +17110,10 @@
         <f>SUM(G14,G15,G16,G17,G18,G19,G20)</f>
         <v/>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(H14,H15,H16,H17,H18,H19,H20)</f>
-        <v/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7">
         <f>SUM(I14,I15,I16,I17,I18,I19,I20)</f>
@@ -17115,10 +17137,9 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="7">
+        <f>SUM(C14,D14,E14,F14)</f>
+        <v/>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -17173,10 +17194,9 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="7">
+        <f>SUM(C15,D15,E15,F15)</f>
+        <v/>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -17231,10 +17251,9 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="7">
+        <f>SUM(C16,D16,E16,F16)</f>
+        <v/>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -17289,8 +17308,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>120000</v>
+      <c r="B17" s="7">
+        <f>SUM(C17,D17,E17,F17)</f>
+        <v/>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -17339,8 +17359,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>20000</v>
+      <c r="B18" s="7">
+        <f>SUM(C18,D18,E18,F18)</f>
+        <v/>
       </c>
       <c r="C18" s="7" t="n">
         <v>5000</v>
@@ -17387,10 +17408,9 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B19" s="7">
+        <f>SUM(C19,D19,E19,F19)</f>
+        <v/>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -17445,8 +17465,9 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
-        <v>30000</v>
+      <c r="B20" s="7">
+        <f>SUM(C20,D20,E20,F20)</f>
+        <v/>
       </c>
       <c r="C20" s="7" t="n">
         <v>30000</v>
@@ -17499,8 +17520,9 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>200000</v>
+      <c r="B21" s="7">
+        <f>SUM(C21,D21,E21,F21)</f>
+        <v/>
       </c>
       <c r="C21" s="7" t="n">
         <v>50000</v>
@@ -17547,8 +17569,9 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>452500</v>
+      <c r="B22" s="7">
+        <f>SUM(C22,D22,E22,F22)</f>
+        <v/>
       </c>
       <c r="C22" s="7" t="n">
         <v>62500</v>
@@ -17595,8 +17618,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
-        <v>45037.68</v>
+      <c r="B23" s="7">
+        <f>SUM(C23,D23,E23,F23)</f>
+        <v/>
       </c>
       <c r="C23" s="7" t="n">
         <v>3037.68</v>
@@ -17643,10 +17667,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="7">
+        <f>SUM(C24,D24,E24,F24)</f>
+        <v/>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -17701,10 +17724,9 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="7">
+        <f>SUM(C25,D25,E25,F25)</f>
+        <v/>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -17759,10 +17781,9 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="7">
+        <f>SUM(C26,D26,E26,F26)</f>
+        <v/>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -17817,10 +17838,9 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="7">
+        <f>SUM(C27,D27,E27,F27)</f>
+        <v/>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -17875,10 +17895,9 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="7">
+        <f>SUM(C28,D28,E28,F28)</f>
+        <v/>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -17933,10 +17952,9 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="7">
+        <f>SUM(C29,D29,E29,F29)</f>
+        <v/>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -17991,10 +18009,9 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="7">
+        <f>SUM(C30,D30,E30,F30)</f>
+        <v/>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -18049,10 +18066,9 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="7">
+        <f>SUM(C31,D31,E31,F31)</f>
+        <v/>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -18107,10 +18123,9 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="7">
+        <f>SUM(C32,D32,E32,F32)</f>
+        <v/>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -18165,10 +18180,9 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B33" s="7">
+        <f>SUM(C33,D33,E33,F33)</f>
+        <v/>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -18247,9 +18261,10 @@
         <f>SUM(G35,G36,G37,G38,G39,G40,G41,G42)</f>
         <v/>
       </c>
-      <c r="H34" s="7">
-        <f>SUM(H35,H36,H37,H38,H39,H40,H41,H42)</f>
-        <v/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" s="7">
         <f>SUM(I35,I36,I37,I38,I39,I40,I41,I42)</f>
@@ -18273,10 +18288,9 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="7">
+        <f>SUM(C35,D35,E35,F35)</f>
+        <v/>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -18331,8 +18345,9 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>120000</v>
+      <c r="B36" s="7">
+        <f>SUM(C36,D36,E36,F36)</f>
+        <v/>
       </c>
       <c r="C36" s="7" t="n">
         <v>30000</v>
@@ -18379,10 +18394,9 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="7">
+        <f>SUM(C37,D37,E37,F37)</f>
+        <v/>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
@@ -18437,10 +18451,9 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="7">
+        <f>SUM(C38,D38,E38,F38)</f>
+        <v/>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -18495,8 +18508,9 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
-        <v>39500</v>
+      <c r="B39" s="7">
+        <f>SUM(C39,D39,E39,F39)</f>
+        <v/>
       </c>
       <c r="C39" s="7" t="n">
         <v>3500</v>
@@ -18543,10 +18557,9 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="7">
+        <f>SUM(C40,D40,E40,F40)</f>
+        <v/>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -18601,8 +18614,9 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n">
-        <v>1500</v>
+      <c r="B41" s="7">
+        <f>SUM(C41,D41,E41,F41)</f>
+        <v/>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
@@ -18651,10 +18665,9 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="7">
+        <f>SUM(C42,D42,E42,F42)</f>
+        <v/>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -18733,9 +18746,10 @@
         <f>G4-G10</f>
         <v/>
       </c>
-      <c r="H43" s="9">
-        <f>H4-H10</f>
-        <v/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="9">
         <f>I4-I10</f>
@@ -18783,9 +18797,10 @@
         <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
-        <v/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="10">
         <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
@@ -18833,9 +18848,10 @@
         <f>SUM(G46,G47,G48,G52,G56,G57,G58,G59,G60,G63,G64,G65,G66,G67,G68,G69,G70,G71,G72,G73,G74,G75,G76,G77,G78,G79)</f>
         <v/>
       </c>
-      <c r="H45" s="7">
-        <f>SUM(H46,H47,H48,H52,H56,H57,H58,H59,H60,H63,H64,H65,H66,H67,H68,H69,H70,H71,H72,H73,H74,H75,H76,H77,H78,H79)</f>
-        <v/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="7">
         <f>SUM(I46,I47,I48,I52,I56,I57,I58,I59,I60,I63,I64,I65,I66,I67,I68,I69,I70,I71,I72,I73,I74,I75,I76,I77,I78,I79)</f>
@@ -18859,10 +18875,9 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="7">
+        <f>SUM(C46,D46,E46,F46)</f>
+        <v/>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
@@ -18917,10 +18932,9 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="7">
+        <f>SUM(C47,D47,E47,F47)</f>
+        <v/>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -18999,9 +19013,10 @@
         <f>SUM(G49,G50,G51)</f>
         <v/>
       </c>
-      <c r="H48" s="7">
-        <f>SUM(H49,H50,H51)</f>
-        <v/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="7">
         <f>SUM(I49,I50,I51)</f>
@@ -19025,10 +19040,9 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="7">
+        <f>SUM(C49,D49,E49,F49)</f>
+        <v/>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -19083,10 +19097,9 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="7">
+        <f>SUM(C50,D50,E50,F50)</f>
+        <v/>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -19141,10 +19154,9 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="7">
+        <f>SUM(C51,D51,E51,F51)</f>
+        <v/>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -19223,9 +19235,10 @@
         <f>SUM(G53,G54,G55)</f>
         <v/>
       </c>
-      <c r="H52" s="7">
-        <f>SUM(H53,H54,H55)</f>
-        <v/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="7">
         <f>SUM(I53,I54,I55)</f>
@@ -19249,10 +19262,9 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="7">
+        <f>SUM(C53,D53,E53,F53)</f>
+        <v/>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -19307,10 +19319,9 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="7">
+        <f>SUM(C54,D54,E54,F54)</f>
+        <v/>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -19365,10 +19376,9 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B55" s="7">
+        <f>SUM(C55,D55,E55,F55)</f>
+        <v/>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -19423,10 +19433,9 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="7">
+        <f>SUM(C56,D56,E56,F56)</f>
+        <v/>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -19481,10 +19490,9 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="7">
+        <f>SUM(C57,D57,E57,F57)</f>
+        <v/>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -19539,10 +19547,9 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="7">
+        <f>SUM(C58,D58,E58,F58)</f>
+        <v/>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -19597,10 +19604,9 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="7">
+        <f>SUM(C59,D59,E59,F59)</f>
+        <v/>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -19679,9 +19685,10 @@
         <f>SUM(G61,G62)</f>
         <v/>
       </c>
-      <c r="H60" s="7">
-        <f>SUM(H61,H62)</f>
-        <v/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="7">
         <f>SUM(I61,I62)</f>
@@ -19705,10 +19712,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="7">
+        <f>SUM(C61,D61,E61,F61)</f>
+        <v/>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -19763,10 +19769,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="7">
+        <f>SUM(C62,D62,E62,F62)</f>
+        <v/>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -19821,10 +19826,9 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="7">
+        <f>SUM(C63,D63,E63,F63)</f>
+        <v/>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -19879,10 +19883,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="7">
+        <f>SUM(C64,D64,E64,F64)</f>
+        <v/>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -19937,10 +19940,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="7">
+        <f>SUM(C65,D65,E65,F65)</f>
+        <v/>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -19995,10 +19997,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="7">
+        <f>SUM(C66,D66,E66,F66)</f>
+        <v/>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -20053,10 +20054,9 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="7">
+        <f>SUM(C67,D67,E67,F67)</f>
+        <v/>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -20111,10 +20111,9 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="7">
+        <f>SUM(C68,D68,E68,F68)</f>
+        <v/>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -20169,10 +20168,9 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="7">
+        <f>SUM(C69,D69,E69,F69)</f>
+        <v/>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -20227,10 +20225,9 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="7">
+        <f>SUM(C70,D70,E70,F70)</f>
+        <v/>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -20285,10 +20282,9 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="7">
+        <f>SUM(C71,D71,E71,F71)</f>
+        <v/>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -20343,10 +20339,9 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="7">
+        <f>SUM(C72,D72,E72,F72)</f>
+        <v/>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -20401,10 +20396,9 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="7">
+        <f>SUM(C73,D73,E73,F73)</f>
+        <v/>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -20459,10 +20453,9 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="7">
+        <f>SUM(C74,D74,E74,F74)</f>
+        <v/>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -20517,10 +20510,9 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="7">
+        <f>SUM(C75,D75,E75,F75)</f>
+        <v/>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -20575,10 +20567,9 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="7">
+        <f>SUM(C76,D76,E76,F76)</f>
+        <v/>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -20633,10 +20624,9 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="7">
+        <f>SUM(C77,D77,E77,F77)</f>
+        <v/>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -20691,10 +20681,9 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="7">
+        <f>SUM(C78,D78,E78,F78)</f>
+        <v/>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -20749,10 +20738,9 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="7">
+        <f>SUM(C79,D79,E79,F79)</f>
+        <v/>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -20831,9 +20819,10 @@
         <f>G43-G45</f>
         <v/>
       </c>
-      <c r="H80" s="9">
-        <f>H43-H45</f>
-        <v/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" s="9">
         <f>I43-I45</f>
@@ -20881,9 +20870,10 @@
         <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
-      <c r="H81" s="10">
-        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
-        <v/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" s="10">
         <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
@@ -20931,9 +20921,10 @@
         <f>SUM(G83,G84,G85,G86)</f>
         <v/>
       </c>
-      <c r="H82" s="7">
-        <f>SUM(H83,H84,H85,H86)</f>
-        <v/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" s="7">
         <f>SUM(I83,I84,I85,I86)</f>
@@ -20957,10 +20948,9 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="7">
+        <f>SUM(C83,D83,E83,F83)</f>
+        <v/>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -21015,10 +21005,9 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="7">
+        <f>SUM(C84,D84,E84,F84)</f>
+        <v/>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -21073,10 +21062,9 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="7">
+        <f>SUM(C85,D85,E85,F85)</f>
+        <v/>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -21131,10 +21119,9 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="7">
+        <f>SUM(C86,D86,E86,F86)</f>
+        <v/>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -21213,9 +21200,10 @@
         <f>SUM(G88)</f>
         <v/>
       </c>
-      <c r="H87" s="7">
-        <f>SUM(H88)</f>
-        <v/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="7">
         <f>SUM(I88)</f>
@@ -21239,10 +21227,9 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="7">
+        <f>SUM(C88,D88,E88,F88)</f>
+        <v/>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -21321,9 +21308,10 @@
         <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
-        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
-        <v/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="9">
         <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
@@ -21371,9 +21359,10 @@
         <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
-      <c r="H90" s="10">
-        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
-        <v/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I90" s="10">
         <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
@@ -21421,9 +21410,10 @@
         <f>SUM(G92,G93)</f>
         <v/>
       </c>
-      <c r="H91" s="7">
-        <f>SUM(H92,H93)</f>
-        <v/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I91" s="7">
         <f>SUM(I92,I93)</f>
@@ -21447,10 +21437,9 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="7">
+        <f>SUM(C92,D92,E92,F92)</f>
+        <v/>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -21505,8 +21494,9 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7" t="n">
-        <v>225000</v>
+      <c r="B93" s="7">
+        <f>SUM(C93,D93,E93,F93)</f>
+        <v/>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -21559,10 +21549,9 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="7">
+        <f>SUM(C94,D94,E94,F94)</f>
+        <v/>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -21641,9 +21630,10 @@
         <f>SUM(G96,G97)</f>
         <v/>
       </c>
-      <c r="H95" s="7">
-        <f>SUM(H96,H97)</f>
-        <v/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="7">
         <f>SUM(I96,I97)</f>
@@ -21667,8 +21657,9 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
-        <v>36900</v>
+      <c r="B96" s="7">
+        <f>SUM(C96,D96,E96,F96)</f>
+        <v/>
       </c>
       <c r="C96" s="7" t="n">
         <v>5700</v>
@@ -21715,8 +21706,9 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7" t="n">
-        <v>121695.74</v>
+      <c r="B97" s="7">
+        <f>SUM(C97,D97,E97,F97)</f>
+        <v/>
       </c>
       <c r="C97" s="7" t="n">
         <v>17805.74</v>
@@ -21787,9 +21779,10 @@
         <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
-      <c r="H98" s="9">
-        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
-        <v/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="9">
         <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
@@ -21837,9 +21830,10 @@
         <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
-      <c r="H99" s="10">
-        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
-        <v/>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="10">
         <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
@@ -22046,9 +22040,10 @@
         <f>SUM(G5,G6)</f>
         <v/>
       </c>
-      <c r="H4" s="7">
-        <f>SUM(H5,H6)</f>
-        <v/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="7">
         <f>SUM(I5,I6)</f>
@@ -22072,10 +22067,9 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="7">
+        <f>SUM(C5,D5,E5,F5)</f>
+        <v/>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -22154,9 +22148,10 @@
         <f>SUM(G7,G8,G9)</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>SUM(H7,H8,H9)</f>
-        <v/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I6" s="7">
         <f>SUM(I7,I8,I9)</f>
@@ -22180,8 +22175,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>2539080</v>
+      <c r="B7" s="7">
+        <f>SUM(C7,D7,E7,F7)</f>
+        <v/>
       </c>
       <c r="C7" s="7" t="n">
         <v>846360</v>
@@ -22230,10 +22226,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="7">
+        <f>SUM(C8,D8,E8,F8)</f>
+        <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -22288,10 +22283,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="7">
+        <f>SUM(C9,D9,E9,F9)</f>
+        <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -22370,9 +22364,10 @@
         <f>SUM(G11,G12,G13,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30,G31,G32,G33,G34)</f>
         <v/>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(H11,H12,H13,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30,H31,H32,H33,H34)</f>
-        <v/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7">
         <f>SUM(I11,I12,I13,I21,I22,I23,I24,I25,I26,I27,I28,I29,I30,I31,I32,I33,I34)</f>
@@ -22396,10 +22391,9 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="7">
+        <f>SUM(C11,D11,E11,F11)</f>
+        <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -22454,8 +22448,9 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
-        <v>10352</v>
+      <c r="B12" s="7">
+        <f>SUM(C12,D12,E12,F12)</f>
+        <v/>
       </c>
       <c r="C12" s="7" t="n">
         <v>10352</v>
@@ -22532,9 +22527,10 @@
         <f>SUM(G14,G15,G16,G17,G18,G19,G20)</f>
         <v/>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(H14,H15,H16,H17,H18,H19,H20)</f>
-        <v/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7">
         <f>SUM(I14,I15,I16,I17,I18,I19,I20)</f>
@@ -22558,10 +22554,9 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="7">
+        <f>SUM(C14,D14,E14,F14)</f>
+        <v/>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -22616,10 +22611,9 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="7">
+        <f>SUM(C15,D15,E15,F15)</f>
+        <v/>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -22674,10 +22668,9 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="7">
+        <f>SUM(C16,D16,E16,F16)</f>
+        <v/>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -22732,8 +22725,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>32073.9</v>
+      <c r="B17" s="7">
+        <f>SUM(C17,D17,E17,F17)</f>
+        <v/>
       </c>
       <c r="C17" s="7" t="n">
         <v>22073.9</v>
@@ -22782,8 +22776,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>18643.49</v>
+      <c r="B18" s="7">
+        <f>SUM(C18,D18,E18,F18)</f>
+        <v/>
       </c>
       <c r="C18" s="7" t="n">
         <v>8643.49</v>
@@ -22832,10 +22827,9 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B19" s="7">
+        <f>SUM(C19,D19,E19,F19)</f>
+        <v/>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -22890,10 +22884,9 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="7">
+        <f>SUM(C20,D20,E20,F20)</f>
+        <v/>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -22948,8 +22941,9 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>820000</v>
+      <c r="B21" s="7">
+        <f>SUM(C21,D21,E21,F21)</f>
+        <v/>
       </c>
       <c r="C21" s="7" t="n">
         <v>260000</v>
@@ -22998,8 +22992,9 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>810000</v>
+      <c r="B22" s="7">
+        <f>SUM(C22,D22,E22,F22)</f>
+        <v/>
       </c>
       <c r="C22" s="7" t="n">
         <v>270000</v>
@@ -23048,10 +23043,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="7">
+        <f>SUM(C23,D23,E23,F23)</f>
+        <v/>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -23106,10 +23100,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="7">
+        <f>SUM(C24,D24,E24,F24)</f>
+        <v/>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -23164,10 +23157,9 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="7">
+        <f>SUM(C25,D25,E25,F25)</f>
+        <v/>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -23222,10 +23214,9 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="7">
+        <f>SUM(C26,D26,E26,F26)</f>
+        <v/>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -23280,10 +23271,9 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="7">
+        <f>SUM(C27,D27,E27,F27)</f>
+        <v/>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -23338,10 +23328,9 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="7">
+        <f>SUM(C28,D28,E28,F28)</f>
+        <v/>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -23396,10 +23385,9 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="7">
+        <f>SUM(C29,D29,E29,F29)</f>
+        <v/>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -23454,8 +23442,9 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
-        <v>8000</v>
+      <c r="B30" s="7">
+        <f>SUM(C30,D30,E30,F30)</f>
+        <v/>
       </c>
       <c r="C30" s="7" t="n">
         <v>2000</v>
@@ -23504,8 +23493,9 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n">
-        <v>7920</v>
+      <c r="B31" s="7">
+        <f>SUM(C31,D31,E31,F31)</f>
+        <v/>
       </c>
       <c r="C31" s="7" t="n">
         <v>7920</v>
@@ -23558,10 +23548,9 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="7">
+        <f>SUM(C32,D32,E32,F32)</f>
+        <v/>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -23616,10 +23605,9 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B33" s="7">
+        <f>SUM(C33,D33,E33,F33)</f>
+        <v/>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -23698,9 +23686,10 @@
         <f>SUM(G35,G36,G37,G38,G39,G40,G41,G42)</f>
         <v/>
       </c>
-      <c r="H34" s="7">
-        <f>SUM(H35,H36,H37,H38,H39,H40,H41,H42)</f>
-        <v/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" s="7">
         <f>SUM(I35,I36,I37,I38,I39,I40,I41,I42)</f>
@@ -23724,8 +23713,9 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n">
-        <v>12500</v>
+      <c r="B35" s="7">
+        <f>SUM(C35,D35,E35,F35)</f>
+        <v/>
       </c>
       <c r="C35" s="7" t="n">
         <v>7500</v>
@@ -23774,8 +23764,9 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>195000</v>
+      <c r="B36" s="7">
+        <f>SUM(C36,D36,E36,F36)</f>
+        <v/>
       </c>
       <c r="C36" s="7" t="n">
         <v>65000</v>
@@ -23824,8 +23815,9 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
-        <v>8620</v>
+      <c r="B37" s="7">
+        <f>SUM(C37,D37,E37,F37)</f>
+        <v/>
       </c>
       <c r="C37" s="7" t="n">
         <v>2620</v>
@@ -23874,10 +23866,9 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="7">
+        <f>SUM(C38,D38,E38,F38)</f>
+        <v/>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -23932,8 +23923,9 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
-        <v>159000</v>
+      <c r="B39" s="7">
+        <f>SUM(C39,D39,E39,F39)</f>
+        <v/>
       </c>
       <c r="C39" s="7" t="n">
         <v>53000</v>
@@ -23982,10 +23974,9 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="7">
+        <f>SUM(C40,D40,E40,F40)</f>
+        <v/>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -24040,8 +24031,9 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n">
-        <v>6000</v>
+      <c r="B41" s="7">
+        <f>SUM(C41,D41,E41,F41)</f>
+        <v/>
       </c>
       <c r="C41" s="7" t="n">
         <v>2000</v>
@@ -24090,10 +24082,9 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="7">
+        <f>SUM(C42,D42,E42,F42)</f>
+        <v/>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -24172,9 +24163,10 @@
         <f>G4-G10</f>
         <v/>
       </c>
-      <c r="H43" s="9">
-        <f>H4-H10</f>
-        <v/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="9">
         <f>I4-I10</f>
@@ -24222,9 +24214,10 @@
         <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
-        <v/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="10">
         <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
@@ -24272,9 +24265,10 @@
         <f>SUM(G46,G47,G48,G52,G56,G57,G58,G59,G60,G63,G64,G65,G66,G67,G68,G69,G70,G71,G72,G73,G74,G75,G76,G77,G78,G79)</f>
         <v/>
       </c>
-      <c r="H45" s="7">
-        <f>SUM(H46,H47,H48,H52,H56,H57,H58,H59,H60,H63,H64,H65,H66,H67,H68,H69,H70,H71,H72,H73,H74,H75,H76,H77,H78,H79)</f>
-        <v/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="7">
         <f>SUM(I46,I47,I48,I52,I56,I57,I58,I59,I60,I63,I64,I65,I66,I67,I68,I69,I70,I71,I72,I73,I74,I75,I76,I77,I78,I79)</f>
@@ -24298,10 +24292,9 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="7">
+        <f>SUM(C46,D46,E46,F46)</f>
+        <v/>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
@@ -24356,10 +24349,9 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="7">
+        <f>SUM(C47,D47,E47,F47)</f>
+        <v/>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -24438,9 +24430,10 @@
         <f>SUM(G49,G50,G51)</f>
         <v/>
       </c>
-      <c r="H48" s="7">
-        <f>SUM(H49,H50,H51)</f>
-        <v/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="7">
         <f>SUM(I49,I50,I51)</f>
@@ -24464,10 +24457,9 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="7">
+        <f>SUM(C49,D49,E49,F49)</f>
+        <v/>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -24522,10 +24514,9 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="7">
+        <f>SUM(C50,D50,E50,F50)</f>
+        <v/>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -24580,10 +24571,9 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="7">
+        <f>SUM(C51,D51,E51,F51)</f>
+        <v/>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -24662,9 +24652,10 @@
         <f>SUM(G53,G54,G55)</f>
         <v/>
       </c>
-      <c r="H52" s="7">
-        <f>SUM(H53,H54,H55)</f>
-        <v/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="7">
         <f>SUM(I53,I54,I55)</f>
@@ -24688,10 +24679,9 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="7">
+        <f>SUM(C53,D53,E53,F53)</f>
+        <v/>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -24746,10 +24736,9 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="7">
+        <f>SUM(C54,D54,E54,F54)</f>
+        <v/>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -24804,10 +24793,9 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B55" s="7">
+        <f>SUM(C55,D55,E55,F55)</f>
+        <v/>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -24862,10 +24850,9 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="7">
+        <f>SUM(C56,D56,E56,F56)</f>
+        <v/>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -24920,10 +24907,9 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="7">
+        <f>SUM(C57,D57,E57,F57)</f>
+        <v/>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -24978,10 +24964,9 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="7">
+        <f>SUM(C58,D58,E58,F58)</f>
+        <v/>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -25036,10 +25021,9 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="7">
+        <f>SUM(C59,D59,E59,F59)</f>
+        <v/>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -25118,9 +25102,10 @@
         <f>SUM(G61,G62)</f>
         <v/>
       </c>
-      <c r="H60" s="7">
-        <f>SUM(H61,H62)</f>
-        <v/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="7">
         <f>SUM(I61,I62)</f>
@@ -25144,10 +25129,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="7">
+        <f>SUM(C61,D61,E61,F61)</f>
+        <v/>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -25202,10 +25186,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="7">
+        <f>SUM(C62,D62,E62,F62)</f>
+        <v/>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -25260,10 +25243,9 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="7">
+        <f>SUM(C63,D63,E63,F63)</f>
+        <v/>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -25318,10 +25300,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="7">
+        <f>SUM(C64,D64,E64,F64)</f>
+        <v/>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -25376,10 +25357,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="7">
+        <f>SUM(C65,D65,E65,F65)</f>
+        <v/>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -25434,10 +25414,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="7">
+        <f>SUM(C66,D66,E66,F66)</f>
+        <v/>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -25492,10 +25471,9 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="7">
+        <f>SUM(C67,D67,E67,F67)</f>
+        <v/>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -25550,10 +25528,9 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="7">
+        <f>SUM(C68,D68,E68,F68)</f>
+        <v/>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -25608,10 +25585,9 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="7">
+        <f>SUM(C69,D69,E69,F69)</f>
+        <v/>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -25666,10 +25642,9 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="7">
+        <f>SUM(C70,D70,E70,F70)</f>
+        <v/>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -25724,10 +25699,9 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="7">
+        <f>SUM(C71,D71,E71,F71)</f>
+        <v/>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -25782,10 +25756,9 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="7">
+        <f>SUM(C72,D72,E72,F72)</f>
+        <v/>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -25840,10 +25813,9 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="7">
+        <f>SUM(C73,D73,E73,F73)</f>
+        <v/>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -25898,10 +25870,9 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="7">
+        <f>SUM(C74,D74,E74,F74)</f>
+        <v/>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -25956,10 +25927,9 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="7">
+        <f>SUM(C75,D75,E75,F75)</f>
+        <v/>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -26014,10 +25984,9 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="7">
+        <f>SUM(C76,D76,E76,F76)</f>
+        <v/>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -26072,10 +26041,9 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="7">
+        <f>SUM(C77,D77,E77,F77)</f>
+        <v/>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -26130,10 +26098,9 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="7">
+        <f>SUM(C78,D78,E78,F78)</f>
+        <v/>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -26188,10 +26155,9 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="7">
+        <f>SUM(C79,D79,E79,F79)</f>
+        <v/>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -26270,9 +26236,10 @@
         <f>G43-G45</f>
         <v/>
       </c>
-      <c r="H80" s="9">
-        <f>H43-H45</f>
-        <v/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" s="9">
         <f>I43-I45</f>
@@ -26320,9 +26287,10 @@
         <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
-      <c r="H81" s="10">
-        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
-        <v/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" s="10">
         <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
@@ -26370,9 +26338,10 @@
         <f>SUM(G83,G84,G85,G86)</f>
         <v/>
       </c>
-      <c r="H82" s="7">
-        <f>SUM(H83,H84,H85,H86)</f>
-        <v/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" s="7">
         <f>SUM(I83,I84,I85,I86)</f>
@@ -26396,10 +26365,9 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="7">
+        <f>SUM(C83,D83,E83,F83)</f>
+        <v/>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -26454,10 +26422,9 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="7">
+        <f>SUM(C84,D84,E84,F84)</f>
+        <v/>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -26512,10 +26479,9 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="7">
+        <f>SUM(C85,D85,E85,F85)</f>
+        <v/>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -26570,10 +26536,9 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="7">
+        <f>SUM(C86,D86,E86,F86)</f>
+        <v/>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -26652,9 +26617,10 @@
         <f>SUM(G88)</f>
         <v/>
       </c>
-      <c r="H87" s="7">
-        <f>SUM(H88)</f>
-        <v/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="7">
         <f>SUM(I88)</f>
@@ -26678,10 +26644,9 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="7">
+        <f>SUM(C88,D88,E88,F88)</f>
+        <v/>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -26760,9 +26725,10 @@
         <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
-        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
-        <v/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="9">
         <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
@@ -26810,9 +26776,10 @@
         <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
-      <c r="H90" s="10">
-        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
-        <v/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I90" s="10">
         <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
@@ -26860,9 +26827,10 @@
         <f>SUM(G92,G93)</f>
         <v/>
       </c>
-      <c r="H91" s="7">
-        <f>SUM(H92,H93)</f>
-        <v/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I91" s="7">
         <f>SUM(I92,I93)</f>
@@ -26886,10 +26854,9 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="7">
+        <f>SUM(C92,D92,E92,F92)</f>
+        <v/>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -26944,10 +26911,9 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="7">
+        <f>SUM(C93,D93,E93,F93)</f>
+        <v/>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -27002,10 +26968,9 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="7">
+        <f>SUM(C94,D94,E94,F94)</f>
+        <v/>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -27084,9 +27049,10 @@
         <f>SUM(G96,G97)</f>
         <v/>
       </c>
-      <c r="H95" s="7">
-        <f>SUM(H96,H97)</f>
-        <v/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="7">
         <f>SUM(I96,I97)</f>
@@ -27110,8 +27076,9 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
-        <v>36000</v>
+      <c r="B96" s="7">
+        <f>SUM(C96,D96,E96,F96)</f>
+        <v/>
       </c>
       <c r="C96" s="7" t="n">
         <v>12000</v>
@@ -27160,8 +27127,9 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7" t="n">
-        <v>156000</v>
+      <c r="B97" s="7">
+        <f>SUM(C97,D97,E97,F97)</f>
+        <v/>
       </c>
       <c r="C97" s="7" t="n">
         <v>52000</v>
@@ -27234,9 +27202,10 @@
         <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
-      <c r="H98" s="9">
-        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
-        <v/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="9">
         <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
@@ -27284,9 +27253,10 @@
         <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
-      <c r="H99" s="10">
-        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
-        <v/>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="10">
         <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>

--- a/budget/output/Сводный бюджет СПб.xlsx
+++ b/budget/output/Сводный бюджет СПб.xlsx
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>SUM(C5,D5,E5,F5)</f>
+        <f>SUM('Астон.Движение'!B5,'Астон.Реформа'!B5,'Милый дом'!B5,'River Park'!B5)</f>
         <v/>
       </c>
       <c r="C5" s="7">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>SUM(C7,D7,E7,F7)</f>
+        <f>SUM('Астон.Движение'!B7,'Астон.Реформа'!B7,'Милый дом'!B7,'River Park'!B7)</f>
         <v/>
       </c>
       <c r="C7" s="7">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>SUM(C8,D8,E8,F8)</f>
+        <f>SUM('Астон.Движение'!B8,'Астон.Реформа'!B8,'Милый дом'!B8,'River Park'!B8)</f>
         <v/>
       </c>
       <c r="C8" s="7">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>SUM(C9,D9,E9,F9)</f>
+        <f>SUM('Астон.Движение'!B9,'Астон.Реформа'!B9,'Милый дом'!B9,'River Park'!B9)</f>
         <v/>
       </c>
       <c r="C9" s="7">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>SUM(C11,D11,E11,F11)</f>
+        <f>SUM('Астон.Движение'!B11,'Астон.Реформа'!B11,'Милый дом'!B11,'River Park'!B11)</f>
         <v/>
       </c>
       <c r="C11" s="7">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>SUM(C12,D12,E12,F12)</f>
+        <f>SUM('Астон.Движение'!B12,'Астон.Реформа'!B12,'Милый дом'!B12,'River Park'!B12)</f>
         <v/>
       </c>
       <c r="C12" s="7">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>SUM(C14,D14,E14,F14)</f>
+        <f>SUM('Астон.Движение'!B14,'Астон.Реформа'!B14,'Милый дом'!B14,'River Park'!B14)</f>
         <v/>
       </c>
       <c r="C14" s="7">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B15" s="7">
-        <f>SUM(C15,D15,E15,F15)</f>
+        <f>SUM('Астон.Движение'!B15,'Астон.Реформа'!B15,'Милый дом'!B15,'River Park'!B15)</f>
         <v/>
       </c>
       <c r="C15" s="7">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="B16" s="7">
-        <f>SUM(C16,D16,E16,F16)</f>
+        <f>SUM('Астон.Движение'!B16,'Астон.Реформа'!B16,'Милый дом'!B16,'River Park'!B16)</f>
         <v/>
       </c>
       <c r="C16" s="7">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="B17" s="7">
-        <f>SUM(C17,D17,E17,F17)</f>
+        <f>SUM('Астон.Движение'!B17,'Астон.Реформа'!B17,'Милый дом'!B17,'River Park'!B17)</f>
         <v/>
       </c>
       <c r="C17" s="7">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM(C18,D18,E18,F18)</f>
+        <f>SUM('Астон.Движение'!B18,'Астон.Реформа'!B18,'Милый дом'!B18,'River Park'!B18)</f>
         <v/>
       </c>
       <c r="C18" s="7">
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM(C19,D19,E19,F19)</f>
+        <f>SUM('Астон.Движение'!B19,'Астон.Реформа'!B19,'Милый дом'!B19,'River Park'!B19)</f>
         <v/>
       </c>
       <c r="C19" s="7">
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>SUM(C20,D20,E20,F20)</f>
+        <f>SUM('Астон.Движение'!B20,'Астон.Реформа'!B20,'Милый дом'!B20,'River Park'!B20)</f>
         <v/>
       </c>
       <c r="C20" s="7">
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="B21" s="7">
-        <f>SUM(C21,D21,E21,F21)</f>
+        <f>SUM('Астон.Движение'!B21,'Астон.Реформа'!B21,'Милый дом'!B21,'River Park'!B21)</f>
         <v/>
       </c>
       <c r="C21" s="7">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B22" s="7">
-        <f>SUM(C22,D22,E22,F22)</f>
+        <f>SUM('Астон.Движение'!B22,'Астон.Реформа'!B22,'Милый дом'!B22,'River Park'!B22)</f>
         <v/>
       </c>
       <c r="C22" s="7">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="B23" s="7">
-        <f>SUM(C23,D23,E23,F23)</f>
+        <f>SUM('Астон.Движение'!B23,'Астон.Реформа'!B23,'Милый дом'!B23,'River Park'!B23)</f>
         <v/>
       </c>
       <c r="C23" s="7">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>SUM(C24,D24,E24,F24)</f>
+        <f>SUM('Астон.Движение'!B24,'Астон.Реформа'!B24,'Милый дом'!B24,'River Park'!B24)</f>
         <v/>
       </c>
       <c r="C24" s="7">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>SUM(C25,D25,E25,F25)</f>
+        <f>SUM('Астон.Движение'!B25,'Астон.Реформа'!B25,'Милый дом'!B25,'River Park'!B25)</f>
         <v/>
       </c>
       <c r="C25" s="7">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>SUM(C26,D26,E26,F26)</f>
+        <f>SUM('Астон.Движение'!B26,'Астон.Реформа'!B26,'Милый дом'!B26,'River Park'!B26)</f>
         <v/>
       </c>
       <c r="C26" s="7">
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>SUM(C27,D27,E27,F27)</f>
+        <f>SUM('Астон.Движение'!B27,'Астон.Реформа'!B27,'Милый дом'!B27,'River Park'!B27)</f>
         <v/>
       </c>
       <c r="C27" s="7">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="B28" s="7">
-        <f>SUM(C28,D28,E28,F28)</f>
+        <f>SUM('Астон.Движение'!B28,'Астон.Реформа'!B28,'Милый дом'!B28,'River Park'!B28)</f>
         <v/>
       </c>
       <c r="C28" s="7">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="B29" s="7">
-        <f>SUM(C29,D29,E29,F29)</f>
+        <f>SUM('Астон.Движение'!B29,'Астон.Реформа'!B29,'Милый дом'!B29,'River Park'!B29)</f>
         <v/>
       </c>
       <c r="C29" s="7">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="B30" s="7">
-        <f>SUM(C30,D30,E30,F30)</f>
+        <f>SUM('Астон.Движение'!B30,'Астон.Реформа'!B30,'Милый дом'!B30,'River Park'!B30)</f>
         <v/>
       </c>
       <c r="C30" s="7">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="B31" s="7">
-        <f>SUM(C31,D31,E31,F31)</f>
+        <f>SUM('Астон.Движение'!B31,'Астон.Реформа'!B31,'Милый дом'!B31,'River Park'!B31)</f>
         <v/>
       </c>
       <c r="C31" s="7">
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="B32" s="7">
-        <f>SUM(C32,D32,E32,F32)</f>
+        <f>SUM('Астон.Движение'!B32,'Астон.Реформа'!B32,'Милый дом'!B32,'River Park'!B32)</f>
         <v/>
       </c>
       <c r="C32" s="7">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>SUM(C33,D33,E33,F33)</f>
+        <f>SUM('Астон.Движение'!B33,'Астон.Реформа'!B33,'Милый дом'!B33,'River Park'!B33)</f>
         <v/>
       </c>
       <c r="C33" s="7">
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>SUM(C35,D35,E35,F35)</f>
+        <f>SUM('Астон.Движение'!B35,'Астон.Реформа'!B35,'Милый дом'!B35,'River Park'!B35)</f>
         <v/>
       </c>
       <c r="C35" s="7">
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>SUM(C36,D36,E36,F36)</f>
+        <f>SUM('Астон.Движение'!B36,'Астон.Реформа'!B36,'Милый дом'!B36,'River Park'!B36)</f>
         <v/>
       </c>
       <c r="C36" s="7">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>SUM(C37,D37,E37,F37)</f>
+        <f>SUM('Астон.Движение'!B37,'Астон.Реформа'!B37,'Милый дом'!B37,'River Park'!B37)</f>
         <v/>
       </c>
       <c r="C37" s="7">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>SUM(C38,D38,E38,F38)</f>
+        <f>SUM('Астон.Движение'!B38,'Астон.Реформа'!B38,'Милый дом'!B38,'River Park'!B38)</f>
         <v/>
       </c>
       <c r="C38" s="7">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>SUM(C39,D39,E39,F39)</f>
+        <f>SUM('Астон.Движение'!B39,'Астон.Реформа'!B39,'Милый дом'!B39,'River Park'!B39)</f>
         <v/>
       </c>
       <c r="C39" s="7">
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>SUM(C40,D40,E40,F40)</f>
+        <f>SUM('Астон.Движение'!B40,'Астон.Реформа'!B40,'Милый дом'!B40,'River Park'!B40)</f>
         <v/>
       </c>
       <c r="C40" s="7">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>SUM(C41,D41,E41,F41)</f>
+        <f>SUM('Астон.Движение'!B41,'Астон.Реформа'!B41,'Милый дом'!B41,'River Park'!B41)</f>
         <v/>
       </c>
       <c r="C41" s="7">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>SUM(C42,D42,E42,F42)</f>
+        <f>SUM('Астон.Движение'!B42,'Астон.Реформа'!B42,'Милый дом'!B42,'River Park'!B42)</f>
         <v/>
       </c>
       <c r="C42" s="7">
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>SUM(C46,D46,E46,F46)</f>
+        <f>SUM('Астон.Движение'!B46,'Астон.Реформа'!B46,'Милый дом'!B46,'River Park'!B46)</f>
         <v/>
       </c>
       <c r="C46" s="7">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>SUM(C47,D47,E47,F47)</f>
+        <f>SUM('Астон.Движение'!B47,'Астон.Реформа'!B47,'Милый дом'!B47,'River Park'!B47)</f>
         <v/>
       </c>
       <c r="C47" s="7">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>SUM(C49,D49,E49,F49)</f>
+        <f>SUM('Астон.Движение'!B49,'Астон.Реформа'!B49,'Милый дом'!B49,'River Park'!B49)</f>
         <v/>
       </c>
       <c r="C49" s="7">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>SUM(C50,D50,E50,F50)</f>
+        <f>SUM('Астон.Движение'!B50,'Астон.Реформа'!B50,'Милый дом'!B50,'River Park'!B50)</f>
         <v/>
       </c>
       <c r="C50" s="7">
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>SUM(C51,D51,E51,F51)</f>
+        <f>SUM('Астон.Движение'!B51,'Астон.Реформа'!B51,'Милый дом'!B51,'River Park'!B51)</f>
         <v/>
       </c>
       <c r="C51" s="7">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="B53" s="7">
-        <f>SUM(C53,D53,E53,F53)</f>
+        <f>SUM('Астон.Движение'!B53,'Астон.Реформа'!B53,'Милый дом'!B53,'River Park'!B53)</f>
         <v/>
       </c>
       <c r="C53" s="7">
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="B54" s="7">
-        <f>SUM(C54,D54,E54,F54)</f>
+        <f>SUM('Астон.Движение'!B54,'Астон.Реформа'!B54,'Милый дом'!B54,'River Park'!B54)</f>
         <v/>
       </c>
       <c r="C54" s="7">
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="B55" s="7">
-        <f>SUM(C55,D55,E55,F55)</f>
+        <f>SUM('Астон.Движение'!B55,'Астон.Реформа'!B55,'Милый дом'!B55,'River Park'!B55)</f>
         <v/>
       </c>
       <c r="C55" s="7">
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="B56" s="7">
-        <f>SUM(C56,D56,E56,F56)</f>
+        <f>SUM('Астон.Движение'!B56,'Астон.Реформа'!B56,'Милый дом'!B56,'River Park'!B56)</f>
         <v/>
       </c>
       <c r="C56" s="7">
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="B57" s="7">
-        <f>SUM(C57,D57,E57,F57)</f>
+        <f>SUM('Астон.Движение'!B57,'Астон.Реформа'!B57,'Милый дом'!B57,'River Park'!B57)</f>
         <v/>
       </c>
       <c r="C57" s="7">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="B58" s="7">
-        <f>SUM(C58,D58,E58,F58)</f>
+        <f>SUM('Астон.Движение'!B58,'Астон.Реформа'!B58,'Милый дом'!B58,'River Park'!B58)</f>
         <v/>
       </c>
       <c r="C58" s="7">
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="B59" s="7">
-        <f>SUM(C59,D59,E59,F59)</f>
+        <f>SUM('Астон.Движение'!B59,'Астон.Реформа'!B59,'Милый дом'!B59,'River Park'!B59)</f>
         <v/>
       </c>
       <c r="C59" s="7">
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="B61" s="7">
-        <f>SUM(C61,D61,E61,F61)</f>
+        <f>SUM('Астон.Движение'!B61,'Астон.Реформа'!B61,'Милый дом'!B61,'River Park'!B61)</f>
         <v/>
       </c>
       <c r="C61" s="7">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="B62" s="7">
-        <f>SUM(C62,D62,E62,F62)</f>
+        <f>SUM('Астон.Движение'!B62,'Астон.Реформа'!B62,'Милый дом'!B62,'River Park'!B62)</f>
         <v/>
       </c>
       <c r="C62" s="7">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="B63" s="7">
-        <f>SUM(C63,D63,E63,F63)</f>
+        <f>SUM('Астон.Движение'!B63,'Астон.Реформа'!B63,'Милый дом'!B63,'River Park'!B63)</f>
         <v/>
       </c>
       <c r="C63" s="7">
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="B64" s="7">
-        <f>SUM(C64,D64,E64,F64)</f>
+        <f>SUM('Астон.Движение'!B64,'Астон.Реформа'!B64,'Милый дом'!B64,'River Park'!B64)</f>
         <v/>
       </c>
       <c r="C64" s="7">
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="B65" s="7">
-        <f>SUM(C65,D65,E65,F65)</f>
+        <f>SUM('Астон.Движение'!B65,'Астон.Реформа'!B65,'Милый дом'!B65,'River Park'!B65)</f>
         <v/>
       </c>
       <c r="C65" s="7">
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="B66" s="7">
-        <f>SUM(C66,D66,E66,F66)</f>
+        <f>SUM('Астон.Движение'!B66,'Астон.Реформа'!B66,'Милый дом'!B66,'River Park'!B66)</f>
         <v/>
       </c>
       <c r="C66" s="7">
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="B67" s="7">
-        <f>SUM(C67,D67,E67,F67)</f>
+        <f>SUM('Астон.Движение'!B67,'Астон.Реформа'!B67,'Милый дом'!B67,'River Park'!B67)</f>
         <v/>
       </c>
       <c r="C67" s="7">
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="B68" s="7">
-        <f>SUM(C68,D68,E68,F68)</f>
+        <f>SUM('Астон.Движение'!B68,'Астон.Реформа'!B68,'Милый дом'!B68,'River Park'!B68)</f>
         <v/>
       </c>
       <c r="C68" s="7">
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B69" s="7">
-        <f>SUM(C69,D69,E69,F69)</f>
+        <f>SUM('Астон.Движение'!B69,'Астон.Реформа'!B69,'Милый дом'!B69,'River Park'!B69)</f>
         <v/>
       </c>
       <c r="C69" s="7">
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="B70" s="7">
-        <f>SUM(C70,D70,E70,F70)</f>
+        <f>SUM('Астон.Движение'!B70,'Астон.Реформа'!B70,'Милый дом'!B70,'River Park'!B70)</f>
         <v/>
       </c>
       <c r="C70" s="7">
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="B71" s="7">
-        <f>SUM(C71,D71,E71,F71)</f>
+        <f>SUM('Астон.Движение'!B71,'Астон.Реформа'!B71,'Милый дом'!B71,'River Park'!B71)</f>
         <v/>
       </c>
       <c r="C71" s="7">
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="B72" s="7">
-        <f>SUM(C72,D72,E72,F72)</f>
+        <f>SUM('Астон.Движение'!B72,'Астон.Реформа'!B72,'Милый дом'!B72,'River Park'!B72)</f>
         <v/>
       </c>
       <c r="C72" s="7">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="B73" s="7">
-        <f>SUM(C73,D73,E73,F73)</f>
+        <f>SUM('Астон.Движение'!B73,'Астон.Реформа'!B73,'Милый дом'!B73,'River Park'!B73)</f>
         <v/>
       </c>
       <c r="C73" s="7">
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="B74" s="7">
-        <f>SUM(C74,D74,E74,F74)</f>
+        <f>SUM('Астон.Движение'!B74,'Астон.Реформа'!B74,'Милый дом'!B74,'River Park'!B74)</f>
         <v/>
       </c>
       <c r="C74" s="7">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="B75" s="7">
-        <f>SUM(C75,D75,E75,F75)</f>
+        <f>SUM('Астон.Движение'!B75,'Астон.Реформа'!B75,'Милый дом'!B75,'River Park'!B75)</f>
         <v/>
       </c>
       <c r="C75" s="7">
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="B76" s="7">
-        <f>SUM(C76,D76,E76,F76)</f>
+        <f>SUM('Астон.Движение'!B76,'Астон.Реформа'!B76,'Милый дом'!B76,'River Park'!B76)</f>
         <v/>
       </c>
       <c r="C76" s="7">
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="B77" s="7">
-        <f>SUM(C77,D77,E77,F77)</f>
+        <f>SUM('Астон.Движение'!B77,'Астон.Реформа'!B77,'Милый дом'!B77,'River Park'!B77)</f>
         <v/>
       </c>
       <c r="C77" s="7">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="B78" s="7">
-        <f>SUM(C78,D78,E78,F78)</f>
+        <f>SUM('Астон.Движение'!B78,'Астон.Реформа'!B78,'Милый дом'!B78,'River Park'!B78)</f>
         <v/>
       </c>
       <c r="C78" s="7">
@@ -4482,7 +4482,7 @@
         </is>
       </c>
       <c r="B79" s="7">
-        <f>SUM(C79,D79,E79,F79)</f>
+        <f>SUM('Астон.Движение'!B79,'Астон.Реформа'!B79,'Милый дом'!B79,'River Park'!B79)</f>
         <v/>
       </c>
       <c r="C79" s="7">
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="B83" s="7">
-        <f>SUM(C83,D83,E83,F83)</f>
+        <f>SUM('Астон.Движение'!B83,'Астон.Реформа'!B83,'Милый дом'!B83,'River Park'!B83)</f>
         <v/>
       </c>
       <c r="C83" s="7">
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="B84" s="7">
-        <f>SUM(C84,D84,E84,F84)</f>
+        <f>SUM('Астон.Движение'!B84,'Астон.Реформа'!B84,'Милый дом'!B84,'River Park'!B84)</f>
         <v/>
       </c>
       <c r="C84" s="7">
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="B85" s="7">
-        <f>SUM(C85,D85,E85,F85)</f>
+        <f>SUM('Астон.Движение'!B85,'Астон.Реформа'!B85,'Милый дом'!B85,'River Park'!B85)</f>
         <v/>
       </c>
       <c r="C85" s="7">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="B86" s="7">
-        <f>SUM(C86,D86,E86,F86)</f>
+        <f>SUM('Астон.Движение'!B86,'Астон.Реформа'!B86,'Милый дом'!B86,'River Park'!B86)</f>
         <v/>
       </c>
       <c r="C86" s="7">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="B88" s="7">
-        <f>SUM(C88,D88,E88,F88)</f>
+        <f>SUM('Астон.Движение'!B88,'Астон.Реформа'!B88,'Милый дом'!B88,'River Park'!B88)</f>
         <v/>
       </c>
       <c r="C88" s="7">
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="B92" s="7">
-        <f>SUM(C92,D92,E92,F92)</f>
+        <f>SUM('Астон.Движение'!B92,'Астон.Реформа'!B92,'Милый дом'!B92,'River Park'!B92)</f>
         <v/>
       </c>
       <c r="C92" s="7">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="B93" s="7">
-        <f>SUM(C93,D93,E93,F93)</f>
+        <f>SUM('Астон.Движение'!B93,'Астон.Реформа'!B93,'Милый дом'!B93,'River Park'!B93)</f>
         <v/>
       </c>
       <c r="C93" s="7">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="B94" s="7">
-        <f>SUM(C94,D94,E94,F94)</f>
+        <f>SUM('Астон.Движение'!B94,'Астон.Реформа'!B94,'Милый дом'!B94,'River Park'!B94)</f>
         <v/>
       </c>
       <c r="C94" s="7">
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="B96" s="7">
-        <f>SUM(C96,D96,E96,F96)</f>
+        <f>SUM('Астон.Движение'!B96,'Астон.Реформа'!B96,'Милый дом'!B96,'River Park'!B96)</f>
         <v/>
       </c>
       <c r="C96" s="7">
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="B97" s="7">
-        <f>SUM(C97,D97,E97,F97)</f>
+        <f>SUM('Астон.Движение'!B97,'Астон.Реформа'!B97,'Милый дом'!B97,'River Park'!B97)</f>
         <v/>
       </c>
       <c r="C97" s="7">
@@ -5711,9 +5711,8 @@
           <t>Выручка</t>
         </is>
       </c>
-      <c r="B4" s="7">
-        <f>SUM(B5,B6)</f>
-        <v/>
+      <c r="B4" s="7" t="n">
+        <v>656000</v>
       </c>
       <c r="C4" s="7">
         <f>SUM(C5,C6)</f>
@@ -5762,9 +5761,10 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7">
-        <f>SUM(C5,D5,E5,F5)</f>
-        <v/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -5819,9 +5819,8 @@
           <t xml:space="preserve">    Выручка </t>
         </is>
       </c>
-      <c r="B6" s="7">
-        <f>SUM(B7,B8,B9)</f>
-        <v/>
+      <c r="B6" s="7" t="n">
+        <v>656000</v>
       </c>
       <c r="C6" s="7">
         <f>SUM(C7,C8,C9)</f>
@@ -5870,9 +5869,8 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7">
-        <f>SUM(C7,D7,E7,F7)</f>
-        <v/>
+      <c r="B7" s="7" t="n">
+        <v>656000</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>164000</v>
@@ -5919,9 +5917,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7">
-        <f>SUM(C8,D8,E8,F8)</f>
-        <v/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -5976,9 +5975,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7">
-        <f>SUM(C9,D9,E9,F9)</f>
-        <v/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -6033,9 +6033,8 @@
           <t>Прямые расходы</t>
         </is>
       </c>
-      <c r="B10" s="7">
-        <f>SUM(B11,B12,B13,B21,B22,B23,B24,B25,B26,B27,B28,B29,B30,B31,B32,B33,B34)</f>
-        <v/>
+      <c r="B10" s="7" t="n">
+        <v>530680.45</v>
       </c>
       <c r="C10" s="7">
         <f>SUM(C11,C12,C13,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34)</f>
@@ -6084,9 +6083,10 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7">
-        <f>SUM(C11,D11,E11,F11)</f>
-        <v/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -6141,9 +6141,8 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7">
-        <f>SUM(C12,D12,E12,F12)</f>
-        <v/>
+      <c r="B12" s="7" t="n">
+        <v>1486</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>1486</v>
@@ -6196,9 +6195,8 @@
           <t xml:space="preserve">    Переменные</t>
         </is>
       </c>
-      <c r="B13" s="7">
-        <f>SUM(B14,B15,B16,B17,B18,B19,B20)</f>
-        <v/>
+      <c r="B13" s="7" t="n">
+        <v>15262</v>
       </c>
       <c r="C13" s="7">
         <f>SUM(C14,C15,C16,C17,C18,C19,C20)</f>
@@ -6247,9 +6245,10 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7">
-        <f>SUM(C14,D14,E14,F14)</f>
-        <v/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -6304,9 +6303,10 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(C15,D15,E15,F15)</f>
-        <v/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -6361,9 +6361,10 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(C16,D16,E16,F16)</f>
-        <v/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -6418,9 +6419,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7">
-        <f>SUM(C17,D17,E17,F17)</f>
-        <v/>
+      <c r="B17" s="7" t="n">
+        <v>8000</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>2000</v>
@@ -6467,9 +6467,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>SUM(C18,D18,E18,F18)</f>
-        <v/>
+      <c r="B18" s="7" t="n">
+        <v>7262</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>1262</v>
@@ -6516,9 +6515,10 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>SUM(C19,D19,E19,F19)</f>
-        <v/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -6573,9 +6573,10 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>SUM(C20,D20,E20,F20)</f>
-        <v/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -6630,9 +6631,8 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>SUM(C21,D21,E21,F21)</f>
-        <v/>
+      <c r="B21" s="7" t="n">
+        <v>200000</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>50000</v>
@@ -6679,9 +6679,8 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>SUM(C22,D22,E22,F22)</f>
-        <v/>
+      <c r="B22" s="7" t="n">
+        <v>280000</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>70000</v>
@@ -6728,9 +6727,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>SUM(C23,D23,E23,F23)</f>
-        <v/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -6785,9 +6785,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>SUM(C24,D24,E24,F24)</f>
-        <v/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -6842,9 +6843,10 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>SUM(C25,D25,E25,F25)</f>
-        <v/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -6899,9 +6901,10 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>SUM(C26,D26,E26,F26)</f>
-        <v/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -6956,9 +6959,10 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7">
-        <f>SUM(C27,D27,E27,F27)</f>
-        <v/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -7013,9 +7017,10 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7">
-        <f>SUM(C28,D28,E28,F28)</f>
-        <v/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -7070,9 +7075,10 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7">
-        <f>SUM(C29,D29,E29,F29)</f>
-        <v/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -7127,9 +7133,10 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7">
-        <f>SUM(C30,D30,E30,F30)</f>
-        <v/>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -7184,9 +7191,10 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7">
-        <f>SUM(C31,D31,E31,F31)</f>
-        <v/>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -7241,9 +7249,10 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>SUM(C32,D32,E32,F32)</f>
-        <v/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -7298,9 +7307,10 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>SUM(C33,D33,E33,F33)</f>
-        <v/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -7355,9 +7365,8 @@
           <t xml:space="preserve">    Общехозяйственные</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>SUM(B35,B36,B37,B38,B39,B40,B41,B42)</f>
-        <v/>
+      <c r="B34" s="7" t="n">
+        <v>33932.45</v>
       </c>
       <c r="C34" s="7">
         <f>SUM(C35,C36,C37,C38,C39,C40,C41,C42)</f>
@@ -7406,9 +7415,10 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>SUM(C35,D35,E35,F35)</f>
-        <v/>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -7463,9 +7473,10 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7">
-        <f>SUM(C36,D36,E36,F36)</f>
-        <v/>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -7520,9 +7531,8 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7">
-        <f>SUM(C37,D37,E37,F37)</f>
-        <v/>
+      <c r="B37" s="7" t="n">
+        <v>332.45</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>332.45</v>
@@ -7575,9 +7585,10 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7">
-        <f>SUM(C38,D38,E38,F38)</f>
-        <v/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -7632,9 +7643,8 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7">
-        <f>SUM(C39,D39,E39,F39)</f>
-        <v/>
+      <c r="B39" s="7" t="n">
+        <v>33600</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>8400</v>
@@ -7681,9 +7691,10 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>SUM(C40,D40,E40,F40)</f>
-        <v/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -7738,9 +7749,10 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>SUM(C41,D41,E41,F41)</f>
-        <v/>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
@@ -7795,9 +7807,10 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>SUM(C42,D42,E42,F42)</f>
-        <v/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -7852,9 +7865,8 @@
           <t>Валовая прибыль</t>
         </is>
       </c>
-      <c r="B43" s="9">
-        <f>B4-B10</f>
-        <v/>
+      <c r="B43" s="9" t="n">
+        <v>125319.55</v>
       </c>
       <c r="C43" s="9">
         <f>C4-C10</f>
@@ -7903,9 +7915,10 @@
           <t>Валовая рентабельность</t>
         </is>
       </c>
-      <c r="B44" s="10">
-        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
-        <v/>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>19.10%</t>
+        </is>
       </c>
       <c r="C44" s="10">
         <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
@@ -7954,9 +7967,10 @@
           <t>Косвенные расходы</t>
         </is>
       </c>
-      <c r="B45" s="7">
-        <f>SUM(B46,B47,B48,B52,B56,B57,B58,B59,B60,B63,B64,B65,B66,B67,B68,B69,B70,B71,B72,B73,B74,B75,B76,B77,B78,B79)</f>
-        <v/>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C45" s="7">
         <f>SUM(C46,C47,C48,C52,C56,C57,C58,C59,C60,C63,C64,C65,C66,C67,C68,C69,C70,C71,C72,C73,C74,C75,C76,C77,C78,C79)</f>
@@ -8005,9 +8019,10 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7">
-        <f>SUM(C46,D46,E46,F46)</f>
-        <v/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
@@ -8062,9 +8077,10 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7">
-        <f>SUM(C47,D47,E47,F47)</f>
-        <v/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -8119,9 +8135,10 @@
           <t xml:space="preserve">    Автомобиль</t>
         </is>
       </c>
-      <c r="B48" s="7">
-        <f>SUM(B49,B50,B51)</f>
-        <v/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C48" s="7">
         <f>SUM(C49,C50,C51)</f>
@@ -8170,9 +8187,10 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7">
-        <f>SUM(C49,D49,E49,F49)</f>
-        <v/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -8227,9 +8245,10 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7">
-        <f>SUM(C50,D50,E50,F50)</f>
-        <v/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -8284,9 +8303,10 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7">
-        <f>SUM(C51,D51,E51,F51)</f>
-        <v/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -8341,9 +8361,10 @@
           <t xml:space="preserve">    Офисные расходы</t>
         </is>
       </c>
-      <c r="B52" s="7">
-        <f>SUM(B53,B54,B55)</f>
-        <v/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C52" s="7">
         <f>SUM(C53,C54,C55)</f>
@@ -8392,9 +8413,10 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7">
-        <f>SUM(C53,D53,E53,F53)</f>
-        <v/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -8449,9 +8471,10 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7">
-        <f>SUM(C54,D54,E54,F54)</f>
-        <v/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -8506,9 +8529,10 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7">
-        <f>SUM(C55,D55,E55,F55)</f>
-        <v/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -8563,9 +8587,10 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7">
-        <f>SUM(C56,D56,E56,F56)</f>
-        <v/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -8620,9 +8645,10 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7">
-        <f>SUM(C57,D57,E57,F57)</f>
-        <v/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -8677,9 +8703,10 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7">
-        <f>SUM(C58,D58,E58,F58)</f>
-        <v/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -8734,9 +8761,10 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7">
-        <f>SUM(C59,D59,E59,F59)</f>
-        <v/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -8791,9 +8819,10 @@
           <t xml:space="preserve">    Командировочные расходы</t>
         </is>
       </c>
-      <c r="B60" s="7">
-        <f>SUM(B61,B62)</f>
-        <v/>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C60" s="7">
         <f>SUM(C61,C62)</f>
@@ -8842,9 +8871,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7">
-        <f>SUM(C61,D61,E61,F61)</f>
-        <v/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -8899,9 +8929,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7">
-        <f>SUM(C62,D62,E62,F62)</f>
-        <v/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -8956,9 +8987,10 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7">
-        <f>SUM(C63,D63,E63,F63)</f>
-        <v/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -9013,9 +9045,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7">
-        <f>SUM(C64,D64,E64,F64)</f>
-        <v/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -9070,9 +9103,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7">
-        <f>SUM(C65,D65,E65,F65)</f>
-        <v/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -9127,9 +9161,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7">
-        <f>SUM(C66,D66,E66,F66)</f>
-        <v/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -9184,9 +9219,10 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7">
-        <f>SUM(C67,D67,E67,F67)</f>
-        <v/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -9241,9 +9277,10 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7">
-        <f>SUM(C68,D68,E68,F68)</f>
-        <v/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -9298,9 +9335,10 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7">
-        <f>SUM(C69,D69,E69,F69)</f>
-        <v/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -9355,9 +9393,10 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7">
-        <f>SUM(C70,D70,E70,F70)</f>
-        <v/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -9412,9 +9451,10 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7">
-        <f>SUM(C71,D71,E71,F71)</f>
-        <v/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -9469,9 +9509,10 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7">
-        <f>SUM(C72,D72,E72,F72)</f>
-        <v/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -9526,9 +9567,10 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7">
-        <f>SUM(C73,D73,E73,F73)</f>
-        <v/>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -9583,9 +9625,10 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7">
-        <f>SUM(C74,D74,E74,F74)</f>
-        <v/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -9640,9 +9683,10 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7">
-        <f>SUM(C75,D75,E75,F75)</f>
-        <v/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -9697,9 +9741,10 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7">
-        <f>SUM(C76,D76,E76,F76)</f>
-        <v/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -9754,9 +9799,10 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7">
-        <f>SUM(C77,D77,E77,F77)</f>
-        <v/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -9811,9 +9857,10 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7">
-        <f>SUM(C78,D78,E78,F78)</f>
-        <v/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -9868,9 +9915,10 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7">
-        <f>SUM(C79,D79,E79,F79)</f>
-        <v/>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -9925,9 +9973,8 @@
           <t>Операционная прибыль</t>
         </is>
       </c>
-      <c r="B80" s="9">
-        <f>B43-B45</f>
-        <v/>
+      <c r="B80" s="9" t="n">
+        <v>125319.55</v>
       </c>
       <c r="C80" s="9">
         <f>C43-C45</f>
@@ -9976,9 +10023,10 @@
           <t>Операционная рентабельность</t>
         </is>
       </c>
-      <c r="B81" s="10">
-        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
-        <v/>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>19.10%</t>
+        </is>
       </c>
       <c r="C81" s="10">
         <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
@@ -10027,9 +10075,10 @@
           <t>Прочие доходы</t>
         </is>
       </c>
-      <c r="B82" s="7">
-        <f>SUM(B83,B84,B85,B86)</f>
-        <v/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C82" s="7">
         <f>SUM(C83,C84,C85,C86)</f>
@@ -10078,9 +10127,10 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7">
-        <f>SUM(C83,D83,E83,F83)</f>
-        <v/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -10135,9 +10185,10 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7">
-        <f>SUM(C84,D84,E84,F84)</f>
-        <v/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -10192,9 +10243,10 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7">
-        <f>SUM(C85,D85,E85,F85)</f>
-        <v/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -10249,9 +10301,10 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7">
-        <f>SUM(C86,D86,E86,F86)</f>
-        <v/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -10306,9 +10359,10 @@
           <t>Прочие расходы</t>
         </is>
       </c>
-      <c r="B87" s="7">
-        <f>SUM(B88)</f>
-        <v/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C87" s="7">
         <f>SUM(C88)</f>
@@ -10357,9 +10411,10 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7">
-        <f>SUM(C88,D88,E88,F88)</f>
-        <v/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -10414,9 +10469,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B89" s="9">
-        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
-        <v/>
+      <c r="B89" s="9" t="n">
+        <v>125319.55</v>
       </c>
       <c r="C89" s="9">
         <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
@@ -10465,9 +10519,10 @@
           <t>Рентабельность по EBITDA</t>
         </is>
       </c>
-      <c r="B90" s="10">
-        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
-        <v/>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>19.10%</t>
+        </is>
       </c>
       <c r="C90" s="10">
         <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
@@ -10516,9 +10571,10 @@
           <t>Амортизация</t>
         </is>
       </c>
-      <c r="B91" s="7">
-        <f>SUM(B92,B93)</f>
-        <v/>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C91" s="7">
         <f>SUM(C92,C93)</f>
@@ -10567,9 +10623,10 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7">
-        <f>SUM(C92,D92,E92,F92)</f>
-        <v/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -10624,9 +10681,10 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7">
-        <f>SUM(C93,D93,E93,F93)</f>
-        <v/>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -10681,9 +10739,10 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7">
-        <f>SUM(C94,D94,E94,F94)</f>
-        <v/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -10738,9 +10797,8 @@
           <t>Налог на прибыль</t>
         </is>
       </c>
-      <c r="B95" s="7">
-        <f>SUM(B96,B97)</f>
-        <v/>
+      <c r="B95" s="7" t="n">
+        <v>46000</v>
       </c>
       <c r="C95" s="7">
         <f>SUM(C96,C97)</f>
@@ -10789,9 +10847,8 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7">
-        <f>SUM(C96,D96,E96,F96)</f>
-        <v/>
+      <c r="B96" s="7" t="n">
+        <v>46000</v>
       </c>
       <c r="C96" s="7" t="n">
         <v>11500</v>
@@ -10838,9 +10895,10 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7">
-        <f>SUM(C97,D97,E97,F97)</f>
-        <v/>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
@@ -10895,9 +10953,8 @@
           <t>Чистая прибыль (убыток)</t>
         </is>
       </c>
-      <c r="B98" s="9">
-        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
-        <v/>
+      <c r="B98" s="9" t="n">
+        <v>79319.55000000005</v>
       </c>
       <c r="C98" s="9">
         <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
@@ -10946,9 +11003,10 @@
           <t>Рентабельность чистой прибыли</t>
         </is>
       </c>
-      <c r="B99" s="10">
-        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
-        <v/>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>12.09%</t>
+        </is>
       </c>
       <c r="C99" s="10">
         <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
@@ -11156,9 +11214,8 @@
           <t>Выручка</t>
         </is>
       </c>
-      <c r="B4" s="7">
-        <f>SUM(B5,B6)</f>
-        <v/>
+      <c r="B4" s="7" t="n">
+        <v>384000</v>
       </c>
       <c r="C4" s="7">
         <f>SUM(C5,C6)</f>
@@ -11207,9 +11264,10 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7">
-        <f>SUM(C5,D5,E5,F5)</f>
-        <v/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -11264,9 +11322,8 @@
           <t xml:space="preserve">    Выручка </t>
         </is>
       </c>
-      <c r="B6" s="7">
-        <f>SUM(B7,B8,B9)</f>
-        <v/>
+      <c r="B6" s="7" t="n">
+        <v>384000</v>
       </c>
       <c r="C6" s="7">
         <f>SUM(C7,C8,C9)</f>
@@ -11315,9 +11372,8 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7">
-        <f>SUM(C7,D7,E7,F7)</f>
-        <v/>
+      <c r="B7" s="7" t="n">
+        <v>384000</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>96000</v>
@@ -11364,9 +11420,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7">
-        <f>SUM(C8,D8,E8,F8)</f>
-        <v/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -11421,9 +11478,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7">
-        <f>SUM(C9,D9,E9,F9)</f>
-        <v/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -11478,9 +11536,8 @@
           <t>Прямые расходы</t>
         </is>
       </c>
-      <c r="B10" s="7">
-        <f>SUM(B11,B12,B13,B21,B22,B23,B24,B25,B26,B27,B28,B29,B30,B31,B32,B33,B34)</f>
-        <v/>
+      <c r="B10" s="7" t="n">
+        <v>350000</v>
       </c>
       <c r="C10" s="7">
         <f>SUM(C11,C12,C13,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34)</f>
@@ -11529,9 +11586,10 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7">
-        <f>SUM(C11,D11,E11,F11)</f>
-        <v/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -11586,9 +11644,10 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7">
-        <f>SUM(C12,D12,E12,F12)</f>
-        <v/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -11643,9 +11702,8 @@
           <t xml:space="preserve">    Переменные</t>
         </is>
       </c>
-      <c r="B13" s="7">
-        <f>SUM(B14,B15,B16,B17,B18,B19,B20)</f>
-        <v/>
+      <c r="B13" s="7" t="n">
+        <v>16000</v>
       </c>
       <c r="C13" s="7">
         <f>SUM(C14,C15,C16,C17,C18,C19,C20)</f>
@@ -11694,9 +11752,10 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7">
-        <f>SUM(C14,D14,E14,F14)</f>
-        <v/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -11751,9 +11810,10 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(C15,D15,E15,F15)</f>
-        <v/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -11808,9 +11868,10 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(C16,D16,E16,F16)</f>
-        <v/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -11865,9 +11926,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7">
-        <f>SUM(C17,D17,E17,F17)</f>
-        <v/>
+      <c r="B17" s="7" t="n">
+        <v>8000</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>2000</v>
@@ -11914,9 +11974,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>SUM(C18,D18,E18,F18)</f>
-        <v/>
+      <c r="B18" s="7" t="n">
+        <v>8000</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>2000</v>
@@ -11963,9 +12022,10 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>SUM(C19,D19,E19,F19)</f>
-        <v/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -12020,9 +12080,10 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>SUM(C20,D20,E20,F20)</f>
-        <v/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -12077,9 +12138,8 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>SUM(C21,D21,E21,F21)</f>
-        <v/>
+      <c r="B21" s="7" t="n">
+        <v>140000</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>35000</v>
@@ -12126,9 +12186,8 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>SUM(C22,D22,E22,F22)</f>
-        <v/>
+      <c r="B22" s="7" t="n">
+        <v>140000</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>35000</v>
@@ -12175,9 +12234,8 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>SUM(C23,D23,E23,F23)</f>
-        <v/>
+      <c r="B23" s="7" t="n">
+        <v>42000</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -12226,9 +12284,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>SUM(C24,D24,E24,F24)</f>
-        <v/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -12283,9 +12342,10 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>SUM(C25,D25,E25,F25)</f>
-        <v/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -12340,9 +12400,10 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>SUM(C26,D26,E26,F26)</f>
-        <v/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -12397,9 +12458,10 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7">
-        <f>SUM(C27,D27,E27,F27)</f>
-        <v/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -12454,9 +12516,10 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7">
-        <f>SUM(C28,D28,E28,F28)</f>
-        <v/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -12511,9 +12574,10 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7">
-        <f>SUM(C29,D29,E29,F29)</f>
-        <v/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -12568,9 +12632,10 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7">
-        <f>SUM(C30,D30,E30,F30)</f>
-        <v/>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -12625,9 +12690,10 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7">
-        <f>SUM(C31,D31,E31,F31)</f>
-        <v/>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -12682,9 +12748,10 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>SUM(C32,D32,E32,F32)</f>
-        <v/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -12739,9 +12806,10 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>SUM(C33,D33,E33,F33)</f>
-        <v/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -12796,9 +12864,8 @@
           <t xml:space="preserve">    Общехозяйственные</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>SUM(B35,B36,B37,B38,B39,B40,B41,B42)</f>
-        <v/>
+      <c r="B34" s="7" t="n">
+        <v>12000</v>
       </c>
       <c r="C34" s="7">
         <f>SUM(C35,C36,C37,C38,C39,C40,C41,C42)</f>
@@ -12847,9 +12914,10 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>SUM(C35,D35,E35,F35)</f>
-        <v/>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -12904,9 +12972,10 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7">
-        <f>SUM(C36,D36,E36,F36)</f>
-        <v/>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -12961,9 +13030,10 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7">
-        <f>SUM(C37,D37,E37,F37)</f>
-        <v/>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
@@ -13018,9 +13088,10 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7">
-        <f>SUM(C38,D38,E38,F38)</f>
-        <v/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -13075,9 +13146,8 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7">
-        <f>SUM(C39,D39,E39,F39)</f>
-        <v/>
+      <c r="B39" s="7" t="n">
+        <v>12000</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>3000</v>
@@ -13124,9 +13194,10 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>SUM(C40,D40,E40,F40)</f>
-        <v/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -13181,9 +13252,10 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>SUM(C41,D41,E41,F41)</f>
-        <v/>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
@@ -13238,9 +13310,10 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>SUM(C42,D42,E42,F42)</f>
-        <v/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -13295,9 +13368,8 @@
           <t>Валовая прибыль</t>
         </is>
       </c>
-      <c r="B43" s="9">
-        <f>B4-B10</f>
-        <v/>
+      <c r="B43" s="9" t="n">
+        <v>34000</v>
       </c>
       <c r="C43" s="9">
         <f>C4-C10</f>
@@ -13346,9 +13418,10 @@
           <t>Валовая рентабельность</t>
         </is>
       </c>
-      <c r="B44" s="10">
-        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
-        <v/>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>8.85%</t>
+        </is>
       </c>
       <c r="C44" s="10">
         <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
@@ -13397,9 +13470,10 @@
           <t>Косвенные расходы</t>
         </is>
       </c>
-      <c r="B45" s="7">
-        <f>SUM(B46,B47,B48,B52,B56,B57,B58,B59,B60,B63,B64,B65,B66,B67,B68,B69,B70,B71,B72,B73,B74,B75,B76,B77,B78,B79)</f>
-        <v/>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C45" s="7">
         <f>SUM(C46,C47,C48,C52,C56,C57,C58,C59,C60,C63,C64,C65,C66,C67,C68,C69,C70,C71,C72,C73,C74,C75,C76,C77,C78,C79)</f>
@@ -13448,9 +13522,10 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7">
-        <f>SUM(C46,D46,E46,F46)</f>
-        <v/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
@@ -13505,9 +13580,10 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7">
-        <f>SUM(C47,D47,E47,F47)</f>
-        <v/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -13562,9 +13638,10 @@
           <t xml:space="preserve">    Автомобиль</t>
         </is>
       </c>
-      <c r="B48" s="7">
-        <f>SUM(B49,B50,B51)</f>
-        <v/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C48" s="7">
         <f>SUM(C49,C50,C51)</f>
@@ -13613,9 +13690,10 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7">
-        <f>SUM(C49,D49,E49,F49)</f>
-        <v/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -13670,9 +13748,10 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7">
-        <f>SUM(C50,D50,E50,F50)</f>
-        <v/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -13727,9 +13806,10 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7">
-        <f>SUM(C51,D51,E51,F51)</f>
-        <v/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -13784,9 +13864,10 @@
           <t xml:space="preserve">    Офисные расходы</t>
         </is>
       </c>
-      <c r="B52" s="7">
-        <f>SUM(B53,B54,B55)</f>
-        <v/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C52" s="7">
         <f>SUM(C53,C54,C55)</f>
@@ -13835,9 +13916,10 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7">
-        <f>SUM(C53,D53,E53,F53)</f>
-        <v/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -13892,9 +13974,10 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7">
-        <f>SUM(C54,D54,E54,F54)</f>
-        <v/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -13949,9 +14032,10 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7">
-        <f>SUM(C55,D55,E55,F55)</f>
-        <v/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -14006,9 +14090,10 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7">
-        <f>SUM(C56,D56,E56,F56)</f>
-        <v/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -14063,9 +14148,10 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7">
-        <f>SUM(C57,D57,E57,F57)</f>
-        <v/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -14120,9 +14206,10 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7">
-        <f>SUM(C58,D58,E58,F58)</f>
-        <v/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -14177,9 +14264,10 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7">
-        <f>SUM(C59,D59,E59,F59)</f>
-        <v/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -14234,9 +14322,10 @@
           <t xml:space="preserve">    Командировочные расходы</t>
         </is>
       </c>
-      <c r="B60" s="7">
-        <f>SUM(B61,B62)</f>
-        <v/>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C60" s="7">
         <f>SUM(C61,C62)</f>
@@ -14285,9 +14374,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7">
-        <f>SUM(C61,D61,E61,F61)</f>
-        <v/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -14342,9 +14432,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7">
-        <f>SUM(C62,D62,E62,F62)</f>
-        <v/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -14399,9 +14490,10 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7">
-        <f>SUM(C63,D63,E63,F63)</f>
-        <v/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -14456,9 +14548,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7">
-        <f>SUM(C64,D64,E64,F64)</f>
-        <v/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -14513,9 +14606,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7">
-        <f>SUM(C65,D65,E65,F65)</f>
-        <v/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -14570,9 +14664,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7">
-        <f>SUM(C66,D66,E66,F66)</f>
-        <v/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -14627,9 +14722,10 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7">
-        <f>SUM(C67,D67,E67,F67)</f>
-        <v/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -14684,9 +14780,10 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7">
-        <f>SUM(C68,D68,E68,F68)</f>
-        <v/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -14741,9 +14838,10 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7">
-        <f>SUM(C69,D69,E69,F69)</f>
-        <v/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -14798,9 +14896,10 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7">
-        <f>SUM(C70,D70,E70,F70)</f>
-        <v/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -14855,9 +14954,10 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7">
-        <f>SUM(C71,D71,E71,F71)</f>
-        <v/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -14912,9 +15012,10 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7">
-        <f>SUM(C72,D72,E72,F72)</f>
-        <v/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -14969,9 +15070,10 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7">
-        <f>SUM(C73,D73,E73,F73)</f>
-        <v/>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -15026,9 +15128,10 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7">
-        <f>SUM(C74,D74,E74,F74)</f>
-        <v/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -15083,9 +15186,10 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7">
-        <f>SUM(C75,D75,E75,F75)</f>
-        <v/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -15140,9 +15244,10 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7">
-        <f>SUM(C76,D76,E76,F76)</f>
-        <v/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -15197,9 +15302,10 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7">
-        <f>SUM(C77,D77,E77,F77)</f>
-        <v/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -15254,9 +15360,10 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7">
-        <f>SUM(C78,D78,E78,F78)</f>
-        <v/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -15311,9 +15418,10 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7">
-        <f>SUM(C79,D79,E79,F79)</f>
-        <v/>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -15368,9 +15476,8 @@
           <t>Операционная прибыль</t>
         </is>
       </c>
-      <c r="B80" s="9">
-        <f>B43-B45</f>
-        <v/>
+      <c r="B80" s="9" t="n">
+        <v>34000</v>
       </c>
       <c r="C80" s="9">
         <f>C43-C45</f>
@@ -15419,9 +15526,10 @@
           <t>Операционная рентабельность</t>
         </is>
       </c>
-      <c r="B81" s="10">
-        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
-        <v/>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>8.85%</t>
+        </is>
       </c>
       <c r="C81" s="10">
         <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
@@ -15470,9 +15578,10 @@
           <t>Прочие доходы</t>
         </is>
       </c>
-      <c r="B82" s="7">
-        <f>SUM(B83,B84,B85,B86)</f>
-        <v/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C82" s="7">
         <f>SUM(C83,C84,C85,C86)</f>
@@ -15521,9 +15630,10 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7">
-        <f>SUM(C83,D83,E83,F83)</f>
-        <v/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -15578,9 +15688,10 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7">
-        <f>SUM(C84,D84,E84,F84)</f>
-        <v/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -15635,9 +15746,10 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7">
-        <f>SUM(C85,D85,E85,F85)</f>
-        <v/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -15692,9 +15804,10 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7">
-        <f>SUM(C86,D86,E86,F86)</f>
-        <v/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -15749,9 +15862,10 @@
           <t>Прочие расходы</t>
         </is>
       </c>
-      <c r="B87" s="7">
-        <f>SUM(B88)</f>
-        <v/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C87" s="7">
         <f>SUM(C88)</f>
@@ -15800,9 +15914,10 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7">
-        <f>SUM(C88,D88,E88,F88)</f>
-        <v/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -15857,9 +15972,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B89" s="9">
-        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
-        <v/>
+      <c r="B89" s="9" t="n">
+        <v>34000</v>
       </c>
       <c r="C89" s="9">
         <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
@@ -15908,9 +16022,10 @@
           <t>Рентабельность по EBITDA</t>
         </is>
       </c>
-      <c r="B90" s="10">
-        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
-        <v/>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>8.85%</t>
+        </is>
       </c>
       <c r="C90" s="10">
         <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
@@ -15959,9 +16074,10 @@
           <t>Амортизация</t>
         </is>
       </c>
-      <c r="B91" s="7">
-        <f>SUM(B92,B93)</f>
-        <v/>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C91" s="7">
         <f>SUM(C92,C93)</f>
@@ -16010,9 +16126,10 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7">
-        <f>SUM(C92,D92,E92,F92)</f>
-        <v/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -16067,9 +16184,10 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7">
-        <f>SUM(C93,D93,E93,F93)</f>
-        <v/>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -16124,9 +16242,10 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7">
-        <f>SUM(C94,D94,E94,F94)</f>
-        <v/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -16181,9 +16300,8 @@
           <t>Налог на прибыль</t>
         </is>
       </c>
-      <c r="B95" s="7">
-        <f>SUM(B96,B97)</f>
-        <v/>
+      <c r="B95" s="7" t="n">
+        <v>26800</v>
       </c>
       <c r="C95" s="7">
         <f>SUM(C96,C97)</f>
@@ -16232,9 +16350,8 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7">
-        <f>SUM(C96,D96,E96,F96)</f>
-        <v/>
+      <c r="B96" s="7" t="n">
+        <v>26800</v>
       </c>
       <c r="C96" s="7" t="n">
         <v>6700</v>
@@ -16281,9 +16398,10 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7">
-        <f>SUM(C97,D97,E97,F97)</f>
-        <v/>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
@@ -16338,9 +16456,8 @@
           <t>Чистая прибыль (убыток)</t>
         </is>
       </c>
-      <c r="B98" s="9">
-        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
-        <v/>
+      <c r="B98" s="9" t="n">
+        <v>7200</v>
       </c>
       <c r="C98" s="9">
         <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
@@ -16389,9 +16506,10 @@
           <t>Рентабельность чистой прибыли</t>
         </is>
       </c>
-      <c r="B99" s="10">
-        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
-        <v/>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>1.88%</t>
+        </is>
       </c>
       <c r="C99" s="10">
         <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
@@ -16599,9 +16717,8 @@
           <t>Выручка</t>
         </is>
       </c>
-      <c r="B4" s="7">
-        <f>SUM(B5,B6)</f>
-        <v/>
+      <c r="B4" s="7" t="n">
+        <v>2451750.6</v>
       </c>
       <c r="C4" s="7">
         <f>SUM(C5,C6)</f>
@@ -16650,9 +16767,10 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7">
-        <f>SUM(C5,D5,E5,F5)</f>
-        <v/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -16707,9 +16825,8 @@
           <t xml:space="preserve">    Выручка </t>
         </is>
       </c>
-      <c r="B6" s="7">
-        <f>SUM(B7,B8,B9)</f>
-        <v/>
+      <c r="B6" s="7" t="n">
+        <v>2451750.6</v>
       </c>
       <c r="C6" s="7">
         <f>SUM(C7,C8,C9)</f>
@@ -16758,9 +16875,8 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7">
-        <f>SUM(C7,D7,E7,F7)</f>
-        <v/>
+      <c r="B7" s="7" t="n">
+        <v>2451750.6</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>373920.6</v>
@@ -16807,9 +16923,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7">
-        <f>SUM(C8,D8,E8,F8)</f>
-        <v/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -16864,9 +16981,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7">
-        <f>SUM(C9,D9,E9,F9)</f>
-        <v/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -16921,9 +17039,8 @@
           <t>Прямые расходы</t>
         </is>
       </c>
-      <c r="B10" s="7">
-        <f>SUM(B11,B12,B13,B21,B22,B23,B24,B25,B26,B27,B28,B29,B30,B31,B32,B33,B34)</f>
-        <v/>
+      <c r="B10" s="7" t="n">
+        <v>1028537.68</v>
       </c>
       <c r="C10" s="7">
         <f>SUM(C11,C12,C13,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34)</f>
@@ -16972,9 +17089,10 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7">
-        <f>SUM(C11,D11,E11,F11)</f>
-        <v/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -17029,9 +17147,10 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7">
-        <f>SUM(C12,D12,E12,F12)</f>
-        <v/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -17086,9 +17205,8 @@
           <t xml:space="preserve">    Переменные</t>
         </is>
       </c>
-      <c r="B13" s="7">
-        <f>SUM(B14,B15,B16,B17,B18,B19,B20)</f>
-        <v/>
+      <c r="B13" s="7" t="n">
+        <v>170000</v>
       </c>
       <c r="C13" s="7">
         <f>SUM(C14,C15,C16,C17,C18,C19,C20)</f>
@@ -17137,9 +17255,10 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7">
-        <f>SUM(C14,D14,E14,F14)</f>
-        <v/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -17194,9 +17313,10 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(C15,D15,E15,F15)</f>
-        <v/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -17251,9 +17371,10 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(C16,D16,E16,F16)</f>
-        <v/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -17308,9 +17429,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7">
-        <f>SUM(C17,D17,E17,F17)</f>
-        <v/>
+      <c r="B17" s="7" t="n">
+        <v>120000</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -17359,9 +17479,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>SUM(C18,D18,E18,F18)</f>
-        <v/>
+      <c r="B18" s="7" t="n">
+        <v>20000</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>5000</v>
@@ -17408,9 +17527,10 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>SUM(C19,D19,E19,F19)</f>
-        <v/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -17465,9 +17585,8 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>SUM(C20,D20,E20,F20)</f>
-        <v/>
+      <c r="B20" s="7" t="n">
+        <v>30000</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>30000</v>
@@ -17520,9 +17639,8 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>SUM(C21,D21,E21,F21)</f>
-        <v/>
+      <c r="B21" s="7" t="n">
+        <v>200000</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>50000</v>
@@ -17569,9 +17687,8 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>SUM(C22,D22,E22,F22)</f>
-        <v/>
+      <c r="B22" s="7" t="n">
+        <v>452500</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>62500</v>
@@ -17618,9 +17735,8 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>SUM(C23,D23,E23,F23)</f>
-        <v/>
+      <c r="B23" s="7" t="n">
+        <v>45037.68</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>3037.68</v>
@@ -17667,9 +17783,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>SUM(C24,D24,E24,F24)</f>
-        <v/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -17724,9 +17841,10 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>SUM(C25,D25,E25,F25)</f>
-        <v/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -17781,9 +17899,10 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>SUM(C26,D26,E26,F26)</f>
-        <v/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -17838,9 +17957,10 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7">
-        <f>SUM(C27,D27,E27,F27)</f>
-        <v/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -17895,9 +18015,10 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7">
-        <f>SUM(C28,D28,E28,F28)</f>
-        <v/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -17952,9 +18073,10 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7">
-        <f>SUM(C29,D29,E29,F29)</f>
-        <v/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -18009,9 +18131,10 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7">
-        <f>SUM(C30,D30,E30,F30)</f>
-        <v/>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -18066,9 +18189,10 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7">
-        <f>SUM(C31,D31,E31,F31)</f>
-        <v/>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -18123,9 +18247,10 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>SUM(C32,D32,E32,F32)</f>
-        <v/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -18180,9 +18305,10 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>SUM(C33,D33,E33,F33)</f>
-        <v/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -18237,9 +18363,8 @@
           <t xml:space="preserve">    Общехозяйственные</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>SUM(B35,B36,B37,B38,B39,B40,B41,B42)</f>
-        <v/>
+      <c r="B34" s="7" t="n">
+        <v>161000</v>
       </c>
       <c r="C34" s="7">
         <f>SUM(C35,C36,C37,C38,C39,C40,C41,C42)</f>
@@ -18288,9 +18413,10 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>SUM(C35,D35,E35,F35)</f>
-        <v/>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -18345,9 +18471,8 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7">
-        <f>SUM(C36,D36,E36,F36)</f>
-        <v/>
+      <c r="B36" s="7" t="n">
+        <v>120000</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>30000</v>
@@ -18394,9 +18519,10 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7">
-        <f>SUM(C37,D37,E37,F37)</f>
-        <v/>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
@@ -18451,9 +18577,10 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7">
-        <f>SUM(C38,D38,E38,F38)</f>
-        <v/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -18508,9 +18635,8 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7">
-        <f>SUM(C39,D39,E39,F39)</f>
-        <v/>
+      <c r="B39" s="7" t="n">
+        <v>39500</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>3500</v>
@@ -18557,9 +18683,10 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>SUM(C40,D40,E40,F40)</f>
-        <v/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -18614,9 +18741,8 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>SUM(C41,D41,E41,F41)</f>
-        <v/>
+      <c r="B41" s="7" t="n">
+        <v>1500</v>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
@@ -18665,9 +18791,10 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>SUM(C42,D42,E42,F42)</f>
-        <v/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -18722,9 +18849,8 @@
           <t>Валовая прибыль</t>
         </is>
       </c>
-      <c r="B43" s="9">
-        <f>B4-B10</f>
-        <v/>
+      <c r="B43" s="9" t="n">
+        <v>1423212.92</v>
       </c>
       <c r="C43" s="9">
         <f>C4-C10</f>
@@ -18773,9 +18899,10 @@
           <t>Валовая рентабельность</t>
         </is>
       </c>
-      <c r="B44" s="10">
-        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
-        <v/>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>58.05%</t>
+        </is>
       </c>
       <c r="C44" s="10">
         <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
@@ -18824,9 +18951,10 @@
           <t>Косвенные расходы</t>
         </is>
       </c>
-      <c r="B45" s="7">
-        <f>SUM(B46,B47,B48,B52,B56,B57,B58,B59,B60,B63,B64,B65,B66,B67,B68,B69,B70,B71,B72,B73,B74,B75,B76,B77,B78,B79)</f>
-        <v/>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C45" s="7">
         <f>SUM(C46,C47,C48,C52,C56,C57,C58,C59,C60,C63,C64,C65,C66,C67,C68,C69,C70,C71,C72,C73,C74,C75,C76,C77,C78,C79)</f>
@@ -18875,9 +19003,10 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7">
-        <f>SUM(C46,D46,E46,F46)</f>
-        <v/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
@@ -18932,9 +19061,10 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7">
-        <f>SUM(C47,D47,E47,F47)</f>
-        <v/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -18989,9 +19119,10 @@
           <t xml:space="preserve">    Автомобиль</t>
         </is>
       </c>
-      <c r="B48" s="7">
-        <f>SUM(B49,B50,B51)</f>
-        <v/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C48" s="7">
         <f>SUM(C49,C50,C51)</f>
@@ -19040,9 +19171,10 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7">
-        <f>SUM(C49,D49,E49,F49)</f>
-        <v/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -19097,9 +19229,10 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7">
-        <f>SUM(C50,D50,E50,F50)</f>
-        <v/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -19154,9 +19287,10 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7">
-        <f>SUM(C51,D51,E51,F51)</f>
-        <v/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -19211,9 +19345,10 @@
           <t xml:space="preserve">    Офисные расходы</t>
         </is>
       </c>
-      <c r="B52" s="7">
-        <f>SUM(B53,B54,B55)</f>
-        <v/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C52" s="7">
         <f>SUM(C53,C54,C55)</f>
@@ -19262,9 +19397,10 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7">
-        <f>SUM(C53,D53,E53,F53)</f>
-        <v/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -19319,9 +19455,10 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7">
-        <f>SUM(C54,D54,E54,F54)</f>
-        <v/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -19376,9 +19513,10 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7">
-        <f>SUM(C55,D55,E55,F55)</f>
-        <v/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -19433,9 +19571,10 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7">
-        <f>SUM(C56,D56,E56,F56)</f>
-        <v/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -19490,9 +19629,10 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7">
-        <f>SUM(C57,D57,E57,F57)</f>
-        <v/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -19547,9 +19687,10 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7">
-        <f>SUM(C58,D58,E58,F58)</f>
-        <v/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -19604,9 +19745,10 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7">
-        <f>SUM(C59,D59,E59,F59)</f>
-        <v/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -19661,9 +19803,10 @@
           <t xml:space="preserve">    Командировочные расходы</t>
         </is>
       </c>
-      <c r="B60" s="7">
-        <f>SUM(B61,B62)</f>
-        <v/>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C60" s="7">
         <f>SUM(C61,C62)</f>
@@ -19712,9 +19855,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7">
-        <f>SUM(C61,D61,E61,F61)</f>
-        <v/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -19769,9 +19913,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7">
-        <f>SUM(C62,D62,E62,F62)</f>
-        <v/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -19826,9 +19971,10 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7">
-        <f>SUM(C63,D63,E63,F63)</f>
-        <v/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -19883,9 +20029,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7">
-        <f>SUM(C64,D64,E64,F64)</f>
-        <v/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -19940,9 +20087,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7">
-        <f>SUM(C65,D65,E65,F65)</f>
-        <v/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -19997,9 +20145,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7">
-        <f>SUM(C66,D66,E66,F66)</f>
-        <v/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -20054,9 +20203,10 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7">
-        <f>SUM(C67,D67,E67,F67)</f>
-        <v/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -20111,9 +20261,10 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7">
-        <f>SUM(C68,D68,E68,F68)</f>
-        <v/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -20168,9 +20319,10 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7">
-        <f>SUM(C69,D69,E69,F69)</f>
-        <v/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -20225,9 +20377,10 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7">
-        <f>SUM(C70,D70,E70,F70)</f>
-        <v/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -20282,9 +20435,10 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7">
-        <f>SUM(C71,D71,E71,F71)</f>
-        <v/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -20339,9 +20493,10 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7">
-        <f>SUM(C72,D72,E72,F72)</f>
-        <v/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -20396,9 +20551,10 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7">
-        <f>SUM(C73,D73,E73,F73)</f>
-        <v/>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -20453,9 +20609,10 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7">
-        <f>SUM(C74,D74,E74,F74)</f>
-        <v/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -20510,9 +20667,10 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7">
-        <f>SUM(C75,D75,E75,F75)</f>
-        <v/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -20567,9 +20725,10 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7">
-        <f>SUM(C76,D76,E76,F76)</f>
-        <v/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -20624,9 +20783,10 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7">
-        <f>SUM(C77,D77,E77,F77)</f>
-        <v/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -20681,9 +20841,10 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7">
-        <f>SUM(C78,D78,E78,F78)</f>
-        <v/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -20738,9 +20899,10 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7">
-        <f>SUM(C79,D79,E79,F79)</f>
-        <v/>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -20795,9 +20957,8 @@
           <t>Операционная прибыль</t>
         </is>
       </c>
-      <c r="B80" s="9">
-        <f>B43-B45</f>
-        <v/>
+      <c r="B80" s="9" t="n">
+        <v>1423212.92</v>
       </c>
       <c r="C80" s="9">
         <f>C43-C45</f>
@@ -20846,9 +21007,10 @@
           <t>Операционная рентабельность</t>
         </is>
       </c>
-      <c r="B81" s="10">
-        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
-        <v/>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>58.05%</t>
+        </is>
       </c>
       <c r="C81" s="10">
         <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
@@ -20897,9 +21059,10 @@
           <t>Прочие доходы</t>
         </is>
       </c>
-      <c r="B82" s="7">
-        <f>SUM(B83,B84,B85,B86)</f>
-        <v/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C82" s="7">
         <f>SUM(C83,C84,C85,C86)</f>
@@ -20948,9 +21111,10 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7">
-        <f>SUM(C83,D83,E83,F83)</f>
-        <v/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -21005,9 +21169,10 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7">
-        <f>SUM(C84,D84,E84,F84)</f>
-        <v/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -21062,9 +21227,10 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7">
-        <f>SUM(C85,D85,E85,F85)</f>
-        <v/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -21119,9 +21285,10 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7">
-        <f>SUM(C86,D86,E86,F86)</f>
-        <v/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -21176,9 +21343,10 @@
           <t>Прочие расходы</t>
         </is>
       </c>
-      <c r="B87" s="7">
-        <f>SUM(B88)</f>
-        <v/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C87" s="7">
         <f>SUM(C88)</f>
@@ -21227,9 +21395,10 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7">
-        <f>SUM(C88,D88,E88,F88)</f>
-        <v/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -21284,9 +21453,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B89" s="9">
-        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
-        <v/>
+      <c r="B89" s="9" t="n">
+        <v>1423212.92</v>
       </c>
       <c r="C89" s="9">
         <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
@@ -21335,9 +21503,10 @@
           <t>Рентабельность по EBITDA</t>
         </is>
       </c>
-      <c r="B90" s="10">
-        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
-        <v/>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>58.05%</t>
+        </is>
       </c>
       <c r="C90" s="10">
         <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
@@ -21386,9 +21555,8 @@
           <t>Амортизация</t>
         </is>
       </c>
-      <c r="B91" s="7">
-        <f>SUM(B92,B93)</f>
-        <v/>
+      <c r="B91" s="7" t="n">
+        <v>225000</v>
       </c>
       <c r="C91" s="7">
         <f>SUM(C92,C93)</f>
@@ -21437,9 +21605,10 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7">
-        <f>SUM(C92,D92,E92,F92)</f>
-        <v/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -21494,9 +21663,8 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7">
-        <f>SUM(C93,D93,E93,F93)</f>
-        <v/>
+      <c r="B93" s="7" t="n">
+        <v>225000</v>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -21549,9 +21717,10 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7">
-        <f>SUM(C94,D94,E94,F94)</f>
-        <v/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -21606,9 +21775,8 @@
           <t>Налог на прибыль</t>
         </is>
       </c>
-      <c r="B95" s="7">
-        <f>SUM(B96,B97)</f>
-        <v/>
+      <c r="B95" s="7" t="n">
+        <v>158595.74</v>
       </c>
       <c r="C95" s="7">
         <f>SUM(C96,C97)</f>
@@ -21657,9 +21825,8 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7">
-        <f>SUM(C96,D96,E96,F96)</f>
-        <v/>
+      <c r="B96" s="7" t="n">
+        <v>36900</v>
       </c>
       <c r="C96" s="7" t="n">
         <v>5700</v>
@@ -21706,9 +21873,8 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7">
-        <f>SUM(C97,D97,E97,F97)</f>
-        <v/>
+      <c r="B97" s="7" t="n">
+        <v>121695.74</v>
       </c>
       <c r="C97" s="7" t="n">
         <v>17805.74</v>
@@ -21755,9 +21921,8 @@
           <t>Чистая прибыль (убыток)</t>
         </is>
       </c>
-      <c r="B98" s="9">
-        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
-        <v/>
+      <c r="B98" s="9" t="n">
+        <v>1039617.18</v>
       </c>
       <c r="C98" s="9">
         <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
@@ -21806,9 +21971,10 @@
           <t>Рентабельность чистой прибыли</t>
         </is>
       </c>
-      <c r="B99" s="10">
-        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
-        <v/>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>42.40%</t>
+        </is>
       </c>
       <c r="C99" s="10">
         <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
@@ -22016,9 +22182,8 @@
           <t>Выручка</t>
         </is>
       </c>
-      <c r="B4" s="7">
-        <f>SUM(B5,B6)</f>
-        <v/>
+      <c r="B4" s="7" t="n">
+        <v>2539080</v>
       </c>
       <c r="C4" s="7">
         <f>SUM(C5,C6)</f>
@@ -22067,9 +22232,10 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7">
-        <f>SUM(C5,D5,E5,F5)</f>
-        <v/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -22124,9 +22290,8 @@
           <t xml:space="preserve">    Выручка </t>
         </is>
       </c>
-      <c r="B6" s="7">
-        <f>SUM(B7,B8,B9)</f>
-        <v/>
+      <c r="B6" s="7" t="n">
+        <v>2539080</v>
       </c>
       <c r="C6" s="7">
         <f>SUM(C7,C8,C9)</f>
@@ -22175,9 +22340,8 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7">
-        <f>SUM(C7,D7,E7,F7)</f>
-        <v/>
+      <c r="B7" s="7" t="n">
+        <v>2539080</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>846360</v>
@@ -22226,9 +22390,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7">
-        <f>SUM(C8,D8,E8,F8)</f>
-        <v/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -22283,9 +22448,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7">
-        <f>SUM(C9,D9,E9,F9)</f>
-        <v/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -22340,9 +22506,8 @@
           <t>Прямые расходы</t>
         </is>
       </c>
-      <c r="B10" s="7">
-        <f>SUM(B11,B12,B13,B21,B22,B23,B24,B25,B26,B27,B28,B29,B30,B31,B32,B33,B34)</f>
-        <v/>
+      <c r="B10" s="7" t="n">
+        <v>2088109.39</v>
       </c>
       <c r="C10" s="7">
         <f>SUM(C11,C12,C13,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34)</f>
@@ -22391,9 +22556,10 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7">
-        <f>SUM(C11,D11,E11,F11)</f>
-        <v/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -22448,9 +22614,8 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7">
-        <f>SUM(C12,D12,E12,F12)</f>
-        <v/>
+      <c r="B12" s="7" t="n">
+        <v>10352</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>10352</v>
@@ -22503,9 +22668,8 @@
           <t xml:space="preserve">    Переменные</t>
         </is>
       </c>
-      <c r="B13" s="7">
-        <f>SUM(B14,B15,B16,B17,B18,B19,B20)</f>
-        <v/>
+      <c r="B13" s="7" t="n">
+        <v>50717.39</v>
       </c>
       <c r="C13" s="7">
         <f>SUM(C14,C15,C16,C17,C18,C19,C20)</f>
@@ -22554,9 +22718,10 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7">
-        <f>SUM(C14,D14,E14,F14)</f>
-        <v/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -22611,9 +22776,10 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(C15,D15,E15,F15)</f>
-        <v/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -22668,9 +22834,10 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(C16,D16,E16,F16)</f>
-        <v/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -22725,9 +22892,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7">
-        <f>SUM(C17,D17,E17,F17)</f>
-        <v/>
+      <c r="B17" s="7" t="n">
+        <v>32073.9</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>22073.9</v>
@@ -22776,9 +22942,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>SUM(C18,D18,E18,F18)</f>
-        <v/>
+      <c r="B18" s="7" t="n">
+        <v>18643.49</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>8643.49</v>
@@ -22827,9 +22992,10 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>SUM(C19,D19,E19,F19)</f>
-        <v/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -22884,9 +23050,10 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>SUM(C20,D20,E20,F20)</f>
-        <v/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -22941,9 +23108,8 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>SUM(C21,D21,E21,F21)</f>
-        <v/>
+      <c r="B21" s="7" t="n">
+        <v>820000</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>260000</v>
@@ -22992,9 +23158,8 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>SUM(C22,D22,E22,F22)</f>
-        <v/>
+      <c r="B22" s="7" t="n">
+        <v>810000</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>270000</v>
@@ -23043,9 +23208,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>SUM(C23,D23,E23,F23)</f>
-        <v/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -23100,9 +23266,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>SUM(C24,D24,E24,F24)</f>
-        <v/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -23157,9 +23324,10 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>SUM(C25,D25,E25,F25)</f>
-        <v/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -23214,9 +23382,10 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>SUM(C26,D26,E26,F26)</f>
-        <v/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -23271,9 +23440,10 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7">
-        <f>SUM(C27,D27,E27,F27)</f>
-        <v/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -23328,9 +23498,10 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7">
-        <f>SUM(C28,D28,E28,F28)</f>
-        <v/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -23385,9 +23556,10 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7">
-        <f>SUM(C29,D29,E29,F29)</f>
-        <v/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -23442,9 +23614,8 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7">
-        <f>SUM(C30,D30,E30,F30)</f>
-        <v/>
+      <c r="B30" s="7" t="n">
+        <v>8000</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>2000</v>
@@ -23493,9 +23664,8 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7">
-        <f>SUM(C31,D31,E31,F31)</f>
-        <v/>
+      <c r="B31" s="7" t="n">
+        <v>7920</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>7920</v>
@@ -23548,9 +23718,10 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>SUM(C32,D32,E32,F32)</f>
-        <v/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -23605,9 +23776,10 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>SUM(C33,D33,E33,F33)</f>
-        <v/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -23662,9 +23834,8 @@
           <t xml:space="preserve">    Общехозяйственные</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>SUM(B35,B36,B37,B38,B39,B40,B41,B42)</f>
-        <v/>
+      <c r="B34" s="7" t="n">
+        <v>381120</v>
       </c>
       <c r="C34" s="7">
         <f>SUM(C35,C36,C37,C38,C39,C40,C41,C42)</f>
@@ -23713,9 +23884,8 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>SUM(C35,D35,E35,F35)</f>
-        <v/>
+      <c r="B35" s="7" t="n">
+        <v>12500</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>7500</v>
@@ -23764,9 +23934,8 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7">
-        <f>SUM(C36,D36,E36,F36)</f>
-        <v/>
+      <c r="B36" s="7" t="n">
+        <v>195000</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>65000</v>
@@ -23815,9 +23984,8 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7">
-        <f>SUM(C37,D37,E37,F37)</f>
-        <v/>
+      <c r="B37" s="7" t="n">
+        <v>8620</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>2620</v>
@@ -23866,9 +24034,10 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7">
-        <f>SUM(C38,D38,E38,F38)</f>
-        <v/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -23923,9 +24092,8 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7">
-        <f>SUM(C39,D39,E39,F39)</f>
-        <v/>
+      <c r="B39" s="7" t="n">
+        <v>159000</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>53000</v>
@@ -23974,9 +24142,10 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>SUM(C40,D40,E40,F40)</f>
-        <v/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -24031,9 +24200,8 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>SUM(C41,D41,E41,F41)</f>
-        <v/>
+      <c r="B41" s="7" t="n">
+        <v>6000</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>2000</v>
@@ -24082,9 +24250,10 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>SUM(C42,D42,E42,F42)</f>
-        <v/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -24139,9 +24308,8 @@
           <t>Валовая прибыль</t>
         </is>
       </c>
-      <c r="B43" s="9">
-        <f>B4-B10</f>
-        <v/>
+      <c r="B43" s="9" t="n">
+        <v>450970.6100000001</v>
       </c>
       <c r="C43" s="9">
         <f>C4-C10</f>
@@ -24190,9 +24358,10 @@
           <t>Валовая рентабельность</t>
         </is>
       </c>
-      <c r="B44" s="10">
-        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
-        <v/>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>17.76%</t>
+        </is>
       </c>
       <c r="C44" s="10">
         <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
@@ -24241,9 +24410,10 @@
           <t>Косвенные расходы</t>
         </is>
       </c>
-      <c r="B45" s="7">
-        <f>SUM(B46,B47,B48,B52,B56,B57,B58,B59,B60,B63,B64,B65,B66,B67,B68,B69,B70,B71,B72,B73,B74,B75,B76,B77,B78,B79)</f>
-        <v/>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C45" s="7">
         <f>SUM(C46,C47,C48,C52,C56,C57,C58,C59,C60,C63,C64,C65,C66,C67,C68,C69,C70,C71,C72,C73,C74,C75,C76,C77,C78,C79)</f>
@@ -24292,9 +24462,10 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7">
-        <f>SUM(C46,D46,E46,F46)</f>
-        <v/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
@@ -24349,9 +24520,10 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7">
-        <f>SUM(C47,D47,E47,F47)</f>
-        <v/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -24406,9 +24578,10 @@
           <t xml:space="preserve">    Автомобиль</t>
         </is>
       </c>
-      <c r="B48" s="7">
-        <f>SUM(B49,B50,B51)</f>
-        <v/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C48" s="7">
         <f>SUM(C49,C50,C51)</f>
@@ -24457,9 +24630,10 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7">
-        <f>SUM(C49,D49,E49,F49)</f>
-        <v/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -24514,9 +24688,10 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7">
-        <f>SUM(C50,D50,E50,F50)</f>
-        <v/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -24571,9 +24746,10 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7">
-        <f>SUM(C51,D51,E51,F51)</f>
-        <v/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -24628,9 +24804,10 @@
           <t xml:space="preserve">    Офисные расходы</t>
         </is>
       </c>
-      <c r="B52" s="7">
-        <f>SUM(B53,B54,B55)</f>
-        <v/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C52" s="7">
         <f>SUM(C53,C54,C55)</f>
@@ -24679,9 +24856,10 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7">
-        <f>SUM(C53,D53,E53,F53)</f>
-        <v/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -24736,9 +24914,10 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7">
-        <f>SUM(C54,D54,E54,F54)</f>
-        <v/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -24793,9 +24972,10 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7">
-        <f>SUM(C55,D55,E55,F55)</f>
-        <v/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -24850,9 +25030,10 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7">
-        <f>SUM(C56,D56,E56,F56)</f>
-        <v/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -24907,9 +25088,10 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7">
-        <f>SUM(C57,D57,E57,F57)</f>
-        <v/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -24964,9 +25146,10 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7">
-        <f>SUM(C58,D58,E58,F58)</f>
-        <v/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -25021,9 +25204,10 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7">
-        <f>SUM(C59,D59,E59,F59)</f>
-        <v/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -25078,9 +25262,10 @@
           <t xml:space="preserve">    Командировочные расходы</t>
         </is>
       </c>
-      <c r="B60" s="7">
-        <f>SUM(B61,B62)</f>
-        <v/>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C60" s="7">
         <f>SUM(C61,C62)</f>
@@ -25129,9 +25314,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7">
-        <f>SUM(C61,D61,E61,F61)</f>
-        <v/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -25186,9 +25372,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7">
-        <f>SUM(C62,D62,E62,F62)</f>
-        <v/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -25243,9 +25430,10 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7">
-        <f>SUM(C63,D63,E63,F63)</f>
-        <v/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -25300,9 +25488,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7">
-        <f>SUM(C64,D64,E64,F64)</f>
-        <v/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -25357,9 +25546,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7">
-        <f>SUM(C65,D65,E65,F65)</f>
-        <v/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -25414,9 +25604,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7">
-        <f>SUM(C66,D66,E66,F66)</f>
-        <v/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -25471,9 +25662,10 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7">
-        <f>SUM(C67,D67,E67,F67)</f>
-        <v/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -25528,9 +25720,10 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7">
-        <f>SUM(C68,D68,E68,F68)</f>
-        <v/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -25585,9 +25778,10 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7">
-        <f>SUM(C69,D69,E69,F69)</f>
-        <v/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -25642,9 +25836,10 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7">
-        <f>SUM(C70,D70,E70,F70)</f>
-        <v/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -25699,9 +25894,10 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7">
-        <f>SUM(C71,D71,E71,F71)</f>
-        <v/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -25756,9 +25952,10 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7">
-        <f>SUM(C72,D72,E72,F72)</f>
-        <v/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -25813,9 +26010,10 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7">
-        <f>SUM(C73,D73,E73,F73)</f>
-        <v/>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -25870,9 +26068,10 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7">
-        <f>SUM(C74,D74,E74,F74)</f>
-        <v/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -25927,9 +26126,10 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7">
-        <f>SUM(C75,D75,E75,F75)</f>
-        <v/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -25984,9 +26184,10 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7">
-        <f>SUM(C76,D76,E76,F76)</f>
-        <v/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -26041,9 +26242,10 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7">
-        <f>SUM(C77,D77,E77,F77)</f>
-        <v/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -26098,9 +26300,10 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7">
-        <f>SUM(C78,D78,E78,F78)</f>
-        <v/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -26155,9 +26358,10 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7">
-        <f>SUM(C79,D79,E79,F79)</f>
-        <v/>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -26212,9 +26416,8 @@
           <t>Операционная прибыль</t>
         </is>
       </c>
-      <c r="B80" s="9">
-        <f>B43-B45</f>
-        <v/>
+      <c r="B80" s="9" t="n">
+        <v>450970.6100000001</v>
       </c>
       <c r="C80" s="9">
         <f>C43-C45</f>
@@ -26263,9 +26466,10 @@
           <t>Операционная рентабельность</t>
         </is>
       </c>
-      <c r="B81" s="10">
-        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
-        <v/>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>17.76%</t>
+        </is>
       </c>
       <c r="C81" s="10">
         <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
@@ -26314,9 +26518,10 @@
           <t>Прочие доходы</t>
         </is>
       </c>
-      <c r="B82" s="7">
-        <f>SUM(B83,B84,B85,B86)</f>
-        <v/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C82" s="7">
         <f>SUM(C83,C84,C85,C86)</f>
@@ -26365,9 +26570,10 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7">
-        <f>SUM(C83,D83,E83,F83)</f>
-        <v/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -26422,9 +26628,10 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7">
-        <f>SUM(C84,D84,E84,F84)</f>
-        <v/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -26479,9 +26686,10 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7">
-        <f>SUM(C85,D85,E85,F85)</f>
-        <v/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -26536,9 +26744,10 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7">
-        <f>SUM(C86,D86,E86,F86)</f>
-        <v/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -26593,9 +26802,10 @@
           <t>Прочие расходы</t>
         </is>
       </c>
-      <c r="B87" s="7">
-        <f>SUM(B88)</f>
-        <v/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C87" s="7">
         <f>SUM(C88)</f>
@@ -26644,9 +26854,10 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7">
-        <f>SUM(C88,D88,E88,F88)</f>
-        <v/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -26701,9 +26912,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B89" s="9">
-        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
-        <v/>
+      <c r="B89" s="9" t="n">
+        <v>450970.6100000001</v>
       </c>
       <c r="C89" s="9">
         <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
@@ -26752,9 +26962,10 @@
           <t>Рентабельность по EBITDA</t>
         </is>
       </c>
-      <c r="B90" s="10">
-        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
-        <v/>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>17.76%</t>
+        </is>
       </c>
       <c r="C90" s="10">
         <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
@@ -26803,9 +27014,10 @@
           <t>Амортизация</t>
         </is>
       </c>
-      <c r="B91" s="7">
-        <f>SUM(B92,B93)</f>
-        <v/>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C91" s="7">
         <f>SUM(C92,C93)</f>
@@ -26854,9 +27066,10 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7">
-        <f>SUM(C92,D92,E92,F92)</f>
-        <v/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -26911,9 +27124,10 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7">
-        <f>SUM(C93,D93,E93,F93)</f>
-        <v/>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -26968,9 +27182,10 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7">
-        <f>SUM(C94,D94,E94,F94)</f>
-        <v/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -27025,9 +27240,8 @@
           <t>Налог на прибыль</t>
         </is>
       </c>
-      <c r="B95" s="7">
-        <f>SUM(B96,B97)</f>
-        <v/>
+      <c r="B95" s="7" t="n">
+        <v>192000</v>
       </c>
       <c r="C95" s="7">
         <f>SUM(C96,C97)</f>
@@ -27076,9 +27290,8 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7">
-        <f>SUM(C96,D96,E96,F96)</f>
-        <v/>
+      <c r="B96" s="7" t="n">
+        <v>36000</v>
       </c>
       <c r="C96" s="7" t="n">
         <v>12000</v>
@@ -27127,9 +27340,8 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7">
-        <f>SUM(C97,D97,E97,F97)</f>
-        <v/>
+      <c r="B97" s="7" t="n">
+        <v>156000</v>
       </c>
       <c r="C97" s="7" t="n">
         <v>52000</v>
@@ -27178,9 +27390,8 @@
           <t>Чистая прибыль (убыток)</t>
         </is>
       </c>
-      <c r="B98" s="9">
-        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
-        <v/>
+      <c r="B98" s="9" t="n">
+        <v>258970.6100000001</v>
       </c>
       <c r="C98" s="9">
         <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
@@ -27229,9 +27440,10 @@
           <t>Рентабельность чистой прибыли</t>
         </is>
       </c>
-      <c r="B99" s="10">
-        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
-        <v/>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>10.20%</t>
+        </is>
       </c>
       <c r="C99" s="10">
         <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
